--- a/examples/002463_沪电股份_估值模型.xlsx
+++ b/examples/002463_沪电股份_估值模型.xlsx
@@ -19,12 +19,29 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIN" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity_Roll" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative_Val" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCFE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative_Val" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="SCEN_SWITCH">Assumptions!$C$5</definedName>
+    <definedName name="WACC_USED">Assumptions!$C$86</definedName>
+    <definedName name="WACC_CALC">Assumptions!$C$84</definedName>
+    <definedName name="TERM_G">Assumptions!$C$87</definedName>
+    <definedName name="KE">Assumptions!$C$82</definedName>
+    <definedName name="KD">Assumptions!$C$83</definedName>
+    <definedName name="RF_RATE">Assumptions!$C$75</definedName>
+    <definedName name="ERP">Assumptions!$C$76</definedName>
+    <definedName name="BETA_U">Assumptions!$C$77</definedName>
+    <definedName name="TAX_RATE_Y1">Assumptions!$C$37</definedName>
+    <definedName name="PAYOUT_Y1">Assumptions!$C$57</definedName>
+    <definedName name="MIN_CASH_PCT">Assumptions!$C$61</definedName>
+    <definedName name="SHARES_DIL">Equity_Roll!$C$21</definedName>
+    <definedName name="DCF_PS">DCF!$D$25</definedName>
+    <definedName name="FCFE_PS">FCFE!$D$18</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="1000" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -872,7 +889,7 @@
         </is>
       </c>
       <c r="C24" s="4">
-        <f>TEXT(Summary!C11,"0.00")&amp;" ~ "&amp;TEXT(Summary!D11,"0.00")</f>
+        <f>TEXT(Summary!C12,"0.00")&amp;" ~ "&amp;TEXT(Summary!D12,"0.00")</f>
         <v/>
       </c>
     </row>
@@ -883,7 +900,7 @@
         </is>
       </c>
       <c r="C25" s="4">
-        <f>Checks!F22</f>
+        <f>Checks!F24</f>
         <v/>
       </c>
     </row>
@@ -5866,6 +5883,487 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>沪电股份 — FCFE 股权自由现金流估值 (Ke折现, 与FCFF双视图)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>单位: 人民币百万元 | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得股权价值, 无需EV→Equity桥</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>归母净利润</t>
+        </is>
+      </c>
+      <c r="E4" s="26">
+        <f>IS!E20</f>
+        <v/>
+      </c>
+      <c r="F4" s="26">
+        <f>IS!F20</f>
+        <v/>
+      </c>
+      <c r="G4" s="26">
+        <f>IS!G20</f>
+        <v/>
+      </c>
+      <c r="H4" s="26">
+        <f>IS!H20</f>
+        <v/>
+      </c>
+      <c r="I4" s="26">
+        <f>IS!I20</f>
+        <v/>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>＝IS归母净利(含FIN调度后的利息)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>加: D&amp;A</t>
+        </is>
+      </c>
+      <c r="E5" s="26">
+        <f>PPE!E19</f>
+        <v/>
+      </c>
+      <c r="F5" s="26">
+        <f>PPE!F19</f>
+        <v/>
+      </c>
+      <c r="G5" s="26">
+        <f>PPE!G19</f>
+        <v/>
+      </c>
+      <c r="H5" s="26">
+        <f>PPE!H19</f>
+        <v/>
+      </c>
+      <c r="I5" s="26">
+        <f>PPE!I19</f>
+        <v/>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>＝PP&amp;E页折旧+无形摊销</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>减: ΔNWC</t>
+        </is>
+      </c>
+      <c r="E6" s="26">
+        <f>Schedules!E18</f>
+        <v/>
+      </c>
+      <c r="F6" s="26">
+        <f>Schedules!F18</f>
+        <v/>
+      </c>
+      <c r="G6" s="26">
+        <f>Schedules!G18</f>
+        <v/>
+      </c>
+      <c r="H6" s="26">
+        <f>Schedules!H18</f>
+        <v/>
+      </c>
+      <c r="I6" s="26">
+        <f>Schedules!I18</f>
+        <v/>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>＝Schedules; NWC增加为现金流出</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>减: Capex</t>
+        </is>
+      </c>
+      <c r="E7" s="26">
+        <f>PPE!E14</f>
+        <v/>
+      </c>
+      <c r="F7" s="26">
+        <f>PPE!F14</f>
+        <v/>
+      </c>
+      <c r="G7" s="26">
+        <f>PPE!G14</f>
+        <v/>
+      </c>
+      <c r="H7" s="26">
+        <f>PPE!H14</f>
+        <v/>
+      </c>
+      <c r="I7" s="26">
+        <f>PPE!I14</f>
+        <v/>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>＝PP&amp;E页资本开支</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>加: 净新增借款</t>
+        </is>
+      </c>
+      <c r="E8" s="26">
+        <f>FIN!E57</f>
+        <v/>
+      </c>
+      <c r="F8" s="26">
+        <f>FIN!F57</f>
+        <v/>
+      </c>
+      <c r="G8" s="26">
+        <f>FIN!G57</f>
+        <v/>
+      </c>
+      <c r="H8" s="26">
+        <f>FIN!H57</f>
+        <v/>
+      </c>
+      <c r="I8" s="26">
+        <f>FIN!I57</f>
+        <v/>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>＝FIN四档债务期末-期初(revolver新增-sweep偿还-计划还款); 股权口径下债务净变动归股东</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>FCFE</t>
+        </is>
+      </c>
+      <c r="E9" s="35">
+        <f>E4+E5-E6-E7+E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="35">
+        <f>F4+F5-F6-F7+F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="35">
+        <f>G4+G5-G6-G7+G8</f>
+        <v/>
+      </c>
+      <c r="H9" s="35">
+        <f>H4+H5-H6-H7+H8</f>
+        <v/>
+      </c>
+      <c r="I9" s="35">
+        <f>I4+I5-I6-I7+I8</f>
+        <v/>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>＝归母+D&amp;A-ΔNWC-Capex+净新增借款</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>折现年序(年中)</t>
+        </is>
+      </c>
+      <c r="E10" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H10" s="41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I10" s="41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>年中折现, 与DCF页同口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>折现因子 (Ke)</t>
+        </is>
+      </c>
+      <c r="E11" s="31">
+        <f>1/(1+KE)^E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="31">
+        <f>1/(1+KE)^F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="31">
+        <f>1/(1+KE)^G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="31">
+        <f>1/(1+KE)^H10</f>
+        <v/>
+      </c>
+      <c r="I11" s="31">
+        <f>1/(1+KE)^I10</f>
+        <v/>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>＝1/(1+Ke)^t; Ke为named range(Assumptions股权成本)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>PV(FCFE)</t>
+        </is>
+      </c>
+      <c r="E12" s="26">
+        <f>E9*E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="26">
+        <f>F9*F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="26">
+        <f>G9*G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="26">
+        <f>H9*H11</f>
+        <v/>
+      </c>
+      <c r="I12" s="26">
+        <f>I9*I11</f>
+        <v/>
+      </c>
+      <c r="J12" s="11" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>显性期PV合计 (2026-2030)</t>
+        </is>
+      </c>
+      <c r="D14" s="35">
+        <f>SUM(E12:I12)</f>
+        <v/>
+      </c>
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>终值 TV (Gordon)</t>
+        </is>
+      </c>
+      <c r="D15" s="26">
+        <f>I9*(1+TERM_G)/(KE-TERM_G)</f>
+        <v/>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>＝FCFE2030×(1+g)/(Ke-g); Ke/g均为named range</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>PV(终值)</t>
+        </is>
+      </c>
+      <c r="D16" s="26">
+        <f>D15*I11</f>
+        <v/>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>终值按t=4.5折现(与DCF页一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>股权价值 (FCFE口径)</t>
+        </is>
+      </c>
+      <c r="D17" s="35">
+        <f>D14+D16</f>
+        <v/>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>FCFE直接折现为股权价值, 无需净现金桥</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>每股价值 (元)</t>
+        </is>
+      </c>
+      <c r="D18" s="15">
+        <f>D17/SHARES_DIL</f>
+        <v/>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>＝股权价值/稀释股数(named range)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>对照: FCFF口径每股价值 (元)</t>
+        </is>
+      </c>
+      <c r="D19" s="14">
+        <f>DCF!D25</f>
+        <v/>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>＝DCF页主输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>两法差异 (FCFE/FCFF-1)</t>
+        </is>
+      </c>
+      <c r="D20" s="42">
+        <f>D18/D19-1</f>
+        <v/>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Checks页含一致性信息行</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>两法差异原因</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>①折现率不同: FCFF按WACC(全资本成本, 税盾在分母)折现, FCFE按Ke(纯股权成本)折现; ②口径不同: FCFF为企业自由现金流, 须经EV→Equity桥加回净现金/扣有息负债, FCFE已含净新增借款、直接对应股权; ③杠杆路径不同: FCFE逐年反映FIN页revolver/sweep实际债务调度(资本结构动态变化), FCFF隐含目标结构(Wd)恒定; ④两法在"恒定资本结构+一致税盾处理"下理论等价, 实务差异主要来自债务调度时点、净现金桥与折现率差; 差异幅度大时应复查融资假设</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6393,7 +6891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6894,7 +7392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7645,13 +8143,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8072,132 +8570,168 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>信息项: 隐含折旧率(折旧/期初固资净值)</t>
-        </is>
-      </c>
-      <c r="E16" s="55">
-        <f>PPE!E20</f>
-        <v/>
-      </c>
-      <c r="F16" s="55">
-        <f>PPE!F20</f>
-        <v/>
-      </c>
-      <c r="G16" s="55">
-        <f>PPE!G20</f>
-        <v/>
-      </c>
-      <c r="H16" s="55">
-        <f>PPE!H20</f>
-        <v/>
-      </c>
-      <c r="I16" s="55">
-        <f>PPE!I20</f>
-        <v/>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>信息行: 合理带宽8%-18%</t>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>12. Named ranges存在性 (审计轨迹, 15个)</t>
+        </is>
+      </c>
+      <c r="B15" s="54">
+        <f>AND(ISNUMBER(INDIRECT("SCEN_SWITCH")),ISNUMBER(INDIRECT("WACC_USED")),ISNUMBER(INDIRECT("WACC_CALC")),ISNUMBER(INDIRECT("TERM_G")),ISNUMBER(INDIRECT("KE")),ISNUMBER(INDIRECT("KD")),ISNUMBER(INDIRECT("RF_RATE")),ISNUMBER(INDIRECT("ERP")),ISNUMBER(INDIRECT("BETA_U")),ISNUMBER(INDIRECT("TAX_RATE_Y1")),ISNUMBER(INDIRECT("PAYOUT_Y1")),ISNUMBER(INDIRECT("MIN_CASH_PCT")),ISNUMBER(INDIRECT("SHARES_DIL")),ISNUMBER(INDIRECT("DCF_PS")),ISNUMBER(INDIRECT("FCFE_PS")))</f>
+        <v/>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>WACC采用值/永续g/Ke/Kd/rf/ERP/βu/税率/股利/最低现金/情景开关/稀释股数/DCF&amp;FCFE每股; 任一named range被删则FALSE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>信息项: 2026E模型收入/一致预期</t>
-        </is>
-      </c>
-      <c r="B17" s="16">
-        <f>IS!E4/Assumptions!$C$12</f>
+          <t>信息项: 隐含折旧率(折旧/期初固资净值)</t>
+        </is>
+      </c>
+      <c r="E17" s="55">
+        <f>PPE!E20</f>
+        <v/>
+      </c>
+      <c r="F17" s="55">
+        <f>PPE!F20</f>
+        <v/>
+      </c>
+      <c r="G17" s="55">
+        <f>PPE!G20</f>
+        <v/>
+      </c>
+      <c r="H17" s="55">
+        <f>PPE!H20</f>
+        <v/>
+      </c>
+      <c r="I17" s="55">
+        <f>PPE!I20</f>
         <v/>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>接近100%即基准贴合一致预期</t>
+          <t>信息行: 合理带宽8%-18%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>信息项: 2026E模型归母/一致预期</t>
+          <t>信息项: 2026E模型收入/一致预期</t>
         </is>
       </c>
       <c r="B18" s="16">
-        <f>IS!E20/Assumptions!$C$13</f>
-        <v/>
+        <f>IS!E4/Assumptions!$C$12</f>
+        <v/>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>接近100%即基准贴合一致预期</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>信息项: WACC计算值/采用值</t>
+          <t>信息项: 2026E模型归母/一致预期</t>
         </is>
       </c>
       <c r="B19" s="16">
-        <f>Assumptions!C84</f>
-        <v/>
-      </c>
-      <c r="C19" s="16">
-        <f>Assumptions!C86</f>
-        <v/>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>左=计算值, 右=采用值(override为空时两者相等)</t>
-        </is>
+        <f>IS!E20/Assumptions!$C$13</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>信息项: WACC计算值/采用值</t>
+        </is>
+      </c>
+      <c r="B20" s="16">
+        <f>Assumptions!C84</f>
+        <v/>
+      </c>
+      <c r="C20" s="16">
+        <f>Assumptions!C86</f>
+        <v/>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>左=计算值, 右=采用值(override为空时两者相等)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>信息项: FCFE/FCFF每股价值比</t>
+        </is>
+      </c>
+      <c r="B21" s="16">
+        <f>FCFE!D18/DCF!D25</f>
+        <v/>
+      </c>
+      <c r="C21" s="14">
+        <f>FCFE!D18</f>
+        <v/>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>左=FCFE/FCFF比值, 右=FCFE每股(元); 两法差异原因见FCFE页底部注记</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>信息项: 2030E现金 vs 最低现金</t>
         </is>
       </c>
-      <c r="B20" s="26">
+      <c r="B22" s="26">
         <f>BS!I4</f>
         <v/>
       </c>
-      <c r="C20" s="26">
+      <c r="C22" s="26">
         <f>FIN!I13</f>
         <v/>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>两者应相等(sweep后现金=最低现金, 溢出去理财)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="56" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">汇总: 全部通过 = </t>
         </is>
       </c>
-      <c r="F22" s="57">
-        <f>IF(AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14),"全部通过=TRUE","存在未通过=FALSE")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="F24" s="57">
+        <f>IF(AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15),"全部通过=TRUE","存在未通过=FALSE")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>布尔汇总</t>
         </is>
       </c>
-      <c r="F23" s="27">
-        <f>AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14)</f>
+      <c r="F25" s="27">
+        <f>AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8210,7 +8744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8441,147 +8975,192 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>现价 (2026-08-17)</t>
+          <t>FCFE股权现金流 — 基准</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Ke折现(股权口径)</t>
         </is>
       </c>
       <c r="C10" s="14">
-        <f>Assumptions!$C$7</f>
+        <f>FCFE!D18</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>Assumptions!$C$7</f>
-        <v/>
-      </c>
-      <c r="E10" s="14">
-        <f>Assumptions!$C$7</f>
-        <v/>
+        <f>FCFE!D18</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>(C10+D10)/2</f>
+        <v/>
+      </c>
+      <c r="F10" s="16">
+        <f>E10/Assumptions!$C$7-1</f>
+        <v/>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>FCFE=归母+D&amp;A-ΔNWC-Capex+净新增借款(FIN调度), 与FCFF双视图对照</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>现价 (2026-08-17)</t>
+        </is>
+      </c>
+      <c r="C11" s="14">
+        <f>Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="D11" s="14">
+        <f>Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>Assumptions!$C$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>综合参考区间(全方法包络)</t>
         </is>
       </c>
-      <c r="C11" s="17">
-        <f>MIN(C5:C9)</f>
-        <v/>
-      </c>
-      <c r="D11" s="17">
-        <f>MAX(D5:D9)</f>
-        <v/>
-      </c>
-      <c r="E11" s="17">
-        <f>(C11+D11)/2</f>
-        <v/>
-      </c>
-      <c r="F11" s="18">
-        <f>E11/Assumptions!$C$7-1</f>
-        <v/>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="C12" s="17">
+        <f>MIN(C5:C10)</f>
+        <v/>
+      </c>
+      <c r="D12" s="17">
+        <f>MAX(D5:D10)</f>
+        <v/>
+      </c>
+      <c r="E12" s="17">
+        <f>(C12+D12)/2</f>
+        <v/>
+      </c>
+      <c r="F12" s="18">
+        <f>E12/Assumptions!$C$7-1</f>
+        <v/>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>熊简化法DCF下限 ~ 牛简化法/相对估值上限的包络</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>区间可视化 (每个▮≈10元, 起点=区间低值)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>方法</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>区间条(低→高, 括号为现价相对位置)</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>DCF绝对估值 — 基准</t>
-        </is>
-      </c>
-      <c r="B15" s="20">
-        <f>REPT("▮",MAX(1,ROUND((D5-C5)/10,0)))&amp;"  ["&amp;TEXT(C5,"0")&amp;"—"&amp;TEXT(D5,"0")&amp;"]"</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>DCF绝对估值 — 熊市</t>
+          <t>DCF绝对估值 — 基准</t>
         </is>
       </c>
       <c r="B16" s="20">
-        <f>REPT("▮",MAX(1,ROUND((D6-C6)/10,0)))&amp;"  ["&amp;TEXT(C6,"0")&amp;"—"&amp;TEXT(D6,"0")&amp;"]"</f>
+        <f>REPT("▮",MAX(1,ROUND((D5-C5)/10,0)))&amp;"  ["&amp;TEXT(C5,"0")&amp;"—"&amp;TEXT(D5,"0")&amp;"]"</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>DCF绝对估值 — 牛市</t>
+          <t>DCF绝对估值 — 熊市</t>
         </is>
       </c>
       <c r="B17" s="20">
-        <f>REPT("▮",MAX(1,ROUND((D7-C7)/10,0)))&amp;"  ["&amp;TEXT(C7,"0")&amp;"—"&amp;TEXT(D7,"0")&amp;"]"</f>
+        <f>REPT("▮",MAX(1,ROUND((D6-C6)/10,0)))&amp;"  ["&amp;TEXT(C6,"0")&amp;"—"&amp;TEXT(D6,"0")&amp;"]"</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>相对估值 — 模型2026E归母</t>
+          <t>DCF绝对估值 — 牛市</t>
         </is>
       </c>
       <c r="B18" s="20">
-        <f>REPT("▮",MAX(1,ROUND((D8-C8)/10,0)))&amp;"  ["&amp;TEXT(C8,"0")&amp;"—"&amp;TEXT(D8,"0")&amp;"]"</f>
+        <f>REPT("▮",MAX(1,ROUND((D7-C7)/10,0)))&amp;"  ["&amp;TEXT(C7,"0")&amp;"—"&amp;TEXT(D7,"0")&amp;"]"</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
+          <t>相对估值 — 模型2026E归母</t>
+        </is>
+      </c>
+      <c r="B19" s="20">
+        <f>REPT("▮",MAX(1,ROUND((D8-C8)/10,0)))&amp;"  ["&amp;TEXT(C8,"0")&amp;"—"&amp;TEXT(D8,"0")&amp;"]"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
           <t>相对估值 — 一致预期2026E归母</t>
         </is>
       </c>
-      <c r="B19" s="20">
+      <c r="B20" s="20">
         <f>REPT("▮",MAX(1,ROUND((D9-C9)/10,0)))&amp;"  ["&amp;TEXT(C9,"0")&amp;"—"&amp;TEXT(D9,"0")&amp;"]"</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>FCFE股权现金流 — 基准</t>
+        </is>
+      </c>
+      <c r="B21" s="20">
+        <f>REPT("▮",MAX(1,ROUND((D10-C10)/10,0)))&amp;"  ["&amp;TEXT(C10,"0")&amp;"—"&amp;TEXT(D10,"0")&amp;"]"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>关键假设提示</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>WACC采用值与可比beta联动(Assumptions第十节); 三情景主模型切换见Assumptions情景开关; 校验状态见Checks页</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B17:G17"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/002463_沪电股份_估值模型.xlsx
+++ b/examples/002463_沪电股份_估值模型.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue_Segments" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CF" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedules" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIN" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity_Roll" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCFE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative_Val" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Revenue_Segments" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="IS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="BS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CF" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Schedules" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PPE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="FIN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Equity_Roll" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="DCF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="FCFE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Relative_Val" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Checks" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="SCEN_SWITCH">Assumptions!$C$5</definedName>
@@ -39,8 +39,8 @@
     <definedName name="PAYOUT_Y1">Assumptions!$C$57</definedName>
     <definedName name="MIN_CASH_PCT">Assumptions!$C$61</definedName>
     <definedName name="SHARES_DIL">Equity_Roll!$C$21</definedName>
-    <definedName name="DCF_PS">DCF!$D$25</definedName>
-    <definedName name="FCFE_PS">FCFE!$D$18</definedName>
+    <definedName name="DCF_PS">DCF!$D$26</definedName>
+    <definedName name="FCFE_PS">FCFE!$D$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="1000" iterateDelta="0.0001"/>
 </workbook>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C21" s="4">
-        <f>DCF!D25</f>
+        <f>DCF!D26</f>
         <v/>
       </c>
     </row>
@@ -942,7 +942,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>5. DCF年中折现: 估值基准日2026-08-17, t=0.5/1.5/.../4.5; EV→Equity桥含货币资金/交易性金融资产/其他权益工具投资/有息负债;</t>
+          <t>5. DCF年中折现: 估值基准日2026-08-17, t=0.5/1.5/.../4.5; EV→Equity桥含货币资金/交易性金融资产/其他权益工具投资/有息负债/少数股东权益;</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5767,101 +5767,117 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>减: 少数股东权益(2025A末)</t>
+        </is>
+      </c>
+      <c r="D23" s="26">
+        <f>-BS!D44</f>
+        <v/>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>EV桥得归母口径股权价值须扣少数股东权益(账面值); 无少数股东权益的标的为0, 不影响结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>净现金调整合计</t>
         </is>
       </c>
-      <c r="D23" s="26">
-        <f>D19+D20+D21+D22</f>
-        <v/>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="D24" s="26">
+        <f>D19+D20+D21+D22+D23</f>
+        <v/>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>供Sensitivity/Scenarios页引用</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>股权价值</t>
-        </is>
-      </c>
-      <c r="D24" s="35">
-        <f>D18+D23</f>
-        <v/>
-      </c>
-      <c r="J24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>股权价值</t>
+        </is>
+      </c>
+      <c r="D25" s="35">
+        <f>D18+D24</f>
+        <v/>
+      </c>
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>每股价值 (元)</t>
         </is>
       </c>
-      <c r="D25" s="15">
-        <f>D24/Equity_Roll!$C$21</f>
-        <v/>
-      </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="D26" s="15">
+        <f>D25/Equity_Roll!$C$21</f>
+        <v/>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>＝股权价值/稀释股数(Equity_Roll页)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>现价 (2026-08-17)</t>
         </is>
       </c>
-      <c r="D26" s="14">
+      <c r="D27" s="14">
         <f>Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>隐含涨跌幅</t>
         </is>
       </c>
-      <c r="D27" s="42">
-        <f>D25/D26-1</f>
-        <v/>
-      </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>隐含2026E P/E</t>
-        </is>
-      </c>
-      <c r="D28" s="43">
-        <f>D24/IS!E20</f>
-        <v/>
-      </c>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>＝股权价值/2026E归母</t>
-        </is>
-      </c>
+      <c r="D28" s="42">
+        <f>D26/D27-1</f>
+        <v/>
+      </c>
+      <c r="J28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>隐含2026E P/E</t>
+        </is>
+      </c>
+      <c r="D29" s="43">
+        <f>D25/IS!E20</f>
+        <v/>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>＝股权价值/2026E归母</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
           <t>隐含2026E EV/EBITDA</t>
         </is>
       </c>
-      <c r="D29" s="43">
+      <c r="D30" s="43">
         <f>D18/(IS!E23+PPE!E19)</f>
         <v/>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>注: 估值基准日2026-08-17, 与2026财年现金流起点存在时间错位; 年中折现(t=0.5起)为该错位的标准近似处理, 不再单独做stub调整</t>
         </is>
@@ -5870,7 +5886,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5883,7 +5899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5908,7 +5924,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>单位: 人民币百万元 | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得股权价值, 无需EV→Equity桥</t>
+          <t>单位: 人民币百万元 | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得归母股权价值(少数股东权益见DCF页EV→Equity桥); 终值取正常化FCFE(净新增借款按g封顶)</t>
         </is>
       </c>
     </row>
@@ -6110,248 +6126,296 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>理财净变动(勾稽参考, 不计入FCFE)</t>
+        </is>
+      </c>
+      <c r="E9" s="26">
+        <f>-FIN!E62</f>
+        <v/>
+      </c>
+      <c r="F9" s="26">
+        <f>-FIN!F62</f>
+        <v/>
+      </c>
+      <c r="G9" s="26">
+        <f>-FIN!G62</f>
+        <v/>
+      </c>
+      <c r="H9" s="26">
+        <f>-FIN!H62</f>
+        <v/>
+      </c>
+      <c r="I9" s="26">
+        <f>-FIN!I62</f>
+        <v/>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>＝-FIN理财净变动: sweep溢出购买理财为现金↔理财的形态转换(资产仍在表内归属股东), 故不计入FCFE; 显性列示供FCFE↔FCFF差异勾稽(FCFF也未扣理财购买, 两法在此口径一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>FCFE</t>
         </is>
       </c>
-      <c r="E9" s="35">
+      <c r="E10" s="35">
         <f>E4+E5-E6-E7+E8</f>
         <v/>
       </c>
-      <c r="F9" s="35">
+      <c r="F10" s="35">
         <f>F4+F5-F6-F7+F8</f>
         <v/>
       </c>
-      <c r="G9" s="35">
+      <c r="G10" s="35">
         <f>G4+G5-G6-G7+G8</f>
         <v/>
       </c>
-      <c r="H9" s="35">
+      <c r="H10" s="35">
         <f>H4+H5-H6-H7+H8</f>
         <v/>
       </c>
-      <c r="I9" s="35">
+      <c r="I10" s="35">
         <f>I4+I5-I6-I7+I8</f>
         <v/>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>＝归母+D&amp;A-ΔNWC-Capex+净新增借款</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>折现年序(年中)</t>
-        </is>
-      </c>
-      <c r="E10" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G10" s="41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H10" s="41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I10" s="41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>年中折现, 与DCF页同口径</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>折现因子 (Ke)</t>
-        </is>
-      </c>
-      <c r="E11" s="31">
-        <f>1/(1+KE)^E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="31">
-        <f>1/(1+KE)^F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="31">
-        <f>1/(1+KE)^G10</f>
-        <v/>
-      </c>
-      <c r="H11" s="31">
-        <f>1/(1+KE)^H10</f>
-        <v/>
-      </c>
-      <c r="I11" s="31">
-        <f>1/(1+KE)^I10</f>
-        <v/>
+          <t>折现年序(年中)</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G11" s="41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H11" s="41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I11" s="41" t="n">
+        <v>4.5</v>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>＝1/(1+Ke)^t; Ke为named range(Assumptions股权成本)</t>
+          <t>年中折现, 与DCF页同口径</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>折现因子 (Ke)</t>
+        </is>
+      </c>
+      <c r="E12" s="31">
+        <f>1/(1+KE)^E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="31">
+        <f>1/(1+KE)^F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="31">
+        <f>1/(1+KE)^G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="31">
+        <f>1/(1+KE)^H11</f>
+        <v/>
+      </c>
+      <c r="I12" s="31">
+        <f>1/(1+KE)^I11</f>
+        <v/>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>＝1/(1+Ke)^t; Ke为named range(Assumptions股权成本)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>PV(FCFE)</t>
         </is>
       </c>
-      <c r="E12" s="26">
-        <f>E9*E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="26">
-        <f>F9*F11</f>
-        <v/>
-      </c>
-      <c r="G12" s="26">
-        <f>G9*G11</f>
-        <v/>
-      </c>
-      <c r="H12" s="26">
-        <f>H9*H11</f>
-        <v/>
-      </c>
-      <c r="I12" s="26">
-        <f>I9*I11</f>
-        <v/>
-      </c>
-      <c r="J12" s="11" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="E13" s="26">
+        <f>E10*E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="26">
+        <f>F10*F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="26">
+        <f>G10*G12</f>
+        <v/>
+      </c>
+      <c r="H13" s="26">
+        <f>H10*H12</f>
+        <v/>
+      </c>
+      <c r="I13" s="26">
+        <f>I10*I12</f>
+        <v/>
+      </c>
+      <c r="J13" s="11" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>显性期PV合计 (2026-2030)</t>
         </is>
       </c>
-      <c r="D14" s="35">
-        <f>SUM(E12:I12)</f>
-        <v/>
-      </c>
-      <c r="J14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>终值 TV (Gordon)</t>
-        </is>
-      </c>
-      <c r="D15" s="26">
-        <f>I9*(1+TERM_G)/(KE-TERM_G)</f>
-        <v/>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>＝FCFE2030×(1+g)/(Ke-g); Ke/g均为named range</t>
-        </is>
-      </c>
+      <c r="D15" s="35">
+        <f>SUM(E13:I13)</f>
+        <v/>
+      </c>
+      <c r="J15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>正常化FCFE (2030E, 终值口径)</t>
+        </is>
+      </c>
+      <c r="D16" s="26">
+        <f>I10-I8+MIN(I8,FIN!I56*TERM_G)</f>
+        <v/>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>净新增借款按g封顶: 终值内净新增借款取MIN(实际调度, 2030E期末有息负债×g), 防止显性期末大额净融资被Gordon公式永续外推; 去杠杆/平稳年(实际≤封顶值)维持实际调度不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>终值 TV (Gordon, 正常化FCFE)</t>
+        </is>
+      </c>
+      <c r="D17" s="26">
+        <f>D16*(1+TERM_G)/(KE-TERM_G)</f>
+        <v/>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>＝正常化FCFE2030×(1+g)/(Ke-g); Ke/g均为named range</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>PV(终值)</t>
         </is>
       </c>
-      <c r="D16" s="26">
-        <f>D15*I11</f>
-        <v/>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="D18" s="26">
+        <f>D17*I12</f>
+        <v/>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>终值按t=4.5折现(与DCF页一致)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>股权价值 (FCFE口径)</t>
         </is>
       </c>
-      <c r="D17" s="35">
-        <f>D14+D16</f>
-        <v/>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="D19" s="35">
+        <f>D15+D18</f>
+        <v/>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>FCFE直接折现为股权价值, 无需净现金桥</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>每股价值 (元)</t>
-        </is>
-      </c>
-      <c r="D18" s="15">
-        <f>D17/SHARES_DIL</f>
-        <v/>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>＝股权价值/稀释股数(named range)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>对照: FCFF口径每股价值 (元)</t>
-        </is>
-      </c>
-      <c r="D19" s="14">
-        <f>DCF!D25</f>
-        <v/>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>＝DCF页主输出</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>每股价值 (元)</t>
+        </is>
+      </c>
+      <c r="D20" s="15">
+        <f>D19/SHARES_DIL</f>
+        <v/>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>＝股权价值/稀释股数(named range)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>对照: FCFF口径每股价值 (元)</t>
+        </is>
+      </c>
+      <c r="D21" s="14">
+        <f>DCF!D26</f>
+        <v/>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>＝DCF页主输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>两法差异 (FCFE/FCFF-1)</t>
         </is>
       </c>
-      <c r="D20" s="42">
-        <f>D18/D19-1</f>
-        <v/>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="D22" s="42">
+        <f>D20/D21-1</f>
+        <v/>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve"> Checks页含一致性信息行</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>两法差异原因</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>①折现率不同: FCFF按WACC(全资本成本, 税盾在分母)折现, FCFE按Ke(纯股权成本)折现; ②口径不同: FCFF为企业自由现金流, 须经EV→Equity桥加回净现金/扣有息负债, FCFE已含净新增借款、直接对应股权; ③杠杆路径不同: FCFE逐年反映FIN页revolver/sweep实际债务调度(资本结构动态变化), FCFF隐含目标结构(Wd)恒定; ④两法在"恒定资本结构+一致税盾处理"下理论等价, 实务差异主要来自债务调度时点、净现金桥与折现率差; 差异幅度大时应复查融资假设</t>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>①折现率不同: FCFF按WACC(全资本成本, 税盾在分母)折现, FCFE按Ke(纯股权成本)折现; ②口径不同: FCFF为企业自由现金流, 须经EV→Equity桥加回净现金/扣有息负债/扣少数股东权益, FCFE基于归母净利折现、直接对应归母股权价值, 少数股东权益已在DCF页EV→Equity桥扣除, 本页无需再扣; ③杠杆路径不同: FCFE逐年反映FIN页revolver/sweep实际债务调度(资本结构动态变化), FCFF隐含目标结构(Wd)恒定; ④理财净变动(上行勾稽参考行)为现金形态转换, 两法均未计入, 不构成差异来源; ⑤两法在"恒定资本结构+一致税盾处理"下理论等价, 实务差异主要来自债务调度时点、净现金桥与折现率差; 差异幅度大时应复查融资假设</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="B23:J23"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B21:J21"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6964,23 +7028,23 @@
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+C$5)/($B6-C$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+C$5)/($B6-C$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+D$5)/($B6-D$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+D$5)/($B6-D$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+E$5)/($B6-E$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+E$5)/($B6-E$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+F$5)/($B6-F$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+F$5)/($B6-F$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+G$5)/($B6-G$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+G$5)/($B6-G$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -6990,23 +7054,23 @@
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+C$5)/($B7-C$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+C$5)/($B7-C$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+D$5)/($B7-D$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+D$5)/($B7-D$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+E$5)/($B7-E$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+E$5)/($B7-E$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+F$5)/($B7-F$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+F$5)/($B7-F$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+G$5)/($B7-G$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+G$5)/($B7-G$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -7016,23 +7080,23 @@
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+C$5)/($B8-C$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+C$5)/($B8-C$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+D$5)/($B8-D$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+D$5)/($B8-D$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E8" s="49">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+E$5)/($B8-E$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+E$5)/($B8-E$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+F$5)/($B8-F$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+F$5)/($B8-F$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+G$5)/($B8-G$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+G$5)/($B8-G$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -7042,23 +7106,23 @@
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+C$5)/($B9-C$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+C$5)/($B9-C$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+D$5)/($B9-D$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+D$5)/($B9-D$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+E$5)/($B9-E$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+E$5)/($B9-E$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+F$5)/($B9-F$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+F$5)/($B9-F$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+G$5)/($B9-G$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+G$5)/($B9-G$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -7068,23 +7132,23 @@
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+C$5)/($B10-C$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+C$5)/($B10-C$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+D$5)/($B10-D$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+D$5)/($B10-D$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+E$5)/($B10-E$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+E$5)/($B10-E$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+F$5)/($B10-F$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+F$5)/($B10-F$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+G$5)/($B10-G$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+G$5)/($B10-G$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -7313,11 +7377,11 @@
         <v>-40</v>
       </c>
       <c r="C24" s="14">
-        <f>((DCF!E$10+$B24/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B24/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B24/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B24/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B24/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B24/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B24/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B24/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B24/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B24/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B24/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B24/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>C24/DCF!$D$25-1</f>
+        <f>C24/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7326,11 +7390,11 @@
         <v>-20</v>
       </c>
       <c r="C25" s="14">
-        <f>((DCF!E$10+$B25/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B25/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B25/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B25/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B25/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B25/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B25/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B25/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B25/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B25/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B25/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B25/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>C25/DCF!$D$25-1</f>
+        <f>C25/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7339,11 +7403,11 @@
         <v>0</v>
       </c>
       <c r="C26" s="49">
-        <f>((DCF!E$10+$B26/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B26/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>C26/DCF!$D$25-1</f>
+        <f>C26/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7352,11 +7416,11 @@
         <v>20</v>
       </c>
       <c r="C27" s="14">
-        <f>((DCF!E$10+$B27/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B27/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>C27/DCF!$D$25-1</f>
+        <f>C27/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7365,11 +7429,11 @@
         <v>40</v>
       </c>
       <c r="C28" s="14">
-        <f>((DCF!E$10+$B28/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B28/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B28/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B28/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B28/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B28/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B28/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B28/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B28/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B28/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B28/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B28/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>C28/DCF!$D$25-1</f>
+        <f>C28/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7617,7 +7681,7 @@
         </is>
       </c>
       <c r="B12" s="17">
-        <f>(E11/(1+Assumptions!$C$86)^0.5+F11/(1+Assumptions!$C$86)^1.5+G11/(1+Assumptions!$C$86)^2.5+H11/(1+Assumptions!$C$86)^3.5+I11/(1+Assumptions!$C$86)^4.5+I11*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(E11/(1+Assumptions!$C$86)^0.5+F11/(1+Assumptions!$C$86)^1.5+G11/(1+Assumptions!$C$86)^2.5+H11/(1+Assumptions!$C$86)^3.5+I11/(1+Assumptions!$C$86)^4.5+I11*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -7796,7 +7860,7 @@
         </is>
       </c>
       <c r="B21" s="17">
-        <f>DCF!D25</f>
+        <f>DCF!D26</f>
         <v/>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -7982,7 +8046,7 @@
         </is>
       </c>
       <c r="B31" s="17">
-        <f>(E30/(1+Assumptions!$C$86)^0.5+F30/(1+Assumptions!$C$86)^1.5+G30/(1+Assumptions!$C$86)^2.5+H30/(1+Assumptions!$C$86)^3.5+I30/(1+Assumptions!$C$86)^4.5+I30*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(E30/(1+Assumptions!$C$86)^0.5+F30/(1+Assumptions!$C$86)^1.5+G30/(1+Assumptions!$C$86)^2.5+H30/(1+Assumptions!$C$86)^3.5+I30/(1+Assumptions!$C$86)^4.5+I30*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -8433,7 +8497,7 @@
         </is>
       </c>
       <c r="B9" s="54">
-        <f>DCF!D25&gt;0</f>
+        <f>DCF!D26&gt;0</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -8449,7 +8513,7 @@
         </is>
       </c>
       <c r="B10" s="54">
-        <f>ABS(Sensitivity!E8-DCF!D25)&lt;0.01</f>
+        <f>ABS(Sensitivity!E8-DCF!D26)&lt;0.01</f>
         <v/>
       </c>
       <c r="J10" s="11" t="inlineStr">
@@ -8672,11 +8736,11 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>FCFE!D18/DCF!D25</f>
+        <f>FCFE!D20/DCF!D26</f>
         <v/>
       </c>
       <c r="C21" s="14">
-        <f>FCFE!D18</f>
+        <f>FCFE!D20</f>
         <v/>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -8819,11 +8883,11 @@
         </is>
       </c>
       <c r="C5" s="14">
-        <f>DCF!D25</f>
+        <f>DCF!D26</f>
         <v/>
       </c>
       <c r="D5" s="14">
-        <f>DCF!D25</f>
+        <f>DCF!D26</f>
         <v/>
       </c>
       <c r="E5" s="15">
@@ -8984,11 +9048,11 @@
         </is>
       </c>
       <c r="C10" s="14">
-        <f>FCFE!D18</f>
+        <f>FCFE!D20</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>FCFE!D18</f>
+        <f>FCFE!D20</f>
         <v/>
       </c>
       <c r="E10" s="15">

--- a/examples/002463_沪电股份_估值模型.xlsx
+++ b/examples/002463_沪电股份_估值模型.xlsx
@@ -1,48 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Revenue_Segments" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="IS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="BS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CF" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Schedules" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="PPE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="FIN" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Equity_Roll" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="DCF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="FCFE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Relative_Val" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Checks" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue_Segments" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CF" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedules" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity_Roll" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCFE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative_Val" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="SCEN_SWITCH">Assumptions!$C$5</definedName>
-    <definedName name="WACC_USED">Assumptions!$C$86</definedName>
-    <definedName name="WACC_CALC">Assumptions!$C$84</definedName>
-    <definedName name="TERM_G">Assumptions!$C$87</definedName>
-    <definedName name="KE">Assumptions!$C$82</definedName>
-    <definedName name="KD">Assumptions!$C$83</definedName>
-    <definedName name="RF_RATE">Assumptions!$C$75</definedName>
-    <definedName name="ERP">Assumptions!$C$76</definedName>
-    <definedName name="BETA_U">Assumptions!$C$77</definedName>
+    <definedName name="WACC_USED">Assumptions!$C$87</definedName>
+    <definedName name="WACC_CALC">Assumptions!$C$85</definedName>
+    <definedName name="TERM_G">Assumptions!$C$88</definedName>
+    <definedName name="KE">Assumptions!$C$83</definedName>
+    <definedName name="KD">Assumptions!$C$84</definedName>
+    <definedName name="RF_RATE">Assumptions!$C$76</definedName>
+    <definedName name="ERP">Assumptions!$C$77</definedName>
+    <definedName name="BETA_U">Assumptions!$C$78</definedName>
     <definedName name="TAX_RATE_Y1">Assumptions!$C$37</definedName>
-    <definedName name="PAYOUT_Y1">Assumptions!$C$57</definedName>
-    <definedName name="MIN_CASH_PCT">Assumptions!$C$61</definedName>
+    <definedName name="PAYOUT_Y1">Assumptions!$C$58</definedName>
+    <definedName name="MIN_CASH_PCT">Assumptions!$C$62</definedName>
     <definedName name="SHARES_DIL">Equity_Roll!$C$21</definedName>
     <definedName name="DCF_PS">DCF!$D$26</definedName>
     <definedName name="FCFE_PS">FCFE!$D$20</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="1000" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -269,8 +269,8 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="C20" s="4">
-        <f>TEXT(Assumptions!C84,"0.00%")&amp;" / "&amp;TEXT(Assumptions!C86,"0.00%")</f>
+        <f>TEXT(Assumptions!C85,"0.00%")&amp;" / "&amp;TEXT(Assumptions!C87,"0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1363,23 +1363,23 @@
         </is>
       </c>
       <c r="E13" s="26">
-        <f>IS!E4*Assumptions!$C$61</f>
+        <f>IS!E4*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="F13" s="26">
-        <f>IS!F4*Assumptions!$C$61</f>
+        <f>IS!F4*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="G13" s="26">
-        <f>IS!G4*Assumptions!$C$61</f>
+        <f>IS!G4*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="H13" s="26">
-        <f>IS!H4*Assumptions!$C$61</f>
+        <f>IS!H4*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="I13" s="26">
-        <f>IS!I4*Assumptions!$C$61</f>
+        <f>IS!I4*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="J13" s="11" t="inlineStr">
@@ -1498,23 +1498,23 @@
         </is>
       </c>
       <c r="E19" s="26">
-        <f>Assumptions!C$62</f>
+        <f>Assumptions!C$63</f>
         <v/>
       </c>
       <c r="F19" s="26">
-        <f>Assumptions!D$62</f>
+        <f>Assumptions!D$63</f>
         <v/>
       </c>
       <c r="G19" s="26">
-        <f>Assumptions!E$62</f>
+        <f>Assumptions!E$63</f>
         <v/>
       </c>
       <c r="H19" s="26">
-        <f>Assumptions!F$62</f>
+        <f>Assumptions!F$63</f>
         <v/>
       </c>
       <c r="I19" s="26">
-        <f>Assumptions!G$62</f>
+        <f>Assumptions!G$63</f>
         <v/>
       </c>
       <c r="J19" s="11" t="inlineStr">
@@ -1726,23 +1726,23 @@
         </is>
       </c>
       <c r="E26" s="26">
-        <f>E25*Assumptions!$C$66</f>
+        <f>E25*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="F26" s="26">
-        <f>F25*Assumptions!$C$66</f>
+        <f>F25*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="G26" s="26">
-        <f>G25*Assumptions!$C$66</f>
+        <f>G25*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="H26" s="26">
-        <f>H25*Assumptions!$C$66</f>
+        <f>H25*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="I26" s="26">
-        <f>I25*Assumptions!$C$66</f>
+        <f>I25*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -1797,23 +1797,23 @@
         </is>
       </c>
       <c r="E30" s="26">
-        <f>Assumptions!C$63</f>
+        <f>Assumptions!C$64</f>
         <v/>
       </c>
       <c r="F30" s="26">
-        <f>Assumptions!D$63</f>
+        <f>Assumptions!D$64</f>
         <v/>
       </c>
       <c r="G30" s="26">
-        <f>Assumptions!E$63</f>
+        <f>Assumptions!E$64</f>
         <v/>
       </c>
       <c r="H30" s="26">
-        <f>Assumptions!F$63</f>
+        <f>Assumptions!F$64</f>
         <v/>
       </c>
       <c r="I30" s="26">
-        <f>Assumptions!G$63</f>
+        <f>Assumptions!G$64</f>
         <v/>
       </c>
       <c r="J30" s="11" t="inlineStr">
@@ -1929,23 +1929,23 @@
         </is>
       </c>
       <c r="E34" s="26">
-        <f>E33*Assumptions!$C$67</f>
+        <f>E33*Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="F34" s="26">
-        <f>F33*Assumptions!$C$67</f>
+        <f>F33*Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="G34" s="26">
-        <f>G33*Assumptions!$C$67</f>
+        <f>G33*Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="H34" s="26">
-        <f>H33*Assumptions!$C$67</f>
+        <f>H33*Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="I34" s="26">
-        <f>I33*Assumptions!$C$67</f>
+        <f>I33*Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="J34" s="11" t="inlineStr">
@@ -2000,23 +2000,23 @@
         </is>
       </c>
       <c r="E38" s="26">
-        <f>Assumptions!C$64</f>
+        <f>Assumptions!C$65</f>
         <v/>
       </c>
       <c r="F38" s="26">
-        <f>Assumptions!D$64</f>
+        <f>Assumptions!D$65</f>
         <v/>
       </c>
       <c r="G38" s="26">
-        <f>Assumptions!E$64</f>
+        <f>Assumptions!E$65</f>
         <v/>
       </c>
       <c r="H38" s="26">
-        <f>Assumptions!F$64</f>
+        <f>Assumptions!F$65</f>
         <v/>
       </c>
       <c r="I38" s="26">
-        <f>Assumptions!G$64</f>
+        <f>Assumptions!G$65</f>
         <v/>
       </c>
       <c r="J38" s="11" t="inlineStr">
@@ -2196,23 +2196,23 @@
         </is>
       </c>
       <c r="E44" s="26">
-        <f>E43*Assumptions!$C$68</f>
+        <f>E43*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="F44" s="26">
-        <f>F43*Assumptions!$C$68</f>
+        <f>F43*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="G44" s="26">
-        <f>G43*Assumptions!$C$68</f>
+        <f>G43*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="H44" s="26">
-        <f>H43*Assumptions!$C$68</f>
+        <f>H43*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="I44" s="26">
-        <f>I43*Assumptions!$C$68</f>
+        <f>I43*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="J44" s="11" t="inlineStr">
@@ -2267,23 +2267,23 @@
         </is>
       </c>
       <c r="E48" s="26">
-        <f>Assumptions!C$65</f>
+        <f>Assumptions!C$66</f>
         <v/>
       </c>
       <c r="F48" s="26">
-        <f>Assumptions!D$65</f>
+        <f>Assumptions!D$66</f>
         <v/>
       </c>
       <c r="G48" s="26">
-        <f>Assumptions!E$65</f>
+        <f>Assumptions!E$66</f>
         <v/>
       </c>
       <c r="H48" s="26">
-        <f>Assumptions!F$65</f>
+        <f>Assumptions!F$66</f>
         <v/>
       </c>
       <c r="I48" s="26">
-        <f>Assumptions!G$65</f>
+        <f>Assumptions!G$66</f>
         <v/>
       </c>
       <c r="J48" s="11" t="inlineStr">
@@ -2399,23 +2399,23 @@
         </is>
       </c>
       <c r="E52" s="26">
-        <f>E51*Assumptions!$C$69</f>
+        <f>E51*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="F52" s="26">
-        <f>F51*Assumptions!$C$69</f>
+        <f>F51*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="G52" s="26">
-        <f>G51*Assumptions!$C$69</f>
+        <f>G51*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="H52" s="26">
-        <f>H51*Assumptions!$C$69</f>
+        <f>H51*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="I52" s="26">
-        <f>I51*Assumptions!$C$69</f>
+        <f>I51*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="J52" s="11" t="inlineStr">
@@ -2806,23 +2806,23 @@
         </is>
       </c>
       <c r="E66" s="26">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="F66" s="26">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="G66" s="26">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="H66" s="26">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="I66" s="26">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="J66" s="11" t="inlineStr">
@@ -2891,23 +2891,23 @@
         </is>
       </c>
       <c r="E72" s="26">
-        <f>E18*Assumptions!$C$66+E29*Assumptions!$C$67+E37*Assumptions!$C$68+E47*Assumptions!$C$69</f>
+        <f>E18*Assumptions!$C$67+E29*Assumptions!$C$68+E37*Assumptions!$C$69+E47*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="F72" s="26">
-        <f>F18*Assumptions!$C$66+F29*Assumptions!$C$67+F37*Assumptions!$C$68+F47*Assumptions!$C$69</f>
+        <f>F18*Assumptions!$C$67+F29*Assumptions!$C$68+F37*Assumptions!$C$69+F47*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="G72" s="26">
-        <f>G18*Assumptions!$C$66+G29*Assumptions!$C$67+G37*Assumptions!$C$68+G47*Assumptions!$C$69</f>
+        <f>G18*Assumptions!$C$67+G29*Assumptions!$C$68+G37*Assumptions!$C$69+G47*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="H72" s="26">
-        <f>H18*Assumptions!$C$66+H29*Assumptions!$C$67+H37*Assumptions!$C$68+H47*Assumptions!$C$69</f>
+        <f>H18*Assumptions!$C$67+H29*Assumptions!$C$68+H37*Assumptions!$C$69+H47*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="I72" s="26">
-        <f>I18*Assumptions!$C$66+I29*Assumptions!$C$67+I37*Assumptions!$C$68+I47*Assumptions!$C$69</f>
+        <f>I18*Assumptions!$C$67+I29*Assumptions!$C$68+I37*Assumptions!$C$69+I47*Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
@@ -2918,23 +2918,23 @@
         </is>
       </c>
       <c r="E73" s="26">
-        <f>E6*Assumptions!$C$70</f>
+        <f>E6*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="F73" s="26">
-        <f>F6*Assumptions!$C$70</f>
+        <f>F6*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="G73" s="26">
-        <f>G6*Assumptions!$C$70</f>
+        <f>G6*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="H73" s="26">
-        <f>H6*Assumptions!$C$70</f>
+        <f>H6*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="I73" s="26">
-        <f>I6*Assumptions!$C$70</f>
+        <f>I6*Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -2972,23 +2972,23 @@
         </is>
       </c>
       <c r="E75" s="26">
-        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E74)*(1-Assumptions!C$37)</f>
+        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E74)*(1-Assumptions!C$37)*(1-Assumptions!C$38)</f>
         <v/>
       </c>
       <c r="F75" s="26">
-        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F74)*(1-Assumptions!D$37)</f>
+        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F74)*(1-Assumptions!D$37)*(1-Assumptions!D$38)</f>
         <v/>
       </c>
       <c r="G75" s="26">
-        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G74)*(1-Assumptions!E$37)</f>
+        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G74)*(1-Assumptions!E$37)*(1-Assumptions!E$38)</f>
         <v/>
       </c>
       <c r="H75" s="26">
-        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H74)*(1-Assumptions!F$37)</f>
+        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H74)*(1-Assumptions!F$37)*(1-Assumptions!F$38)</f>
         <v/>
       </c>
       <c r="I75" s="26">
-        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I74)*(1-Assumptions!G$37)</f>
+        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I74)*(1-Assumptions!G$37)*(1-Assumptions!G$38)</f>
         <v/>
       </c>
     </row>
@@ -3161,23 +3161,23 @@
         </is>
       </c>
       <c r="E82" s="26">
-        <f>(E18+E80)/2*Assumptions!$C$66+(E29+E32)/2*Assumptions!$C$67+(E37+E81)/2*Assumptions!$C$68+(E47+E50)/2*Assumptions!$C$69</f>
+        <f>(E18+E80)/2*Assumptions!$C$67+(E29+E32)/2*Assumptions!$C$68+(E37+E81)/2*Assumptions!$C$69+(E47+E50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="F82" s="26">
-        <f>(F18+F80)/2*Assumptions!$C$66+(F29+F32)/2*Assumptions!$C$67+(F37+F81)/2*Assumptions!$C$68+(F47+F50)/2*Assumptions!$C$69</f>
+        <f>(F18+F80)/2*Assumptions!$C$67+(F29+F32)/2*Assumptions!$C$68+(F37+F81)/2*Assumptions!$C$69+(F47+F50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="G82" s="26">
-        <f>(G18+G80)/2*Assumptions!$C$66+(G29+G32)/2*Assumptions!$C$67+(G37+G81)/2*Assumptions!$C$68+(G47+G50)/2*Assumptions!$C$69</f>
+        <f>(G18+G80)/2*Assumptions!$C$67+(G29+G32)/2*Assumptions!$C$68+(G37+G81)/2*Assumptions!$C$69+(G47+G50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="H82" s="26">
-        <f>(H18+H80)/2*Assumptions!$C$66+(H29+H32)/2*Assumptions!$C$67+(H37+H81)/2*Assumptions!$C$68+(H47+H50)/2*Assumptions!$C$69</f>
+        <f>(H18+H80)/2*Assumptions!$C$67+(H29+H32)/2*Assumptions!$C$68+(H37+H81)/2*Assumptions!$C$69+(H47+H50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="I82" s="26">
-        <f>(I18+I80)/2*Assumptions!$C$66+(I29+I32)/2*Assumptions!$C$67+(I37+I81)/2*Assumptions!$C$68+(I47+I50)/2*Assumptions!$C$69</f>
+        <f>(I18+I80)/2*Assumptions!$C$67+(I29+I32)/2*Assumptions!$C$68+(I37+I81)/2*Assumptions!$C$69+(I47+I50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
@@ -3215,23 +3215,23 @@
         </is>
       </c>
       <c r="E84" s="26">
-        <f>(E6+E83)/2*Assumptions!$C$70</f>
+        <f>(E6+E83)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="F84" s="26">
-        <f>(F6+F83)/2*Assumptions!$C$70</f>
+        <f>(F6+F83)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="G84" s="26">
-        <f>(G6+G83)/2*Assumptions!$C$70</f>
+        <f>(G6+G83)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="H84" s="26">
-        <f>(H6+H83)/2*Assumptions!$C$70</f>
+        <f>(H6+H83)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="I84" s="26">
-        <f>(I6+I83)/2*Assumptions!$C$70</f>
+        <f>(I6+I83)/2*Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -3384,23 +3384,23 @@
         </is>
       </c>
       <c r="E91" s="26">
-        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E90)*(1-Assumptions!C$37)</f>
+        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E90)*(1-Assumptions!C$37)*(1-Assumptions!C$38)</f>
         <v/>
       </c>
       <c r="F91" s="26">
-        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F90)*(1-Assumptions!D$37)</f>
+        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F90)*(1-Assumptions!D$37)*(1-Assumptions!D$38)</f>
         <v/>
       </c>
       <c r="G91" s="26">
-        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G90)*(1-Assumptions!E$37)</f>
+        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G90)*(1-Assumptions!E$37)*(1-Assumptions!E$38)</f>
         <v/>
       </c>
       <c r="H91" s="26">
-        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H90)*(1-Assumptions!F$37)</f>
+        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H90)*(1-Assumptions!F$37)*(1-Assumptions!F$38)</f>
         <v/>
       </c>
       <c r="I91" s="26">
-        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I90)*(1-Assumptions!G$37)</f>
+        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I90)*(1-Assumptions!G$37)*(1-Assumptions!G$38)</f>
         <v/>
       </c>
     </row>
@@ -3573,23 +3573,23 @@
         </is>
       </c>
       <c r="E98" s="26">
-        <f>(E18+E96)/2*Assumptions!$C$66+(E29+E32)/2*Assumptions!$C$67+(E37+E97)/2*Assumptions!$C$68+(E47+E50)/2*Assumptions!$C$69</f>
+        <f>(E18+E96)/2*Assumptions!$C$67+(E29+E32)/2*Assumptions!$C$68+(E37+E97)/2*Assumptions!$C$69+(E47+E50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="F98" s="26">
-        <f>(F18+F96)/2*Assumptions!$C$66+(F29+F32)/2*Assumptions!$C$67+(F37+F97)/2*Assumptions!$C$68+(F47+F50)/2*Assumptions!$C$69</f>
+        <f>(F18+F96)/2*Assumptions!$C$67+(F29+F32)/2*Assumptions!$C$68+(F37+F97)/2*Assumptions!$C$69+(F47+F50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="G98" s="26">
-        <f>(G18+G96)/2*Assumptions!$C$66+(G29+G32)/2*Assumptions!$C$67+(G37+G97)/2*Assumptions!$C$68+(G47+G50)/2*Assumptions!$C$69</f>
+        <f>(G18+G96)/2*Assumptions!$C$67+(G29+G32)/2*Assumptions!$C$68+(G37+G97)/2*Assumptions!$C$69+(G47+G50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="H98" s="26">
-        <f>(H18+H96)/2*Assumptions!$C$66+(H29+H32)/2*Assumptions!$C$67+(H37+H97)/2*Assumptions!$C$68+(H47+H50)/2*Assumptions!$C$69</f>
+        <f>(H18+H96)/2*Assumptions!$C$67+(H29+H32)/2*Assumptions!$C$68+(H37+H97)/2*Assumptions!$C$69+(H47+H50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="I98" s="26">
-        <f>(I18+I96)/2*Assumptions!$C$66+(I29+I32)/2*Assumptions!$C$67+(I37+I97)/2*Assumptions!$C$68+(I47+I50)/2*Assumptions!$C$69</f>
+        <f>(I18+I96)/2*Assumptions!$C$67+(I29+I32)/2*Assumptions!$C$68+(I37+I97)/2*Assumptions!$C$69+(I47+I50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
@@ -3627,23 +3627,23 @@
         </is>
       </c>
       <c r="E100" s="26">
-        <f>(E6+E99)/2*Assumptions!$C$70</f>
+        <f>(E6+E99)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="F100" s="26">
-        <f>(F6+F99)/2*Assumptions!$C$70</f>
+        <f>(F6+F99)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="G100" s="26">
-        <f>(G6+G99)/2*Assumptions!$C$70</f>
+        <f>(G6+G99)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="H100" s="26">
-        <f>(H6+H99)/2*Assumptions!$C$70</f>
+        <f>(H6+H99)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="I100" s="26">
-        <f>(I6+I99)/2*Assumptions!$C$70</f>
+        <f>(I6+I99)/2*Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -3796,23 +3796,23 @@
         </is>
       </c>
       <c r="E107" s="26">
-        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E106)*(1-Assumptions!C$37)</f>
+        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E106)*(1-Assumptions!C$37)*(1-Assumptions!C$38)</f>
         <v/>
       </c>
       <c r="F107" s="26">
-        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F106)*(1-Assumptions!D$37)</f>
+        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F106)*(1-Assumptions!D$37)*(1-Assumptions!D$38)</f>
         <v/>
       </c>
       <c r="G107" s="26">
-        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G106)*(1-Assumptions!E$37)</f>
+        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G106)*(1-Assumptions!E$37)*(1-Assumptions!E$38)</f>
         <v/>
       </c>
       <c r="H107" s="26">
-        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H106)*(1-Assumptions!F$37)</f>
+        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H106)*(1-Assumptions!F$37)*(1-Assumptions!F$38)</f>
         <v/>
       </c>
       <c r="I107" s="26">
-        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I106)*(1-Assumptions!G$37)</f>
+        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I106)*(1-Assumptions!G$37)*(1-Assumptions!G$38)</f>
         <v/>
       </c>
     </row>
@@ -3985,23 +3985,23 @@
         </is>
       </c>
       <c r="E114" s="26">
-        <f>(E18+E112)/2*Assumptions!$C$66+(E29+E32)/2*Assumptions!$C$67+(E37+E113)/2*Assumptions!$C$68+(E47+E50)/2*Assumptions!$C$69</f>
+        <f>(E18+E112)/2*Assumptions!$C$67+(E29+E32)/2*Assumptions!$C$68+(E37+E113)/2*Assumptions!$C$69+(E47+E50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="F114" s="26">
-        <f>(F18+F112)/2*Assumptions!$C$66+(F29+F32)/2*Assumptions!$C$67+(F37+F113)/2*Assumptions!$C$68+(F47+F50)/2*Assumptions!$C$69</f>
+        <f>(F18+F112)/2*Assumptions!$C$67+(F29+F32)/2*Assumptions!$C$68+(F37+F113)/2*Assumptions!$C$69+(F47+F50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="G114" s="26">
-        <f>(G18+G112)/2*Assumptions!$C$66+(G29+G32)/2*Assumptions!$C$67+(G37+G113)/2*Assumptions!$C$68+(G47+G50)/2*Assumptions!$C$69</f>
+        <f>(G18+G112)/2*Assumptions!$C$67+(G29+G32)/2*Assumptions!$C$68+(G37+G113)/2*Assumptions!$C$69+(G47+G50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="H114" s="26">
-        <f>(H18+H112)/2*Assumptions!$C$66+(H29+H32)/2*Assumptions!$C$67+(H37+H113)/2*Assumptions!$C$68+(H47+H50)/2*Assumptions!$C$69</f>
+        <f>(H18+H112)/2*Assumptions!$C$67+(H29+H32)/2*Assumptions!$C$68+(H37+H113)/2*Assumptions!$C$69+(H47+H50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="I114" s="26">
-        <f>(I18+I112)/2*Assumptions!$C$66+(I29+I32)/2*Assumptions!$C$67+(I37+I113)/2*Assumptions!$C$68+(I47+I50)/2*Assumptions!$C$69</f>
+        <f>(I18+I112)/2*Assumptions!$C$67+(I29+I32)/2*Assumptions!$C$68+(I37+I113)/2*Assumptions!$C$69+(I47+I50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
@@ -4039,23 +4039,23 @@
         </is>
       </c>
       <c r="E116" s="26">
-        <f>(E6+E115)/2*Assumptions!$C$70</f>
+        <f>(E6+E115)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="F116" s="26">
-        <f>(F6+F115)/2*Assumptions!$C$70</f>
+        <f>(F6+F115)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="G116" s="26">
-        <f>(G6+G115)/2*Assumptions!$C$70</f>
+        <f>(G6+G115)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="H116" s="26">
-        <f>(H6+H115)/2*Assumptions!$C$70</f>
+        <f>(H6+H115)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="I116" s="26">
-        <f>(I6+I115)/2*Assumptions!$C$70</f>
+        <f>(I6+I115)/2*Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -4208,23 +4208,23 @@
         </is>
       </c>
       <c r="E123" s="26">
-        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E122)*(1-Assumptions!C$37)</f>
+        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E122)*(1-Assumptions!C$37)*(1-Assumptions!C$38)</f>
         <v/>
       </c>
       <c r="F123" s="26">
-        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F122)*(1-Assumptions!D$37)</f>
+        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F122)*(1-Assumptions!D$37)*(1-Assumptions!D$38)</f>
         <v/>
       </c>
       <c r="G123" s="26">
-        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G122)*(1-Assumptions!E$37)</f>
+        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G122)*(1-Assumptions!E$37)*(1-Assumptions!E$38)</f>
         <v/>
       </c>
       <c r="H123" s="26">
-        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H122)*(1-Assumptions!F$37)</f>
+        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H122)*(1-Assumptions!F$37)*(1-Assumptions!F$38)</f>
         <v/>
       </c>
       <c r="I123" s="26">
-        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I122)*(1-Assumptions!G$37)</f>
+        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I122)*(1-Assumptions!G$37)*(1-Assumptions!G$38)</f>
         <v/>
       </c>
     </row>
@@ -4397,23 +4397,23 @@
         </is>
       </c>
       <c r="E130" s="26">
-        <f>(E18+E128)/2*Assumptions!$C$66+(E29+E32)/2*Assumptions!$C$67+(E37+E129)/2*Assumptions!$C$68+(E47+E50)/2*Assumptions!$C$69</f>
+        <f>(E18+E128)/2*Assumptions!$C$67+(E29+E32)/2*Assumptions!$C$68+(E37+E129)/2*Assumptions!$C$69+(E47+E50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="F130" s="26">
-        <f>(F18+F128)/2*Assumptions!$C$66+(F29+F32)/2*Assumptions!$C$67+(F37+F129)/2*Assumptions!$C$68+(F47+F50)/2*Assumptions!$C$69</f>
+        <f>(F18+F128)/2*Assumptions!$C$67+(F29+F32)/2*Assumptions!$C$68+(F37+F129)/2*Assumptions!$C$69+(F47+F50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="G130" s="26">
-        <f>(G18+G128)/2*Assumptions!$C$66+(G29+G32)/2*Assumptions!$C$67+(G37+G129)/2*Assumptions!$C$68+(G47+G50)/2*Assumptions!$C$69</f>
+        <f>(G18+G128)/2*Assumptions!$C$67+(G29+G32)/2*Assumptions!$C$68+(G37+G129)/2*Assumptions!$C$69+(G47+G50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="H130" s="26">
-        <f>(H18+H128)/2*Assumptions!$C$66+(H29+H32)/2*Assumptions!$C$67+(H37+H129)/2*Assumptions!$C$68+(H47+H50)/2*Assumptions!$C$69</f>
+        <f>(H18+H128)/2*Assumptions!$C$67+(H29+H32)/2*Assumptions!$C$68+(H37+H129)/2*Assumptions!$C$69+(H47+H50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="I130" s="26">
-        <f>(I18+I128)/2*Assumptions!$C$66+(I29+I32)/2*Assumptions!$C$67+(I37+I129)/2*Assumptions!$C$68+(I47+I50)/2*Assumptions!$C$69</f>
+        <f>(I18+I128)/2*Assumptions!$C$67+(I29+I32)/2*Assumptions!$C$68+(I37+I129)/2*Assumptions!$C$69+(I47+I50)/2*Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
@@ -4451,23 +4451,23 @@
         </is>
       </c>
       <c r="E132" s="26">
-        <f>(E6+E131)/2*Assumptions!$C$70</f>
+        <f>(E6+E131)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="F132" s="26">
-        <f>(F6+F131)/2*Assumptions!$C$70</f>
+        <f>(F6+F131)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="G132" s="26">
-        <f>(G6+G131)/2*Assumptions!$C$70</f>
+        <f>(G6+G131)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="H132" s="26">
-        <f>(H6+H131)/2*Assumptions!$C$70</f>
+        <f>(H6+H131)/2*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="I132" s="26">
-        <f>(I6+I131)/2*Assumptions!$C$70</f>
+        <f>(I6+I131)/2*Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -4571,23 +4571,23 @@
         </is>
       </c>
       <c r="E138" s="39">
-        <f>ABS(E65-(E6+E63)/2*Assumptions!$C$70)</f>
+        <f>ABS(E65-(E6+E63)/2*Assumptions!$C$71)</f>
         <v/>
       </c>
       <c r="F138" s="39">
-        <f>ABS(F65-(F6+F63)/2*Assumptions!$C$70)</f>
+        <f>ABS(F65-(F6+F63)/2*Assumptions!$C$71)</f>
         <v/>
       </c>
       <c r="G138" s="39">
-        <f>ABS(G65-(G6+G63)/2*Assumptions!$C$70)</f>
+        <f>ABS(G65-(G6+G63)/2*Assumptions!$C$71)</f>
         <v/>
       </c>
       <c r="H138" s="39">
-        <f>ABS(H65-(H6+H63)/2*Assumptions!$C$70)</f>
+        <f>ABS(H65-(H6+H63)/2*Assumptions!$C$71)</f>
         <v/>
       </c>
       <c r="I138" s="39">
-        <f>ABS(I65-(I6+I63)/2*Assumptions!$C$70)</f>
+        <f>ABS(I65-(I6+I63)/2*Assumptions!$C$71)</f>
         <v/>
       </c>
       <c r="J138" s="11" t="inlineStr">
@@ -4936,23 +4936,23 @@
         </is>
       </c>
       <c r="E9" s="26">
-        <f>IS!E20*Assumptions!$C$58</f>
+        <f>IS!E20*Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>IS!F20*Assumptions!$C$58</f>
+        <f>IS!F20*Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="G9" s="26">
-        <f>IS!G20*Assumptions!$C$58</f>
+        <f>IS!G20*Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>IS!H20*Assumptions!$C$58</f>
+        <f>IS!H20*Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="I9" s="26">
-        <f>IS!I20*Assumptions!$C$58</f>
+        <f>IS!I20*Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -5277,7 +5277,7 @@
           <t>稀释后股数(百万股)</t>
         </is>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="37">
         <f>C19+C20</f>
         <v/>
       </c>
@@ -5376,23 +5376,23 @@
         </is>
       </c>
       <c r="E4" s="26">
-        <f>IS!E23</f>
+        <f>IS!E24</f>
         <v/>
       </c>
       <c r="F4" s="26">
-        <f>IS!F23</f>
+        <f>IS!F24</f>
         <v/>
       </c>
       <c r="G4" s="26">
-        <f>IS!G23</f>
+        <f>IS!G24</f>
         <v/>
       </c>
       <c r="H4" s="26">
-        <f>IS!H23</f>
+        <f>IS!H24</f>
         <v/>
       </c>
       <c r="I4" s="26">
-        <f>IS!I23</f>
+        <f>IS!I24</f>
         <v/>
       </c>
       <c r="J4" s="11" t="inlineStr">
@@ -5607,23 +5607,23 @@
         </is>
       </c>
       <c r="E12" s="31">
-        <f>1/(1+Assumptions!$C$86)^E11</f>
+        <f>1/(1+Assumptions!$C$87)^E11</f>
         <v/>
       </c>
       <c r="F12" s="31">
-        <f>1/(1+Assumptions!$C$86)^F11</f>
+        <f>1/(1+Assumptions!$C$87)^F11</f>
         <v/>
       </c>
       <c r="G12" s="31">
-        <f>1/(1+Assumptions!$C$86)^G11</f>
+        <f>1/(1+Assumptions!$C$87)^G11</f>
         <v/>
       </c>
       <c r="H12" s="31">
-        <f>1/(1+Assumptions!$C$86)^H11</f>
+        <f>1/(1+Assumptions!$C$87)^H11</f>
         <v/>
       </c>
       <c r="I12" s="31">
-        <f>1/(1+Assumptions!$C$86)^I11</f>
+        <f>1/(1+Assumptions!$C$87)^I11</f>
         <v/>
       </c>
       <c r="J12" s="11" t="inlineStr"/>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="D16" s="26">
-        <f>I10*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)</f>
+        <f>I10*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)</f>
         <v/>
       </c>
       <c r="J16" s="11" t="inlineStr">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="D30" s="43">
-        <f>D18/(IS!E23+PPE!E19)</f>
+        <f>D18/(IS!E24+PPE!E19)</f>
         <v/>
       </c>
       <c r="J30" s="11" t="inlineStr"/>
@@ -5924,7 +5924,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>单位: 人民币百万元 | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得归母股权价值(少数股东权益见DCF页EV→Equity桥); 终值取正常化FCFE(净新增借款按g封顶)</t>
+          <t>单位: 人民币百万元 | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得归母股权价值(少数股东权益见DCF页EV→Equity桥); 终值取正常化FCFE(净新增借款按D×g稳态正常化)</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
         </is>
       </c>
       <c r="D16" s="26">
-        <f>I10-I8+MIN(I8,FIN!I56*TERM_G)</f>
+        <f>I10-I8+FIN!I56*TERM_G</f>
         <v/>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>净新增借款按g封顶: 终值内净新增借款取MIN(实际调度, 2030E期末有息负债×g), 防止显性期末大额净融资被Gordon公式永续外推; 去杠杆/平稳年(实际≤封顶值)维持实际调度不变</t>
+          <t>终值净借款按D×g稳态正常化: 终值年净新增借款=2030E期末有息负债×g(替代实际调度值, 对称防止显性期末大额净融资/净偿还被Gordon公式永续外推)</t>
         </is>
       </c>
     </row>
@@ -7002,29 +7002,29 @@
         </is>
       </c>
       <c r="C5" s="42">
-        <f>Assumptions!$C$87-0.0100</f>
+        <f>Assumptions!$C$88-0.0100</f>
         <v/>
       </c>
       <c r="D5" s="42">
-        <f>Assumptions!$C$87-0.0050</f>
+        <f>Assumptions!$C$88-0.0050</f>
         <v/>
       </c>
       <c r="E5" s="42">
-        <f>Assumptions!$C$87</f>
+        <f>Assumptions!$C$88</f>
         <v/>
       </c>
       <c r="F5" s="42">
-        <f>Assumptions!$C$87+0.0050</f>
+        <f>Assumptions!$C$88+0.0050</f>
         <v/>
       </c>
       <c r="G5" s="42">
-        <f>Assumptions!$C$87+0.0100</f>
+        <f>Assumptions!$C$88+0.0100</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="42">
-        <f>Assumptions!$C$86-0.0100</f>
+        <f>Assumptions!$C$87-0.0100</f>
         <v/>
       </c>
       <c r="C6" s="14">
@@ -7050,7 +7050,7 @@
     </row>
     <row r="7">
       <c r="B7" s="42">
-        <f>Assumptions!$C$86-0.0050</f>
+        <f>Assumptions!$C$87-0.0050</f>
         <v/>
       </c>
       <c r="C7" s="14">
@@ -7076,7 +7076,7 @@
     </row>
     <row r="8">
       <c r="B8" s="42">
-        <f>Assumptions!$C$86</f>
+        <f>Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="C8" s="14">
@@ -7102,7 +7102,7 @@
     </row>
     <row r="9">
       <c r="B9" s="42">
-        <f>Assumptions!$C$86+0.0050</f>
+        <f>Assumptions!$C$87+0.0050</f>
         <v/>
       </c>
       <c r="C9" s="14">
@@ -7128,7 +7128,7 @@
     </row>
     <row r="10">
       <c r="B10" s="42">
-        <f>Assumptions!$C$86+0.0100</f>
+        <f>Assumptions!$C$87+0.0100</f>
         <v/>
       </c>
       <c r="C10" s="14">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>机制: DPO变动δ→应付变动→ΔNWC变动→FCFF一阶调整; 未反映利息二阶效应(金额小); δ=0格=DCF基准</t>
+          <t>机制: DPO变动δ→应付变动→ΔNWC变动→FCFF一阶调整; 首年按全额COGS重定价, 以后年按ΔCOGS; 未反映利息二阶效应(金额小); δ=0格=DCF基准</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
         <v>-40</v>
       </c>
       <c r="C24" s="14">
-        <f>((DCF!E$10+$B24/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B24/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B24/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B24/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B24/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B24/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B24/365*(IS!E$6))/(1+Assumptions!$C$87)^0.5+(DCF!F$10+$B24/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$87)^1.5+(DCF!G$10+$B24/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$87)^2.5+(DCF!H$10+$B24/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$87)^3.5+(DCF!I$10+$B24/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$87)^4.5+(DCF!$I$10+$B24/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)/(1+Assumptions!$C$87)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D24" s="16">
@@ -7390,7 +7390,7 @@
         <v>-20</v>
       </c>
       <c r="C25" s="14">
-        <f>((DCF!E$10+$B25/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B25/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B25/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B25/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B25/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B25/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B25/365*(IS!E$6))/(1+Assumptions!$C$87)^0.5+(DCF!F$10+$B25/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$87)^1.5+(DCF!G$10+$B25/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$87)^2.5+(DCF!H$10+$B25/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$87)^3.5+(DCF!I$10+$B25/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$87)^4.5+(DCF!$I$10+$B25/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)/(1+Assumptions!$C$87)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D25" s="16">
@@ -7403,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="49">
-        <f>((DCF!E$10+$B26/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B26/365*(IS!E$6))/(1+Assumptions!$C$87)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$87)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$87)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$87)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$87)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)/(1+Assumptions!$C$87)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D26" s="16">
@@ -7416,7 +7416,7 @@
         <v>20</v>
       </c>
       <c r="C27" s="14">
-        <f>((DCF!E$10+$B27/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B27/365*(IS!E$6))/(1+Assumptions!$C$87)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$87)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$87)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$87)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$87)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)/(1+Assumptions!$C$87)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D27" s="16">
@@ -7429,7 +7429,7 @@
         <v>40</v>
       </c>
       <c r="C28" s="14">
-        <f>((DCF!E$10+$B28/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$86)^0.5+(DCF!F$10+$B28/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$86)^1.5+(DCF!G$10+$B28/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$86)^2.5+(DCF!H$10+$B28/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$86)^3.5+(DCF!I$10+$B28/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$86)^4.5+(DCF!$I$10+$B28/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B28/365*(IS!E$6))/(1+Assumptions!$C$87)^0.5+(DCF!F$10+$B28/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$87)^1.5+(DCF!G$10+$B28/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$87)^2.5+(DCF!H$10+$B28/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$87)^3.5+(DCF!I$10+$B28/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$87)^4.5+(DCF!$I$10+$B28/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)/(1+Assumptions!$C$87)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D28" s="16">
@@ -7440,7 +7440,7 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>DPO每±20天≈FCFF±(Δ营业成本×20/365); 基准DPO路径见Assumptions(198→198天)</t>
+          <t>DPO每±20天: 首年≈FCFF±(营业成本×20/365), 以后年≈±(Δ营业成本×20/365); 基准DPO路径见Assumptions(198→198天)</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>熊市 Bear — 收入增速调整/净利率调整引用Assumptions第91行</t>
+          <t>熊市 Bear — 收入增速调整/净利率调整引用Assumptions第92行</t>
         </is>
       </c>
     </row>
@@ -7573,23 +7573,23 @@
         </is>
       </c>
       <c r="E8" s="26">
-        <f>IS!D4*(1+Revenue_Segments!E29+Assumptions!$C$91)</f>
+        <f>IS!D4*(1+Revenue_Segments!E29+Assumptions!$C$92)</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>E8*(1+Revenue_Segments!F29+Assumptions!$C$91)</f>
+        <f>E8*(1+Revenue_Segments!F29+Assumptions!$C$92)</f>
         <v/>
       </c>
       <c r="G8" s="26">
-        <f>F8*(1+Revenue_Segments!G29+Assumptions!$C$91)</f>
+        <f>F8*(1+Revenue_Segments!G29+Assumptions!$C$92)</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>G8*(1+Revenue_Segments!H29+Assumptions!$C$91)</f>
+        <f>G8*(1+Revenue_Segments!H29+Assumptions!$C$92)</f>
         <v/>
       </c>
       <c r="I8" s="26">
-        <f>H8*(1+Revenue_Segments!I29+Assumptions!$C$91)</f>
+        <f>H8*(1+Revenue_Segments!I29+Assumptions!$C$92)</f>
         <v/>
       </c>
     </row>
@@ -7600,23 +7600,23 @@
         </is>
       </c>
       <c r="E9" s="16">
-        <f>(Revenue_Segments!E30+Assumptions!$D$91-Assumptions!C$31-Assumptions!C$32-Assumptions!C$33-Assumptions!C$34-Assumptions!$C$38)*(1-Assumptions!C$37)</f>
+        <f>(Revenue_Segments!E30+Assumptions!$D$92-Assumptions!C$31-Assumptions!C$32-Assumptions!C$33-Assumptions!C$34-Assumptions!$C$39)*(1-Assumptions!C$37)*(1-Assumptions!C$38)</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(Revenue_Segments!F30+Assumptions!$D$91-Assumptions!D$31-Assumptions!D$32-Assumptions!D$33-Assumptions!D$34-Assumptions!$C$38)*(1-Assumptions!D$37)</f>
+        <f>(Revenue_Segments!F30+Assumptions!$D$92-Assumptions!D$31-Assumptions!D$32-Assumptions!D$33-Assumptions!D$34-Assumptions!$C$39)*(1-Assumptions!D$37)*(1-Assumptions!D$38)</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>(Revenue_Segments!G30+Assumptions!$D$91-Assumptions!E$31-Assumptions!E$32-Assumptions!E$33-Assumptions!E$34-Assumptions!$C$38)*(1-Assumptions!E$37)</f>
+        <f>(Revenue_Segments!G30+Assumptions!$D$92-Assumptions!E$31-Assumptions!E$32-Assumptions!E$33-Assumptions!E$34-Assumptions!$C$39)*(1-Assumptions!E$37)*(1-Assumptions!E$38)</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>(Revenue_Segments!H30+Assumptions!$D$91-Assumptions!F$31-Assumptions!F$32-Assumptions!F$33-Assumptions!F$34-Assumptions!$C$38)*(1-Assumptions!F$37)</f>
+        <f>(Revenue_Segments!H30+Assumptions!$D$92-Assumptions!F$31-Assumptions!F$32-Assumptions!F$33-Assumptions!F$34-Assumptions!$C$39)*(1-Assumptions!F$37)*(1-Assumptions!F$38)</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>(Revenue_Segments!I30+Assumptions!$D$91-Assumptions!G$31-Assumptions!G$32-Assumptions!G$33-Assumptions!G$34-Assumptions!$C$38)*(1-Assumptions!G$37)</f>
+        <f>(Revenue_Segments!I30+Assumptions!$D$92-Assumptions!G$31-Assumptions!G$32-Assumptions!G$33-Assumptions!G$34-Assumptions!$C$39)*(1-Assumptions!G$37)*(1-Assumptions!G$38)</f>
         <v/>
       </c>
     </row>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B12" s="17">
-        <f>(E11/(1+Assumptions!$C$86)^0.5+F11/(1+Assumptions!$C$86)^1.5+G11/(1+Assumptions!$C$86)^2.5+H11/(1+Assumptions!$C$86)^3.5+I11/(1+Assumptions!$C$86)^4.5+I11*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>(E11/(1+Assumptions!$C$87)^0.5+F11/(1+Assumptions!$C$87)^1.5+G11/(1+Assumptions!$C$87)^2.5+H11/(1+Assumptions!$C$87)^3.5+I11/(1+Assumptions!$C$87)^4.5+I11*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)/(1+Assumptions!$C$87)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -7709,7 +7709,7 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>基准 Base — 收入增速调整/净利率调整引用Assumptions第92行</t>
+          <t>基准 Base — 收入增速调整/净利率调整引用Assumptions第93行</t>
         </is>
       </c>
     </row>
@@ -7752,23 +7752,23 @@
         </is>
       </c>
       <c r="E17" s="26">
-        <f>IS!D4*(1+Revenue_Segments!E29+Assumptions!$C$92)</f>
+        <f>IS!D4*(1+Revenue_Segments!E29+Assumptions!$C$93)</f>
         <v/>
       </c>
       <c r="F17" s="26">
-        <f>E17*(1+Revenue_Segments!F29+Assumptions!$C$92)</f>
+        <f>E17*(1+Revenue_Segments!F29+Assumptions!$C$93)</f>
         <v/>
       </c>
       <c r="G17" s="26">
-        <f>F17*(1+Revenue_Segments!G29+Assumptions!$C$92)</f>
+        <f>F17*(1+Revenue_Segments!G29+Assumptions!$C$93)</f>
         <v/>
       </c>
       <c r="H17" s="26">
-        <f>G17*(1+Revenue_Segments!H29+Assumptions!$C$92)</f>
+        <f>G17*(1+Revenue_Segments!H29+Assumptions!$C$93)</f>
         <v/>
       </c>
       <c r="I17" s="26">
-        <f>H17*(1+Revenue_Segments!I29+Assumptions!$C$92)</f>
+        <f>H17*(1+Revenue_Segments!I29+Assumptions!$C$93)</f>
         <v/>
       </c>
     </row>
@@ -7779,23 +7779,23 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>(Revenue_Segments!E30+Assumptions!$D$92-Assumptions!C$31-Assumptions!C$32-Assumptions!C$33-Assumptions!C$34-Assumptions!$C$38)*(1-Assumptions!C$37)</f>
+        <f>(Revenue_Segments!E30+Assumptions!$D$93-Assumptions!C$31-Assumptions!C$32-Assumptions!C$33-Assumptions!C$34-Assumptions!$C$39)*(1-Assumptions!C$37)*(1-Assumptions!C$38)</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>(Revenue_Segments!F30+Assumptions!$D$92-Assumptions!D$31-Assumptions!D$32-Assumptions!D$33-Assumptions!D$34-Assumptions!$C$38)*(1-Assumptions!D$37)</f>
+        <f>(Revenue_Segments!F30+Assumptions!$D$93-Assumptions!D$31-Assumptions!D$32-Assumptions!D$33-Assumptions!D$34-Assumptions!$C$39)*(1-Assumptions!D$37)*(1-Assumptions!D$38)</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>(Revenue_Segments!G30+Assumptions!$D$92-Assumptions!E$31-Assumptions!E$32-Assumptions!E$33-Assumptions!E$34-Assumptions!$C$38)*(1-Assumptions!E$37)</f>
+        <f>(Revenue_Segments!G30+Assumptions!$D$93-Assumptions!E$31-Assumptions!E$32-Assumptions!E$33-Assumptions!E$34-Assumptions!$C$39)*(1-Assumptions!E$37)*(1-Assumptions!E$38)</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>(Revenue_Segments!H30+Assumptions!$D$92-Assumptions!F$31-Assumptions!F$32-Assumptions!F$33-Assumptions!F$34-Assumptions!$C$38)*(1-Assumptions!F$37)</f>
+        <f>(Revenue_Segments!H30+Assumptions!$D$93-Assumptions!F$31-Assumptions!F$32-Assumptions!F$33-Assumptions!F$34-Assumptions!$C$39)*(1-Assumptions!F$37)*(1-Assumptions!F$38)</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>(Revenue_Segments!I30+Assumptions!$D$92-Assumptions!G$31-Assumptions!G$32-Assumptions!G$33-Assumptions!G$34-Assumptions!$C$38)*(1-Assumptions!G$37)</f>
+        <f>(Revenue_Segments!I30+Assumptions!$D$93-Assumptions!G$31-Assumptions!G$32-Assumptions!G$33-Assumptions!G$34-Assumptions!$C$39)*(1-Assumptions!G$37)*(1-Assumptions!G$38)</f>
         <v/>
       </c>
     </row>
@@ -7895,7 +7895,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>牛市 Bull — 收入增速调整/净利率调整引用Assumptions第93行</t>
+          <t>牛市 Bull — 收入增速调整/净利率调整引用Assumptions第94行</t>
         </is>
       </c>
     </row>
@@ -7938,23 +7938,23 @@
         </is>
       </c>
       <c r="E27" s="26">
-        <f>IS!D4*(1+Revenue_Segments!E29+Assumptions!$C$93)</f>
+        <f>IS!D4*(1+Revenue_Segments!E29+Assumptions!$C$94)</f>
         <v/>
       </c>
       <c r="F27" s="26">
-        <f>E27*(1+Revenue_Segments!F29+Assumptions!$C$93)</f>
+        <f>E27*(1+Revenue_Segments!F29+Assumptions!$C$94)</f>
         <v/>
       </c>
       <c r="G27" s="26">
-        <f>F27*(1+Revenue_Segments!G29+Assumptions!$C$93)</f>
+        <f>F27*(1+Revenue_Segments!G29+Assumptions!$C$94)</f>
         <v/>
       </c>
       <c r="H27" s="26">
-        <f>G27*(1+Revenue_Segments!H29+Assumptions!$C$93)</f>
+        <f>G27*(1+Revenue_Segments!H29+Assumptions!$C$94)</f>
         <v/>
       </c>
       <c r="I27" s="26">
-        <f>H27*(1+Revenue_Segments!I29+Assumptions!$C$93)</f>
+        <f>H27*(1+Revenue_Segments!I29+Assumptions!$C$94)</f>
         <v/>
       </c>
     </row>
@@ -7965,23 +7965,23 @@
         </is>
       </c>
       <c r="E28" s="16">
-        <f>(Revenue_Segments!E30+Assumptions!$D$93-Assumptions!C$31-Assumptions!C$32-Assumptions!C$33-Assumptions!C$34-Assumptions!$C$38)*(1-Assumptions!C$37)</f>
+        <f>(Revenue_Segments!E30+Assumptions!$D$94-Assumptions!C$31-Assumptions!C$32-Assumptions!C$33-Assumptions!C$34-Assumptions!$C$39)*(1-Assumptions!C$37)*(1-Assumptions!C$38)</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>(Revenue_Segments!F30+Assumptions!$D$93-Assumptions!D$31-Assumptions!D$32-Assumptions!D$33-Assumptions!D$34-Assumptions!$C$38)*(1-Assumptions!D$37)</f>
+        <f>(Revenue_Segments!F30+Assumptions!$D$94-Assumptions!D$31-Assumptions!D$32-Assumptions!D$33-Assumptions!D$34-Assumptions!$C$39)*(1-Assumptions!D$37)*(1-Assumptions!D$38)</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>(Revenue_Segments!G30+Assumptions!$D$93-Assumptions!E$31-Assumptions!E$32-Assumptions!E$33-Assumptions!E$34-Assumptions!$C$38)*(1-Assumptions!E$37)</f>
+        <f>(Revenue_Segments!G30+Assumptions!$D$94-Assumptions!E$31-Assumptions!E$32-Assumptions!E$33-Assumptions!E$34-Assumptions!$C$39)*(1-Assumptions!E$37)*(1-Assumptions!E$38)</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>(Revenue_Segments!H30+Assumptions!$D$93-Assumptions!F$31-Assumptions!F$32-Assumptions!F$33-Assumptions!F$34-Assumptions!$C$38)*(1-Assumptions!F$37)</f>
+        <f>(Revenue_Segments!H30+Assumptions!$D$94-Assumptions!F$31-Assumptions!F$32-Assumptions!F$33-Assumptions!F$34-Assumptions!$C$39)*(1-Assumptions!F$37)*(1-Assumptions!F$38)</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>(Revenue_Segments!I30+Assumptions!$D$93-Assumptions!G$31-Assumptions!G$32-Assumptions!G$33-Assumptions!G$34-Assumptions!$C$38)*(1-Assumptions!G$37)</f>
+        <f>(Revenue_Segments!I30+Assumptions!$D$94-Assumptions!G$31-Assumptions!G$32-Assumptions!G$33-Assumptions!G$34-Assumptions!$C$39)*(1-Assumptions!G$37)*(1-Assumptions!G$38)</f>
         <v/>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="B31" s="17">
-        <f>(E30/(1+Assumptions!$C$86)^0.5+F30/(1+Assumptions!$C$86)^1.5+G30/(1+Assumptions!$C$86)^2.5+H30/(1+Assumptions!$C$86)^3.5+I30/(1+Assumptions!$C$86)^4.5+I30*(1+Assumptions!$C$87)/(Assumptions!$C$86-Assumptions!$C$87)/(1+Assumptions!$C$86)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>(E30/(1+Assumptions!$C$87)^0.5+F30/(1+Assumptions!$C$87)^1.5+G30/(1+Assumptions!$C$87)^2.5+H30/(1+Assumptions!$C$87)^3.5+I30/(1+Assumptions!$C$87)^4.5+I30*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)/(1+Assumptions!$C$87)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -8449,7 +8449,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>5. 毛利率处于(0,60%)合理区间</t>
+          <t>5. 信息项(不闸门): 毛利率处于(0%,60%)区间</t>
         </is>
       </c>
       <c r="B8" s="54">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>防止假设越界</t>
+          <t>信息行, 不参与布尔汇总; 越界仅提示复核毛利率假设; 区间可经checks.gm_band配置</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="B11" s="54">
-        <f>OR(ABS(Assumptions!C86-Assumptions!C84)&lt;0.000001,Assumptions!C85&lt;&gt;"")</f>
+        <f>OR(ABS(Assumptions!C87-Assumptions!C85)&lt;0.000001,Assumptions!C86&lt;&gt;"")</f>
         <v/>
       </c>
       <c r="J11" s="11" t="inlineStr">
@@ -8716,11 +8716,11 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>Assumptions!C84</f>
+        <f>Assumptions!C85</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>Assumptions!C86</f>
+        <f>Assumptions!C87</f>
         <v/>
       </c>
       <c r="J20" s="11" t="inlineStr">
@@ -8776,7 +8776,7 @@
         </is>
       </c>
       <c r="F24" s="57">
-        <f>IF(AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15),"全部通过=TRUE","存在未通过=FALSE")</f>
+        <f>IF(AND(B4:I4,E5:I5,E6:I6,B7:I7,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15),"全部通过=TRUE","存在未通过=FALSE")</f>
         <v/>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="F25" s="27">
-        <f>AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15)</f>
+        <f>AND(B4:I4,E5:I5,E6:I6,B7:I7,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15)</f>
         <v/>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9948,66 +9948,66 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t>少数股东损益占净利润比</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>按历史均值自动推导: (合并净利-归母)/合并净利 3年均值-0.82%, clamp[0,50%]→采用0.00%; config可经model.mi_share覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
           <t>其他及财务费用率合计(情景页用)</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C38" s="28" t="n">
+      <c r="C39" s="28" t="n">
         <v>-0.0036</v>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>自动推导: 最近年报财务费用率, 供Scenarios页简化净利率计算</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>六、营运资本天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>DSO 应收(票据+账款)天数</t>
-        </is>
-      </c>
-      <c r="B41" s="21" t="inlineStr">
-        <is>
-          <t>天</t>
-        </is>
-      </c>
-      <c r="C41" s="30" t="n">
-        <v>106</v>
-      </c>
-      <c r="D41" s="30" t="n">
-        <v>106</v>
-      </c>
-      <c r="E41" s="30" t="n">
-        <v>106</v>
-      </c>
-      <c r="F41" s="30" t="n">
-        <v>106</v>
-      </c>
-      <c r="G41" s="30" t="n">
-        <v>106</v>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>自动推导: 最近年报DSO 106天持平</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>DIO 存货天数</t>
+          <t>DSO 应收(票据+账款)天数</t>
         </is>
       </c>
       <c r="B42" s="21" t="inlineStr">
@@ -10016,30 +10016,30 @@
         </is>
       </c>
       <c r="C42" s="30" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="D42" s="30" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="E42" s="30" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="F42" s="30" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="G42" s="30" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>自动推导: 最近年报DIO 127天持平</t>
+          <t>自动推导: 最近年报DSO 106天持平</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>DPO 应付(票据+账款)天数</t>
+          <t>DIO 存货天数</t>
         </is>
       </c>
       <c r="B43" s="21" t="inlineStr">
@@ -10048,62 +10048,62 @@
         </is>
       </c>
       <c r="C43" s="30" t="n">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="D43" s="30" t="n">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="E43" s="30" t="n">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="F43" s="30" t="n">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="G43" s="30" t="n">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>自动推导: 最近年报DPO 198天持平</t>
+          <t>自动推导: 最近年报DIO 127天持平</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>预付款项/收入</t>
+          <t>DPO 应付(票据+账款)天数</t>
         </is>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C44" s="28" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="D44" s="28" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="E44" s="28" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="F44" s="28" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="G44" s="28" t="n">
-        <v>0.0052</v>
+          <t>天</t>
+        </is>
+      </c>
+      <c r="C44" s="30" t="n">
+        <v>198</v>
+      </c>
+      <c r="D44" s="30" t="n">
+        <v>198</v>
+      </c>
+      <c r="E44" s="30" t="n">
+        <v>198</v>
+      </c>
+      <c r="F44" s="30" t="n">
+        <v>198</v>
+      </c>
+      <c r="G44" s="30" t="n">
+        <v>198</v>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>自动推导: 最近年报预付/收入持平</t>
+          <t>自动推导: 最近年报DPO 198天持平</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>应付职工薪酬/收入</t>
+          <t>预付款项/收入</t>
         </is>
       </c>
       <c r="B45" s="21" t="inlineStr">
@@ -10112,101 +10112,101 @@
         </is>
       </c>
       <c r="C45" s="28" t="n">
-        <v>0.028</v>
+        <v>0.0052</v>
       </c>
       <c r="D45" s="28" t="n">
-        <v>0.028</v>
+        <v>0.0052</v>
       </c>
       <c r="E45" s="28" t="n">
-        <v>0.028</v>
+        <v>0.0052</v>
       </c>
       <c r="F45" s="28" t="n">
-        <v>0.028</v>
+        <v>0.0052</v>
       </c>
       <c r="G45" s="28" t="n">
-        <v>0.028</v>
+        <v>0.0052</v>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>自动推导: 最近年报应付职工薪酬/收入持平</t>
+          <t>自动推导: 最近年报预付/收入持平</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t>应付职工薪酬/收入</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="D46" s="28" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="E46" s="28" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F46" s="28" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G46" s="28" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>自动推导: 最近年报应付职工薪酬/收入持平</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
           <t>应交税费/收入</t>
         </is>
       </c>
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C46" s="28" t="n">
+      <c r="C47" s="28" t="n">
         <v>0.0145</v>
       </c>
-      <c r="D46" s="28" t="n">
+      <c r="D47" s="28" t="n">
         <v>0.0145</v>
       </c>
-      <c r="E46" s="28" t="n">
+      <c r="E47" s="28" t="n">
         <v>0.0145</v>
       </c>
-      <c r="F46" s="28" t="n">
+      <c r="F47" s="28" t="n">
         <v>0.0145</v>
       </c>
-      <c r="G46" s="28" t="n">
+      <c r="G47" s="28" t="n">
         <v>0.0145</v>
       </c>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="H47" s="9" t="inlineStr">
         <is>
           <t>自动推导: 最近年报应交税费/收入持平</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="19" t="inlineStr">
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>七、资本开支与折旧摊销 (PP&amp;E页驱动)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Capex占收入比</t>
-        </is>
-      </c>
-      <c r="B49" s="21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C49" s="28" t="n">
-        <v>0.1688</v>
-      </c>
-      <c r="D49" s="28" t="n">
-        <v>0.1435</v>
-      </c>
-      <c r="E49" s="28" t="n">
-        <v>0.1182</v>
-      </c>
-      <c r="F49" s="28" t="n">
-        <v>0.1013</v>
-      </c>
-      <c r="G49" s="28" t="n">
-        <v>0.0844</v>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>自动推导: 最近年报Capex/收入16.9%(上限35%)逐年退坡×1/.85/.70/.60/.50</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>在建工程转固率</t>
+          <t>Capex占收入比</t>
         </is>
       </c>
       <c r="B50" s="21" t="inlineStr">
@@ -10215,18 +10215,30 @@
         </is>
       </c>
       <c r="C50" s="28" t="n">
-        <v>0.75</v>
+        <v>0.1688</v>
+      </c>
+      <c r="D50" s="28" t="n">
+        <v>0.1435</v>
+      </c>
+      <c r="E50" s="28" t="n">
+        <v>0.1182</v>
+      </c>
+      <c r="F50" s="28" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="G50" s="28" t="n">
+        <v>0.0844</v>
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 当年转固=(期初在建+当年Capex)×75%</t>
+          <t>自动推导: 最近年报Capex/收入16.9%(上限35%)逐年退坡×1/.85/.70/.60/.50</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>固定资产折旧率(期初净值)</t>
+          <t>在建工程转固率</t>
         </is>
       </c>
       <c r="B51" s="21" t="inlineStr">
@@ -10235,18 +10247,18 @@
         </is>
       </c>
       <c r="C51" s="28" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 固定资产净值口径12%</t>
+          <t>通用默认: 当年转固=(期初在建+当年Capex)×75%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>当年转固部分折旧率</t>
+          <t>固定资产折旧率(期初净值)</t>
         </is>
       </c>
       <c r="B52" s="21" t="inlineStr">
@@ -10255,18 +10267,18 @@
         </is>
       </c>
       <c r="C52" s="28" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 转固按约半年投产计提</t>
+          <t>通用默认: 固定资产净值口径12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>固定资产处置率(期初净值)</t>
+          <t>当年转固部分折旧率</t>
         </is>
       </c>
       <c r="B53" s="21" t="inlineStr">
@@ -10275,156 +10287,144 @@
         </is>
       </c>
       <c r="C53" s="28" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 处置率1%</t>
+          <t>通用默认: 转固按约半年投产计提</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
+          <t>固定资产处置率(期初净值)</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C54" s="28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>通用默认: 处置率1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
           <t>无形资产摊销率(期初)</t>
         </is>
       </c>
-      <c r="B54" s="21" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C54" s="28" t="n">
+      <c r="C55" s="28" t="n">
         <v>0.08</v>
       </c>
-      <c r="H54" s="9" t="inlineStr">
+      <c r="H55" s="9" t="inlineStr">
         <is>
           <t>通用默认: 无形资产摊销率8%</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="19" t="inlineStr">
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>八、股利与盈余公积</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>股利支付率(按上年归母)</t>
-        </is>
-      </c>
-      <c r="B57" s="21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C57" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D57" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E57" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F57" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G57" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>通用默认: 股利支付率30%(按上年归母)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
+          <t>股利支付率(按上年归母)</t>
+        </is>
+      </c>
+      <c r="B58" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C58" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D58" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E58" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F58" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G58" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>通用默认: 股利支付率30%(按上年归母)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
           <t>法定盈余公积计提率(按当年归母)</t>
         </is>
       </c>
-      <c r="B58" s="21" t="inlineStr">
+      <c r="B59" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C58" s="28" t="n">
+      <c r="C59" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="H58" s="9" t="inlineStr">
+      <c r="H59" s="9" t="inlineStr">
         <is>
           <t>通用默认: 法定盈余公积按归母10%计提</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="19" t="inlineStr">
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>九、债务与融资 (FIN页调度输入)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>最低现金占收入比</t>
-        </is>
-      </c>
-      <c r="B61" s="21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C61" s="28" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>通用默认: 最低现金=收入×2%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>短期借款(revolver)计划还款</t>
+          <t>最低现金占收入比</t>
         </is>
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
-          <t>百万</t>
-        </is>
-      </c>
-      <c r="C62" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="29" t="n">
-        <v>0</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="n">
+        <v>0.02</v>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 短借为revolver, 无计划还款</t>
+          <t>通用默认: 最低现金=收入×2%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>一年内到期非流动负债计划还款</t>
+          <t>短期借款(revolver)计划还款</t>
         </is>
       </c>
       <c r="B63" s="21" t="inlineStr">
@@ -10433,30 +10433,30 @@
         </is>
       </c>
       <c r="C63" s="29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D63" s="29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E63" s="29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F63" s="29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G63" s="29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>自动推导: 最近年报末余额500百万按1/5逐年摊还</t>
+          <t>通用默认: 短借为revolver, 无计划还款</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>长期借款计划还款</t>
+          <t>一年内到期非流动负债计划还款</t>
         </is>
       </c>
       <c r="B64" s="21" t="inlineStr">
@@ -10465,30 +10465,30 @@
         </is>
       </c>
       <c r="C64" s="29" t="n">
-        <v>377.1</v>
+        <v>100</v>
       </c>
       <c r="D64" s="29" t="n">
-        <v>377.1</v>
+        <v>100</v>
       </c>
       <c r="E64" s="29" t="n">
-        <v>377.1</v>
+        <v>100</v>
       </c>
       <c r="F64" s="29" t="n">
-        <v>377.1</v>
+        <v>100</v>
       </c>
       <c r="G64" s="29" t="n">
-        <v>377.1</v>
+        <v>100</v>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>自动推导: 最近年报末余额1886百万按1/5逐年摊还</t>
+          <t>自动推导: 最近年报末余额500百万按1/5逐年摊还</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>租赁负债计划还款</t>
+          <t>长期借款计划还款</t>
         </is>
       </c>
       <c r="B65" s="21" t="inlineStr">
@@ -10497,50 +10497,62 @@
         </is>
       </c>
       <c r="C65" s="29" t="n">
-        <v>2.4</v>
+        <v>377.1</v>
       </c>
       <c r="D65" s="29" t="n">
-        <v>2.4</v>
+        <v>377.1</v>
       </c>
       <c r="E65" s="29" t="n">
-        <v>2.4</v>
+        <v>377.1</v>
       </c>
       <c r="F65" s="29" t="n">
-        <v>2.4</v>
+        <v>377.1</v>
       </c>
       <c r="G65" s="29" t="n">
-        <v>2.4</v>
+        <v>377.1</v>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>自动推导: 最近年报末余额11.8百万按1/5逐年摊还</t>
+          <t>自动推导: 最近年报末余额1886百万按1/5逐年摊还</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>短期借款利率</t>
+          <t>租赁负债计划还款</t>
         </is>
       </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C66" s="28" t="n">
-        <v>0.03</v>
+          <t>百万</t>
+        </is>
+      </c>
+      <c r="C66" s="29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D66" s="29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E66" s="29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F66" s="29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G66" s="29" t="n">
+        <v>2.4</v>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 一年期LPR附近</t>
+          <t>自动推导: 最近年报末余额11.8百万按1/5逐年摊还</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>一年内到期非流动负债利率</t>
+          <t>短期借款利率</t>
         </is>
       </c>
       <c r="B67" s="21" t="inlineStr">
@@ -10549,18 +10561,18 @@
         </is>
       </c>
       <c r="C67" s="28" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 参照综合借款成本</t>
+          <t>通用默认: 一年期LPR附近</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>长期借款利率</t>
+          <t>一年内到期非流动负债利率</t>
         </is>
       </c>
       <c r="B68" s="21" t="inlineStr">
@@ -10569,18 +10581,18 @@
         </is>
       </c>
       <c r="C68" s="28" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 项目贷略高</t>
+          <t>通用默认: 参照综合借款成本</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>租赁负债利率</t>
+          <t>长期借款利率</t>
         </is>
       </c>
       <c r="B69" s="21" t="inlineStr">
@@ -10589,18 +10601,18 @@
         </is>
       </c>
       <c r="C69" s="28" t="n">
-        <v>0.045</v>
+        <v>0.037</v>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 租赁内含利率4-5%</t>
+          <t>通用默认: 项目贷略高</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>货币资金收益率(按平均余额)</t>
+          <t>租赁负债利率</t>
         </is>
       </c>
       <c r="B70" s="21" t="inlineStr">
@@ -10609,85 +10621,85 @@
         </is>
       </c>
       <c r="C70" s="28" t="n">
-        <v>0.012</v>
+        <v>0.045</v>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 活期+短期存款1.2%</t>
+          <t>通用默认: 租赁内含利率4-5%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>其他财务费用(手续费/汇兑)</t>
+          <t>货币资金收益率(按平均余额)</t>
         </is>
       </c>
       <c r="B71" s="21" t="inlineStr">
         <is>
-          <t>百万</t>
-        </is>
-      </c>
-      <c r="C71" s="29" t="n">
-        <v>30</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C71" s="28" t="n">
+        <v>0.012</v>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 手续费/汇兑等30百万</t>
+          <t>通用默认: 活期+短期存款1.2%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
+          <t>其他财务费用(手续费/汇兑)</t>
+        </is>
+      </c>
+      <c r="B72" s="21" t="inlineStr">
+        <is>
+          <t>百万</t>
+        </is>
+      </c>
+      <c r="C72" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>通用默认: 手续费/汇兑等30百万</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
           <t>2025A末有息负债合计</t>
         </is>
       </c>
-      <c r="B72" s="21" t="inlineStr">
+      <c r="B73" s="21" t="inlineStr">
         <is>
           <t>百万</t>
         </is>
       </c>
-      <c r="C72" s="25" t="n">
+      <c r="C73" s="25" t="n">
         <v>4567.5</v>
       </c>
-      <c r="H72" s="11" t="inlineStr">
+      <c r="H73" s="11" t="inlineStr">
         <is>
           <t>＝短借2169.9+一年内500.1+长借1885.7+租赁11.8 (东财F10 2025年报); WACC的Wd市值口径引用本行</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="19" t="inlineStr">
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>十、WACC 与终值 (全公式化, 联动Relative_Val可比beta)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>无风险利率 rf</t>
-        </is>
-      </c>
-      <c r="B75" s="21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C75" s="28" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>通用默认: 10年期国债收益率约2.0%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>股权风险溢价 ERP</t>
+          <t>无风险利率 rf</t>
         </is>
       </c>
       <c r="B76" s="21" t="inlineStr">
@@ -10696,81 +10708,80 @@
         </is>
       </c>
       <c r="C76" s="28" t="n">
-        <v>0.055</v>
+        <v>0.02</v>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>通用默认: A股ERP中枢5.5%</t>
+          <t>通用默认: 10年期国债收益率约2.0%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>可比公司无杠杆βu中位数</t>
+          <t>股权风险溢价 ERP</t>
         </is>
       </c>
       <c r="B77" s="21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C77" s="31">
-        <f>Relative_Val!$O$9</f>
-        <v/>
-      </c>
-      <c r="H77" s="11" t="inlineStr">
-        <is>
-          <t>＝MEDIAN(可比公司βl/(1+(1-t)×D/E)), 见Relative_Val页L-O列; 改可比beta输入即联动</t>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C77" s="28" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>通用默认: A股ERP中枢5.5%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>目标债务权重 Wd (市值口径)</t>
+          <t>可比公司无杠杆βu中位数</t>
         </is>
       </c>
       <c r="B78" s="21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C78" s="16">
-        <f>C72/(C72+C9)</f>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C78" s="31">
+        <f>Relative_Val!$O$9</f>
         <v/>
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>＝2025A末有息负债/(有息负债+总市值): 以市值口径现状结构为目标结构</t>
+          <t>＝MEDIAN(可比公司βl/(1+(1-t)×D/E)), 见Relative_Val页L-O列; 改可比beta输入即联动</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>目标 D/E = Wd/(1-Wd)</t>
+          <t>目标债务权重 Wd (市值口径)</t>
         </is>
       </c>
       <c r="B79" s="21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C79" s="31">
-        <f>C78/(1-C78)</f>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C79" s="16">
+        <f>C73/(C73+C9)</f>
         <v/>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>relever用目标产权比率</t>
+          <t>＝2025A末有息负债/(有息负债+总市值): 以市值口径现状结构为目标结构</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>再杠杆βl = βu×(1+(1-t)×D/E)</t>
+          <t>目标 D/E = Wd/(1-Wd)</t>
         </is>
       </c>
       <c r="B80" s="21" t="inlineStr">
@@ -10779,39 +10790,40 @@
         </is>
       </c>
       <c r="C80" s="31">
-        <f>C77*(1+(1-C37)*C79)</f>
+        <f>C79/(1-C79)</f>
         <v/>
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>Hamada公式, t=2026E有效税率</t>
+          <t>relever用目标产权比率</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>个股/执行风险溢价 (已删除=0)</t>
+          <t>再杠杆βl = βu×(1+(1-t)×D/E)</t>
         </is>
       </c>
       <c r="B81" s="21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C81" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>通用默认: 不取个股溢价(避免与β/情景重复计价)</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C81" s="31">
+        <f>C78*(1+(1-C37)*C80)</f>
+        <v/>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>Hamada公式, t=2026E有效税率</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>股权成本 Ke = rf+βl×ERP+溢价</t>
+          <t>个股/执行风险溢价 (已删除=0)</t>
         </is>
       </c>
       <c r="B82" s="21" t="inlineStr">
@@ -10819,20 +10831,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C82" s="16">
-        <f>C75+C80*C76+C81</f>
-        <v/>
-      </c>
-      <c r="H82" s="11" t="inlineStr">
-        <is>
-          <t>CAPM公式(溢价默认为0)</t>
+      <c r="C82" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>通用默认: 不取个股溢价(避免与β/情景重复计价)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>债务成本 Kd</t>
+          <t>股权成本 Ke = rf+βl×ERP+溢价</t>
         </is>
       </c>
       <c r="B83" s="21" t="inlineStr">
@@ -10840,19 +10851,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C83" s="28" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>通用默认: ≈四档债务加权平均利率</t>
+      <c r="C83" s="16">
+        <f>C76+C81*C77+C82</f>
+        <v/>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>CAPM公式(溢价默认为0)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>WACC (计算值)</t>
+          <t>债务成本 Kd</t>
         </is>
       </c>
       <c r="B84" s="21" t="inlineStr">
@@ -10860,20 +10872,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C84" s="16">
-        <f>(1-C78)*C82+C78*C83*(1-C37)</f>
-        <v/>
-      </c>
-      <c r="H84" s="11" t="inlineStr">
-        <is>
-          <t>＝(1-Wd)×Ke + Wd×Kd×(1-t)</t>
+      <c r="C84" s="28" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>通用默认: ≈四档债务加权平均利率</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>WACC override (留空=用计算值)</t>
+          <t>WACC (计算值)</t>
         </is>
       </c>
       <c r="B85" s="21" t="inlineStr">
@@ -10881,17 +10892,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C85" s="28" t="n"/>
+      <c r="C85" s="16">
+        <f>(1-C79)*C83+C79*C84*(1-C37)</f>
+        <v/>
+      </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>蓝色输入, 留空则采用上方计算值; 填入数值则覆盖(Checks页校验采用值=计算值或override非空)</t>
+          <t>＝(1-Wd)×Ke + Wd×Kd×(1-t)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>WACC (采用值)</t>
+          <t>WACC override (留空=用计算值)</t>
         </is>
       </c>
       <c r="B86" s="21" t="inlineStr">
@@ -10899,114 +10913,132 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C86" s="18">
-        <f>IF(C85="",C84,C85)</f>
-        <v/>
-      </c>
+      <c r="C86" s="28" t="n"/>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>＝IF(override="", 计算值, override); DCF/Sensitivity/Scenarios全部引用本行</t>
+          <t>蓝色输入, 留空则采用上方计算值; 填入数值则覆盖(Checks页校验采用值=计算值或override非空)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
+          <t>WACC (采用值)</t>
+        </is>
+      </c>
+      <c r="B87" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C87" s="18">
+        <f>IF(C86="",C85,C86)</f>
+        <v/>
+      </c>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>＝IF(override="", 计算值, override); DCF/Sensitivity/Scenarios全部引用本行</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
           <t>永续增长率 g</t>
         </is>
       </c>
-      <c r="B87" s="21" t="inlineStr">
+      <c r="B88" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C87" s="28" t="n">
+      <c r="C88" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="H87" s="9" t="inlineStr">
+      <c r="H88" s="9" t="inlineStr">
         <is>
           <t>通用默认: 长期名义增速中枢下沿</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="19" t="inlineStr">
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="19" t="inlineStr">
         <is>
           <t>十一、情景参数 (驱动情景开关 &amp; Scenarios页)</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>情景</t>
         </is>
       </c>
-      <c r="C90" s="27" t="inlineStr">
+      <c r="C91" s="27" t="inlineStr">
         <is>
           <t>收入增速调整</t>
         </is>
       </c>
-      <c r="D90" s="27" t="inlineStr">
+      <c r="D91" s="27" t="inlineStr">
         <is>
           <t>净利率调整</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="H91" s="3" t="inlineStr">
         <is>
           <t>情景逻辑</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="32" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="32" t="inlineStr">
         <is>
           <t>熊市 Bear</t>
         </is>
       </c>
-      <c r="C91" s="28" t="n">
+      <c r="C92" s="28" t="n">
         <v>-0.15</v>
       </c>
-      <c r="D91" s="28" t="n">
+      <c r="D92" s="28" t="n">
         <v>-0.03</v>
       </c>
-      <c r="H91" s="11" t="inlineStr">
+      <c r="H92" s="11" t="inlineStr">
         <is>
           <t>通用默认: 分部增速-15pct, 净利率-3pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>基准 Base</t>
-        </is>
-      </c>
-      <c r="C92" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="11" t="inlineStr">
-        <is>
-          <t>基准: 不调整</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
+          <t>基准 Base</t>
+        </is>
+      </c>
+      <c r="C93" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>基准: 不调整</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
           <t>牛市 Bull</t>
         </is>
       </c>
-      <c r="C93" s="28" t="n">
+      <c r="C94" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="D93" s="28" t="n">
+      <c r="D94" s="28" t="n">
         <v>0.015</v>
       </c>
-      <c r="H93" s="11" t="inlineStr">
+      <c r="H94" s="11" t="inlineStr">
         <is>
           <t>通用默认: 分部增速+10pct, 净利率+1.5pct</t>
         </is>
@@ -11015,17 +11047,17 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A89:J89"/>
-    <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A49:J49"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A48:J48"/>
     <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A57:J57"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A90:J90"/>
+    <mergeCell ref="A41:J41"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11249,23 +11281,23 @@
         </is>
       </c>
       <c r="E8" s="16">
-        <f>(Assumptions!C$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$91,Assumptions!$C$92,Assumptions!$C$93))</f>
+        <f>(Assumptions!C$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$92,Assumptions!$C$93,Assumptions!$C$94))</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>(Assumptions!D$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$91,Assumptions!$C$92,Assumptions!$C$93))</f>
+        <f>(Assumptions!D$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$92,Assumptions!$C$93,Assumptions!$C$94))</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>(Assumptions!E$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$91,Assumptions!$C$92,Assumptions!$C$93))</f>
+        <f>(Assumptions!E$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$92,Assumptions!$C$93,Assumptions!$C$94))</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>(Assumptions!F$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$91,Assumptions!$C$92,Assumptions!$C$93))</f>
+        <f>(Assumptions!F$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$92,Assumptions!$C$93,Assumptions!$C$94))</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>(Assumptions!G$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$91,Assumptions!$C$92,Assumptions!$C$93))</f>
+        <f>(Assumptions!G$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$92,Assumptions!$C$93,Assumptions!$C$94))</f>
         <v/>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -11290,23 +11322,23 @@
         <v>0.3691</v>
       </c>
       <c r="E9" s="16">
-        <f>(Assumptions!C$27+CHOOSE(Assumptions!$C$5,Assumptions!$D$91,Assumptions!$D$92,Assumptions!$D$93))</f>
+        <f>(Assumptions!C$27+CHOOSE(Assumptions!$C$5,Assumptions!$D$92,Assumptions!$D$93,Assumptions!$D$94))</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(Assumptions!D$27+CHOOSE(Assumptions!$C$5,Assumptions!$D$91,Assumptions!$D$92,Assumptions!$D$93))</f>
+        <f>(Assumptions!D$27+CHOOSE(Assumptions!$C$5,Assumptions!$D$92,Assumptions!$D$93,Assumptions!$D$94))</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>(Assumptions!E$27+CHOOSE(Assumptions!$C$5,Assumptions!$D$91,Assumptions!$D$92,Assumptions!$D$93))</f>
+        <f>(Assumptions!E$27+CHOOSE(Assumptions!$C$5,Assumptions!$D$92,Assumptions!$D$93,Assumptions!$D$94))</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>(Assumptions!F$27+CHOOSE(Assumptions!$C$5,Assumptions!$D$91,Assumptions!$D$92,Assumptions!$D$93))</f>
+        <f>(Assumptions!F$27+CHOOSE(Assumptions!$C$5,Assumptions!$D$92,Assumptions!$D$93,Assumptions!$D$94))</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>(Assumptions!G$27+CHOOSE(Assumptions!$C$5,Assumptions!$D$91,Assumptions!$D$92,Assumptions!$D$93))</f>
+        <f>(Assumptions!G$27+CHOOSE(Assumptions!$C$5,Assumptions!$D$92,Assumptions!$D$93,Assumptions!$D$94))</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -11470,23 +11502,23 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>(Assumptions!C$24+CHOOSE(Assumptions!$C$5,Assumptions!$C$91,Assumptions!$C$92,Assumptions!$C$93))</f>
+        <f>(Assumptions!C$24+CHOOSE(Assumptions!$C$5,Assumptions!$C$92,Assumptions!$C$93,Assumptions!$C$94))</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>(Assumptions!D$24+CHOOSE(Assumptions!$C$5,Assumptions!$C$91,Assumptions!$C$92,Assumptions!$C$93))</f>
+        <f>(Assumptions!D$24+CHOOSE(Assumptions!$C$5,Assumptions!$C$92,Assumptions!$C$93,Assumptions!$C$94))</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>(Assumptions!E$24+CHOOSE(Assumptions!$C$5,Assumptions!$C$91,Assumptions!$C$92,Assumptions!$C$93))</f>
+        <f>(Assumptions!E$24+CHOOSE(Assumptions!$C$5,Assumptions!$C$92,Assumptions!$C$93,Assumptions!$C$94))</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>(Assumptions!F$24+CHOOSE(Assumptions!$C$5,Assumptions!$C$91,Assumptions!$C$92,Assumptions!$C$93))</f>
+        <f>(Assumptions!F$24+CHOOSE(Assumptions!$C$5,Assumptions!$C$92,Assumptions!$C$93,Assumptions!$C$94))</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>(Assumptions!G$24+CHOOSE(Assumptions!$C$5,Assumptions!$C$91,Assumptions!$C$92,Assumptions!$C$93))</f>
+        <f>(Assumptions!G$24+CHOOSE(Assumptions!$C$5,Assumptions!$C$92,Assumptions!$C$93,Assumptions!$C$94))</f>
         <v/>
       </c>
       <c r="J15" s="11" t="inlineStr">
@@ -11511,23 +11543,23 @@
         <v>0.0288</v>
       </c>
       <c r="E16" s="16">
-        <f>(Assumptions!C$28+CHOOSE(Assumptions!$C$5,Assumptions!$D$91,Assumptions!$D$92,Assumptions!$D$93))</f>
+        <f>(Assumptions!C$28+CHOOSE(Assumptions!$C$5,Assumptions!$D$92,Assumptions!$D$93,Assumptions!$D$94))</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>(Assumptions!D$28+CHOOSE(Assumptions!$C$5,Assumptions!$D$91,Assumptions!$D$92,Assumptions!$D$93))</f>
+        <f>(Assumptions!D$28+CHOOSE(Assumptions!$C$5,Assumptions!$D$92,Assumptions!$D$93,Assumptions!$D$94))</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>(Assumptions!E$28+CHOOSE(Assumptions!$C$5,Assumptions!$D$91,Assumptions!$D$92,Assumptions!$D$93))</f>
+        <f>(Assumptions!E$28+CHOOSE(Assumptions!$C$5,Assumptions!$D$92,Assumptions!$D$93,Assumptions!$D$94))</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>(Assumptions!F$28+CHOOSE(Assumptions!$C$5,Assumptions!$D$91,Assumptions!$D$92,Assumptions!$D$93))</f>
+        <f>(Assumptions!F$28+CHOOSE(Assumptions!$C$5,Assumptions!$D$92,Assumptions!$D$93,Assumptions!$D$94))</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>(Assumptions!G$28+CHOOSE(Assumptions!$C$5,Assumptions!$D$91,Assumptions!$D$92,Assumptions!$D$93))</f>
+        <f>(Assumptions!G$28+CHOOSE(Assumptions!$C$5,Assumptions!$D$92,Assumptions!$D$93,Assumptions!$D$94))</f>
         <v/>
       </c>
       <c r="J16" s="11" t="inlineStr">
@@ -11948,7 +11980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12684,7 +12716,11 @@
         <f>I17-I18</f>
         <v/>
       </c>
-      <c r="J19" s="11" t="inlineStr"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>合并口径(含少数股东损益)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -12692,171 +12728,212 @@
           <t>归母净利润</t>
         </is>
       </c>
-      <c r="B20" s="35">
-        <f>B19</f>
-        <v/>
-      </c>
-      <c r="C20" s="35">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="35">
-        <f>D19</f>
-        <v/>
+      <c r="B20" s="36" t="n">
+        <v>1512.5</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>2587.2</v>
+      </c>
+      <c r="D20" s="36" t="n">
+        <v>3822.3</v>
       </c>
       <c r="E20" s="35">
-        <f>E19</f>
+        <f>E19*(1-Assumptions!C$38)</f>
         <v/>
       </c>
       <c r="F20" s="35">
-        <f>F19</f>
+        <f>F19*(1-Assumptions!D$38)</f>
         <v/>
       </c>
       <c r="G20" s="35">
-        <f>G19</f>
+        <f>G19*(1-Assumptions!E$38)</f>
         <v/>
       </c>
       <c r="H20" s="35">
-        <f>H19</f>
+        <f>H19*(1-Assumptions!F$38)</f>
         <v/>
       </c>
       <c r="I20" s="35">
-        <f>I19</f>
+        <f>I19*(1-Assumptions!G$38)</f>
         <v/>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>历史: 2023A 15.1亿/2024A 25.9亿/2025A 38.2亿</t>
+          <t>历史: 2023A 15.1亿/2024A 25.9亿/2025A 38.2亿 (config硬数, 归母口径=hist.cf.np); 预测=净利润×(1-少数股东损益占比)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  归母净利率</t>
-        </is>
-      </c>
-      <c r="B21" s="16">
-        <f>B20/B4</f>
-        <v/>
-      </c>
-      <c r="C21" s="16">
-        <f>C20/C4</f>
-        <v/>
-      </c>
-      <c r="D21" s="16">
-        <f>D20/D4</f>
-        <v/>
-      </c>
-      <c r="E21" s="16">
-        <f>E20/E4</f>
-        <v/>
-      </c>
-      <c r="F21" s="16">
-        <f>F20/F4</f>
-        <v/>
-      </c>
-      <c r="G21" s="16">
-        <f>G20/G4</f>
-        <v/>
-      </c>
-      <c r="H21" s="16">
-        <f>H20/H4</f>
-        <v/>
-      </c>
-      <c r="I21" s="16">
-        <f>I20/I4</f>
+          <t>少数股东损益</t>
+        </is>
+      </c>
+      <c r="B21" s="26">
+        <f>B19-B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="26">
+        <f>C19-C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="26">
+        <f>D19-D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="26">
+        <f>E19-E20</f>
+        <v/>
+      </c>
+      <c r="F21" s="26">
+        <f>F19-F20</f>
+        <v/>
+      </c>
+      <c r="G21" s="26">
+        <f>G19-G20</f>
+        <v/>
+      </c>
+      <c r="H21" s="26">
+        <f>H19-H20</f>
+        <v/>
+      </c>
+      <c r="I21" s="26">
+        <f>I19-I20</f>
         <v/>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2025A 20.2%</t>
+          <t>＝净利润-归母净利润; 历史为合并与归母口径差(倒挤), 预测=净利润×mi_share</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">  归母净利率</t>
+        </is>
+      </c>
+      <c r="B22" s="16">
+        <f>B20/B4</f>
+        <v/>
+      </c>
+      <c r="C22" s="16">
+        <f>C20/C4</f>
+        <v/>
+      </c>
+      <c r="D22" s="16">
+        <f>D20/D4</f>
+        <v/>
+      </c>
+      <c r="E22" s="16">
+        <f>E20/E4</f>
+        <v/>
+      </c>
+      <c r="F22" s="16">
+        <f>F20/F4</f>
+        <v/>
+      </c>
+      <c r="G22" s="16">
+        <f>G20/G4</f>
+        <v/>
+      </c>
+      <c r="H22" s="16">
+        <f>H20/H4</f>
+        <v/>
+      </c>
+      <c r="I22" s="16">
+        <f>I20/I4</f>
+        <v/>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>2025A 20.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>EPS(元/股)</t>
         </is>
       </c>
-      <c r="B22" s="14">
+      <c r="B23" s="14">
         <f>B20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="C22" s="14">
+      <c r="C23" s="14">
         <f>C20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="D22" s="14">
+      <c r="D23" s="14">
         <f>D20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="E22" s="14">
+      <c r="E23" s="14">
         <f>E20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="F22" s="14">
+      <c r="F23" s="14">
         <f>F20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="G22" s="14">
+      <c r="G23" s="14">
         <f>G20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="H22" s="14">
+      <c r="H23" s="14">
         <f>H20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="I22" s="14">
+      <c r="I23" s="14">
         <f>I20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>＝归母/稀释股数(Equity_Roll页, 现=19.24亿股)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>EBIT (利润总额+财务费用)</t>
         </is>
       </c>
-      <c r="B23" s="35">
+      <c r="B24" s="35">
         <f>B17+B13</f>
         <v/>
       </c>
-      <c r="C23" s="35">
+      <c r="C24" s="35">
         <f>C17+C13</f>
         <v/>
       </c>
-      <c r="D23" s="35">
+      <c r="D24" s="35">
         <f>D17+D13</f>
         <v/>
       </c>
-      <c r="E23" s="35">
+      <c r="E24" s="35">
         <f>E17+E13</f>
         <v/>
       </c>
-      <c r="F23" s="35">
+      <c r="F24" s="35">
         <f>F17+F13</f>
         <v/>
       </c>
-      <c r="G23" s="35">
+      <c r="G24" s="35">
         <f>G17+G13</f>
         <v/>
       </c>
-      <c r="H23" s="35">
+      <c r="H24" s="35">
         <f>H17+H13</f>
         <v/>
       </c>
-      <c r="I23" s="35">
+      <c r="I24" s="35">
         <f>I17+I13</f>
         <v/>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>供DCF页FCFF计算</t>
         </is>
@@ -13056,23 +13133,23 @@
         <v>5507.2</v>
       </c>
       <c r="E6" s="26">
-        <f>Assumptions!C$41/365*IS!E4</f>
+        <f>Assumptions!C$42/365*IS!E4</f>
         <v/>
       </c>
       <c r="F6" s="26">
-        <f>Assumptions!D$41/365*IS!F4</f>
+        <f>Assumptions!D$42/365*IS!F4</f>
         <v/>
       </c>
       <c r="G6" s="26">
-        <f>Assumptions!E$41/365*IS!G4</f>
+        <f>Assumptions!E$42/365*IS!G4</f>
         <v/>
       </c>
       <c r="H6" s="26">
-        <f>Assumptions!F$41/365*IS!H4</f>
+        <f>Assumptions!F$42/365*IS!H4</f>
         <v/>
       </c>
       <c r="I6" s="26">
-        <f>Assumptions!G$41/365*IS!I4</f>
+        <f>Assumptions!G$42/365*IS!I4</f>
         <v/>
       </c>
       <c r="J6" s="11" t="inlineStr">
@@ -13097,23 +13174,23 @@
         <v>98.7</v>
       </c>
       <c r="E7" s="26">
-        <f>IS!E4*Assumptions!C$44</f>
+        <f>IS!E4*Assumptions!C$45</f>
         <v/>
       </c>
       <c r="F7" s="26">
-        <f>IS!F4*Assumptions!D$44</f>
+        <f>IS!F4*Assumptions!D$45</f>
         <v/>
       </c>
       <c r="G7" s="26">
-        <f>IS!G4*Assumptions!E$44</f>
+        <f>IS!G4*Assumptions!E$45</f>
         <v/>
       </c>
       <c r="H7" s="26">
-        <f>IS!H4*Assumptions!F$44</f>
+        <f>IS!H4*Assumptions!F$45</f>
         <v/>
       </c>
       <c r="I7" s="26">
-        <f>IS!I4*Assumptions!G$44</f>
+        <f>IS!I4*Assumptions!G$45</f>
         <v/>
       </c>
       <c r="J7" s="11" t="inlineStr">
@@ -13179,23 +13256,23 @@
         <v>4245.9</v>
       </c>
       <c r="E9" s="26">
-        <f>Assumptions!C$42/365*IS!E6</f>
+        <f>Assumptions!C$43/365*IS!E6</f>
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>Assumptions!D$42/365*IS!F6</f>
+        <f>Assumptions!D$43/365*IS!F6</f>
         <v/>
       </c>
       <c r="G9" s="26">
-        <f>Assumptions!E$42/365*IS!G6</f>
+        <f>Assumptions!E$43/365*IS!G6</f>
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>Assumptions!F$42/365*IS!H6</f>
+        <f>Assumptions!F$43/365*IS!H6</f>
         <v/>
       </c>
       <c r="I9" s="26">
-        <f>Assumptions!G$42/365*IS!I6</f>
+        <f>Assumptions!G$43/365*IS!I6</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -13754,23 +13831,23 @@
         <v>6629.6</v>
       </c>
       <c r="E23" s="26">
-        <f>Assumptions!C$43/365*IS!E6</f>
+        <f>Assumptions!C$44/365*IS!E6</f>
         <v/>
       </c>
       <c r="F23" s="26">
-        <f>Assumptions!D$43/365*IS!F6</f>
+        <f>Assumptions!D$44/365*IS!F6</f>
         <v/>
       </c>
       <c r="G23" s="26">
-        <f>Assumptions!E$43/365*IS!G6</f>
+        <f>Assumptions!E$44/365*IS!G6</f>
         <v/>
       </c>
       <c r="H23" s="26">
-        <f>Assumptions!F$43/365*IS!H6</f>
+        <f>Assumptions!F$44/365*IS!H6</f>
         <v/>
       </c>
       <c r="I23" s="26">
-        <f>Assumptions!G$43/365*IS!I6</f>
+        <f>Assumptions!G$44/365*IS!I6</f>
         <v/>
       </c>
       <c r="J23" s="11" t="inlineStr">
@@ -13836,23 +13913,23 @@
         <v>530.2</v>
       </c>
       <c r="E25" s="26">
-        <f>IS!E4*Assumptions!C$45</f>
+        <f>IS!E4*Assumptions!C$46</f>
         <v/>
       </c>
       <c r="F25" s="26">
-        <f>IS!F4*Assumptions!D$45</f>
+        <f>IS!F4*Assumptions!D$46</f>
         <v/>
       </c>
       <c r="G25" s="26">
-        <f>IS!G4*Assumptions!E$45</f>
+        <f>IS!G4*Assumptions!E$46</f>
         <v/>
       </c>
       <c r="H25" s="26">
-        <f>IS!H4*Assumptions!F$45</f>
+        <f>IS!H4*Assumptions!F$46</f>
         <v/>
       </c>
       <c r="I25" s="26">
-        <f>IS!I4*Assumptions!G$45</f>
+        <f>IS!I4*Assumptions!G$46</f>
         <v/>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -13877,23 +13954,23 @@
         <v>274.2</v>
       </c>
       <c r="E26" s="26">
-        <f>IS!E4*Assumptions!C$46</f>
+        <f>IS!E4*Assumptions!C$47</f>
         <v/>
       </c>
       <c r="F26" s="26">
-        <f>IS!F4*Assumptions!D$46</f>
+        <f>IS!F4*Assumptions!D$47</f>
         <v/>
       </c>
       <c r="G26" s="26">
-        <f>IS!G4*Assumptions!E$46</f>
+        <f>IS!G4*Assumptions!E$47</f>
         <v/>
       </c>
       <c r="H26" s="26">
-        <f>IS!H4*Assumptions!F$46</f>
+        <f>IS!H4*Assumptions!F$47</f>
         <v/>
       </c>
       <c r="I26" s="26">
-        <f>IS!I4*Assumptions!G$46</f>
+        <f>IS!I4*Assumptions!G$47</f>
         <v/>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -14718,35 +14795,35 @@
           <t>配平差额检查(资产-负债权益)</t>
         </is>
       </c>
-      <c r="B47" s="36">
+      <c r="B47" s="37">
         <f>B21-B46</f>
         <v/>
       </c>
-      <c r="C47" s="36">
+      <c r="C47" s="37">
         <f>C21-C46</f>
         <v/>
       </c>
-      <c r="D47" s="36">
+      <c r="D47" s="37">
         <f>D21-D46</f>
         <v/>
       </c>
-      <c r="E47" s="36">
+      <c r="E47" s="37">
         <f>E21-E46</f>
         <v/>
       </c>
-      <c r="F47" s="36">
+      <c r="F47" s="37">
         <f>F21-F46</f>
         <v/>
       </c>
-      <c r="G47" s="36">
+      <c r="G47" s="37">
         <f>G21-G46</f>
         <v/>
       </c>
-      <c r="H47" s="36">
+      <c r="H47" s="37">
         <f>H21-H46</f>
         <v/>
       </c>
-      <c r="I47" s="36">
+      <c r="I47" s="37">
         <f>I21-I46</f>
         <v/>
       </c>
@@ -15034,13 +15111,13 @@
           <t>经营活动现金流量净额</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="36" t="n">
         <v>2243.3</v>
       </c>
-      <c r="C8" s="37" t="n">
+      <c r="C8" s="36" t="n">
         <v>2325.2</v>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="36" t="n">
         <v>3872</v>
       </c>
       <c r="E8" s="35">
@@ -15210,13 +15287,13 @@
           <t>投资活动现金流量净额</t>
         </is>
       </c>
-      <c r="B12" s="37" t="n">
+      <c r="B12" s="36" t="n">
         <v>-1870</v>
       </c>
-      <c r="C12" s="37" t="n">
+      <c r="C12" s="36" t="n">
         <v>-3034.9</v>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="36" t="n">
         <v>-2655.1</v>
       </c>
       <c r="E12" s="35">
@@ -15392,13 +15469,13 @@
           <t>筹资活动现金流量净额</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="36" t="n">
         <v>428.3</v>
       </c>
-      <c r="C16" s="37" t="n">
+      <c r="C16" s="36" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="D16" s="37" t="n">
+      <c r="D16" s="36" t="n">
         <v>-209.7</v>
       </c>
       <c r="E16" s="35">
@@ -15523,13 +15600,13 @@
           <t>期末货币资金(=BS货币资金)</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="36" t="n">
         <v>2097.9</v>
       </c>
-      <c r="C19" s="37" t="n">
+      <c r="C19" s="36" t="n">
         <v>1542.7</v>
       </c>
-      <c r="D19" s="37" t="n">
+      <c r="D19" s="36" t="n">
         <v>2579.1</v>
       </c>
       <c r="E19" s="35">
@@ -16259,23 +16336,23 @@
         </is>
       </c>
       <c r="E22" s="26">
-        <f>E21*Assumptions!$C$54</f>
+        <f>E21*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="F22" s="26">
-        <f>F21*Assumptions!$C$54</f>
+        <f>F21*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="G22" s="26">
-        <f>G21*Assumptions!$C$54</f>
+        <f>G21*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="H22" s="26">
-        <f>H21*Assumptions!$C$54</f>
+        <f>H21*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="I22" s="26">
-        <f>I21*Assumptions!$C$54</f>
+        <f>I21*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="J22" s="11" t="inlineStr">
@@ -16330,23 +16407,23 @@
         </is>
       </c>
       <c r="E26" s="26">
-        <f>IS!D20*Assumptions!C$57</f>
+        <f>IS!D20*Assumptions!C$58</f>
         <v/>
       </c>
       <c r="F26" s="26">
-        <f>IS!E20*Assumptions!D$57</f>
+        <f>IS!E20*Assumptions!D$58</f>
         <v/>
       </c>
       <c r="G26" s="26">
-        <f>IS!F20*Assumptions!E$57</f>
+        <f>IS!F20*Assumptions!E$58</f>
         <v/>
       </c>
       <c r="H26" s="26">
-        <f>IS!G20*Assumptions!F$57</f>
+        <f>IS!G20*Assumptions!F$58</f>
         <v/>
       </c>
       <c r="I26" s="26">
-        <f>IS!H20*Assumptions!G$57</f>
+        <f>IS!H20*Assumptions!G$58</f>
         <v/>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -16499,23 +16576,23 @@
         </is>
       </c>
       <c r="E7" s="26">
-        <f>(E13+E14)*Assumptions!$C$50</f>
+        <f>(E13+E14)*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="F7" s="26">
-        <f>(F13+F14)*Assumptions!$C$50</f>
+        <f>(F13+F14)*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="G7" s="26">
-        <f>(G13+G14)*Assumptions!$C$50</f>
+        <f>(G13+G14)*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="H7" s="26">
-        <f>(H13+H14)*Assumptions!$C$50</f>
+        <f>(H13+H14)*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="I7" s="26">
-        <f>(I13+I14)*Assumptions!$C$50</f>
+        <f>(I13+I14)*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="J7" s="11" t="inlineStr">
@@ -16531,23 +16608,23 @@
         </is>
       </c>
       <c r="E8" s="26">
-        <f>E6*Assumptions!$C$51+E7*Assumptions!$C$52</f>
+        <f>E6*Assumptions!$C$52+E7*Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>F6*Assumptions!$C$51+F7*Assumptions!$C$52</f>
+        <f>F6*Assumptions!$C$52+F7*Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="G8" s="26">
-        <f>G6*Assumptions!$C$51+G7*Assumptions!$C$52</f>
+        <f>G6*Assumptions!$C$52+G7*Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>H6*Assumptions!$C$51+H7*Assumptions!$C$52</f>
+        <f>H6*Assumptions!$C$52+H7*Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="I8" s="26">
-        <f>I6*Assumptions!$C$51+I7*Assumptions!$C$52</f>
+        <f>I6*Assumptions!$C$52+I7*Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -16563,23 +16640,23 @@
         </is>
       </c>
       <c r="E9" s="26">
-        <f>E6*Assumptions!$C$53</f>
+        <f>E6*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>F6*Assumptions!$C$53</f>
+        <f>F6*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="G9" s="26">
-        <f>G6*Assumptions!$C$53</f>
+        <f>G6*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>H6*Assumptions!$C$53</f>
+        <f>H6*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="I9" s="26">
-        <f>I6*Assumptions!$C$53</f>
+        <f>I6*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -16665,23 +16742,23 @@
         </is>
       </c>
       <c r="E14" s="26">
-        <f>IS!E4*Assumptions!C$49</f>
+        <f>IS!E4*Assumptions!C$50</f>
         <v/>
       </c>
       <c r="F14" s="26">
-        <f>IS!F4*Assumptions!D$49</f>
+        <f>IS!F4*Assumptions!D$50</f>
         <v/>
       </c>
       <c r="G14" s="26">
-        <f>IS!G4*Assumptions!E$49</f>
+        <f>IS!G4*Assumptions!E$50</f>
         <v/>
       </c>
       <c r="H14" s="26">
-        <f>IS!H4*Assumptions!F$49</f>
+        <f>IS!H4*Assumptions!F$50</f>
         <v/>
       </c>
       <c r="I14" s="26">
-        <f>IS!I4*Assumptions!G$49</f>
+        <f>IS!I4*Assumptions!G$50</f>
         <v/>
       </c>
       <c r="J14" s="11" t="inlineStr">

--- a/examples/002463_沪电股份_估值模型.xlsx
+++ b/examples/002463_沪电股份_估值模型.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="864">
   <si>
     <r>
       <rPr>
@@ -5250,16 +5250,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PE 30x ~ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">可比中位</t>
+      <t xml:space="preserve">PE 30x </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">单点（无正式可比）</t>
     </r>
   </si>
   <si>
@@ -5327,7 +5327,7 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">带</t>
+      <t xml:space="preserve">单点</t>
     </r>
   </si>
   <si>
@@ -5428,7 +5428,7 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">带</t>
+      <t xml:space="preserve">单点</t>
     </r>
     <r>
       <rPr>
@@ -35532,17 +35532,55 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">已验证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY1/NTM</t>
+      <t xml:space="preserve">排除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未验证远期盈利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仅参照</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -35852,17 +35890,55 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">已验证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY1/NTM</t>
+      <t xml:space="preserve">排除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未验证远期盈利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仅参照</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -36083,59 +36159,198 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">(A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">股</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">家</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">βu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中位数→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumptions WACC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">relever; βl/D/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">为分析师输入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">计价</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">家</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/β4</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">家</t>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参考行情终端</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">β</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与各公司最新年报杠杆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">可按终端数据更新</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">沪电股份</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">现价</t>
     </r>
     <r>
       <rPr>
@@ -36150,67 +36365,93 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">βu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中位数→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Assumptions WACC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">区</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">relever; βl/D/E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">为分析师输入</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
+    <t xml:space="preserve">002463.SZ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026E/2027E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">归母</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一致预期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">腾讯行情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PE-TTM(2026-08-17)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">沪电股份定价 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
         <rFont val="Microsoft YaHei"/>
         <family val="0"/>
         <charset val="1"/>
@@ -36219,68 +36460,189 @@
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">参考行情终端</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">β</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">与各公司最新年报杠杆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">可按终端数据更新</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">沪电股份</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基于模型基准</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">归母</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下限</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">较可比中位数折让</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反映高基数与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CCL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">成本风险</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上限</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝目标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
         <rFont val="Microsoft YaHei"/>
         <family val="0"/>
         <charset val="1"/>
@@ -36289,202 +36651,12 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">现价</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">002463.SZ</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026E/2027E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">归母</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一致预期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">腾讯行情</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PE-TTM(2026-08-17)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">沪电股份定价 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">基于模型基准</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026E</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">归母</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目标</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下限</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">较可比中位数折让</t>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无可比公司配置</t>
     </r>
     <r>
       <rPr>
@@ -36503,143 +36675,7 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">反映高基数与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CCL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">成本风险</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目标</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上限</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＝计价可比</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026E PE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中位数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">含海外</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">; ref_only</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">标记的仅参照行不参与</t>
+      <t xml:space="preserve">兜底</t>
     </r>
     <r>
       <rPr>
@@ -43081,7 +43117,7 @@
     <numFmt numFmtId="174" formatCode="0.0\x"/>
     <numFmt numFmtId="175" formatCode="0\x"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -43303,6 +43339,13 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FF0033CC"/>
       <name val="Microsoft YaHei"/>
       <family val="0"/>
@@ -43397,7 +43440,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -43498,10 +43541,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -43511,6 +43550,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -43638,11 +43681,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -43654,15 +43701,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -43686,11 +43733,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -44140,7 +44187,7 @@
       </c>
       <c r="C23" s="4" t="str">
         <f aca="false">TEXT(Relative_Val!C16,"0.00")&amp;" ~ "&amp;TEXT(Relative_Val!C17,"0.00")</f>
-        <v>82.51 ~ 116.67</v>
+        <v>82.51 ~ 82.51</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44451,18 +44498,18 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>484</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
@@ -44488,7 +44535,7 @@
         <f aca="false">H63</f>
         <v>1340.19613506997</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="26" t="s">
         <v>485</v>
       </c>
     </row>
@@ -44516,7 +44563,7 @@
         <f aca="false">CF!I8</f>
         <v>18553.0113850447</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>487</v>
       </c>
     </row>
@@ -44544,7 +44591,7 @@
         <f aca="false">-PPE!I14+PPE!I9</f>
         <v>-6387.35820631597</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>489</v>
       </c>
     </row>
@@ -44572,7 +44619,7 @@
         <f aca="false">-Schedules!I26</f>
         <v>-4447.24478038396</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>491</v>
       </c>
     </row>
@@ -44600,7 +44647,7 @@
         <f aca="false">-I64</f>
         <v>-1.7529</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>493</v>
       </c>
     </row>
@@ -44628,7 +44675,7 @@
         <f aca="false">-(I20+I31+I39+I49)</f>
         <v>-102.2</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>495</v>
       </c>
     </row>
@@ -44656,7 +44703,7 @@
         <f aca="false">I6+I7+I8+I9+I10+I11</f>
         <v>8954.65163341473</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>497</v>
       </c>
     </row>
@@ -44684,7 +44731,7 @@
         <f aca="false">IS!I4*Assumptions!$C$62</f>
         <v>1565.36528434696</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="28" t="s">
         <v>499</v>
       </c>
     </row>
@@ -44712,7 +44759,7 @@
         <f aca="false">MAX(0,I13-I12)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>501</v>
       </c>
     </row>
@@ -44740,7 +44787,7 @@
         <f aca="false">MAX(0,I12+I14-I13)</f>
         <v>7389.28634906777</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="28" t="s">
         <v>503</v>
       </c>
     </row>
@@ -44782,7 +44829,7 @@
         <f aca="false">H24</f>
         <v>0</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>506</v>
       </c>
     </row>
@@ -44810,7 +44857,7 @@
         <f aca="false">Assumptions!G$63</f>
         <v>0</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>508</v>
       </c>
     </row>
@@ -44838,7 +44885,7 @@
         <f aca="false">MIN(I19,I18)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="25" t="s">
+      <c r="J20" s="28" t="s">
         <v>510</v>
       </c>
     </row>
@@ -44866,7 +44913,7 @@
         <f aca="false">I14</f>
         <v>0</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="J21" s="28" t="s">
         <v>512</v>
       </c>
     </row>
@@ -44894,7 +44941,7 @@
         <f aca="false">I18-I20+I21</f>
         <v>0</v>
       </c>
-      <c r="J22" s="25" t="s">
+      <c r="J22" s="28" t="s">
         <v>514</v>
       </c>
     </row>
@@ -44922,7 +44969,7 @@
         <f aca="false">MIN(I15,I22)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>516</v>
       </c>
     </row>
@@ -44954,7 +45001,7 @@
         <f aca="false">I22-I23</f>
         <v>0</v>
       </c>
-      <c r="J24" s="25" t="s">
+      <c r="J24" s="28" t="s">
         <v>518</v>
       </c>
     </row>
@@ -44982,7 +45029,7 @@
         <f aca="false">(I18+I24)/2</f>
         <v>0</v>
       </c>
-      <c r="J25" s="25" t="s">
+      <c r="J25" s="28" t="s">
         <v>520</v>
       </c>
     </row>
@@ -45010,7 +45057,7 @@
         <f aca="false">I25*Assumptions!$C$67</f>
         <v>0</v>
       </c>
-      <c r="J26" s="25" t="s">
+      <c r="J26" s="28" t="s">
         <v>522</v>
       </c>
     </row>
@@ -45052,7 +45099,7 @@
         <f aca="false">H32</f>
         <v>100.1</v>
       </c>
-      <c r="J29" s="25" t="s">
+      <c r="J29" s="28" t="s">
         <v>506</v>
       </c>
     </row>
@@ -45080,7 +45127,7 @@
         <f aca="false">Assumptions!G$64</f>
         <v>100</v>
       </c>
-      <c r="J30" s="25" t="s">
+      <c r="J30" s="28" t="s">
         <v>524</v>
       </c>
     </row>
@@ -45108,7 +45155,7 @@
         <f aca="false">MIN(I30,I29)</f>
         <v>100</v>
       </c>
-      <c r="J31" s="25" t="s">
+      <c r="J31" s="28" t="s">
         <v>510</v>
       </c>
     </row>
@@ -45140,7 +45187,7 @@
         <f aca="false">I29-I31</f>
         <v>0.100000000000023</v>
       </c>
-      <c r="J32" s="25" t="s">
+      <c r="J32" s="28" t="s">
         <v>525</v>
       </c>
     </row>
@@ -45168,7 +45215,7 @@
         <f aca="false">(I29+I32)/2</f>
         <v>50.1</v>
       </c>
-      <c r="J33" s="25" t="s">
+      <c r="J33" s="28" t="s">
         <v>520</v>
       </c>
     </row>
@@ -45196,7 +45243,7 @@
         <f aca="false">I33*Assumptions!$C$68</f>
         <v>1.7034</v>
       </c>
-      <c r="J34" s="25" t="s">
+      <c r="J34" s="28" t="s">
         <v>522</v>
       </c>
     </row>
@@ -45238,7 +45285,7 @@
         <f aca="false">H42</f>
         <v>0</v>
       </c>
-      <c r="J37" s="25" t="s">
+      <c r="J37" s="28" t="s">
         <v>506</v>
       </c>
     </row>
@@ -45266,7 +45313,7 @@
         <f aca="false">Assumptions!G$65</f>
         <v>377.1</v>
       </c>
-      <c r="J38" s="25" t="s">
+      <c r="J38" s="28" t="s">
         <v>527</v>
       </c>
     </row>
@@ -45294,7 +45341,7 @@
         <f aca="false">MIN(I38,I37)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="25" t="s">
+      <c r="J39" s="28" t="s">
         <v>510</v>
       </c>
     </row>
@@ -45322,7 +45369,7 @@
         <f aca="false">I37-I39</f>
         <v>0</v>
       </c>
-      <c r="J40" s="25" t="s">
+      <c r="J40" s="28" t="s">
         <v>514</v>
       </c>
     </row>
@@ -45350,7 +45397,7 @@
         <f aca="false">MIN(I15-I23,I40)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="25" t="s">
+      <c r="J41" s="28" t="s">
         <v>516</v>
       </c>
     </row>
@@ -45382,7 +45429,7 @@
         <f aca="false">I40-I41</f>
         <v>0</v>
       </c>
-      <c r="J42" s="25" t="s">
+      <c r="J42" s="28" t="s">
         <v>518</v>
       </c>
     </row>
@@ -45410,7 +45457,7 @@
         <f aca="false">(I37+I42)/2</f>
         <v>0</v>
       </c>
-      <c r="J43" s="25" t="s">
+      <c r="J43" s="28" t="s">
         <v>520</v>
       </c>
     </row>
@@ -45438,7 +45485,7 @@
         <f aca="false">I43*Assumptions!$C$69</f>
         <v>0</v>
       </c>
-      <c r="J44" s="25" t="s">
+      <c r="J44" s="28" t="s">
         <v>522</v>
       </c>
     </row>
@@ -45480,7 +45527,7 @@
         <f aca="false">H50</f>
         <v>2.2</v>
       </c>
-      <c r="J47" s="25" t="s">
+      <c r="J47" s="28" t="s">
         <v>506</v>
       </c>
     </row>
@@ -45508,7 +45555,7 @@
         <f aca="false">Assumptions!G$66</f>
         <v>2.4</v>
       </c>
-      <c r="J48" s="25" t="s">
+      <c r="J48" s="28" t="s">
         <v>529</v>
       </c>
     </row>
@@ -45536,7 +45583,7 @@
         <f aca="false">MIN(I48,I47)</f>
         <v>2.2</v>
       </c>
-      <c r="J49" s="25" t="s">
+      <c r="J49" s="28" t="s">
         <v>510</v>
       </c>
     </row>
@@ -45568,7 +45615,7 @@
         <f aca="false">I47-I49</f>
         <v>0</v>
       </c>
-      <c r="J50" s="25" t="s">
+      <c r="J50" s="28" t="s">
         <v>525</v>
       </c>
     </row>
@@ -45596,7 +45643,7 @@
         <f aca="false">(I47+I50)/2</f>
         <v>1.1</v>
       </c>
-      <c r="J51" s="25" t="s">
+      <c r="J51" s="28" t="s">
         <v>520</v>
       </c>
     </row>
@@ -45624,23 +45671,23 @@
         <f aca="false">I51*Assumptions!$C$70</f>
         <v>0.0495</v>
       </c>
-      <c r="J52" s="25" t="s">
+      <c r="J52" s="28" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="25" t="s">
         <v>530</v>
       </c>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="26"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="25"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
@@ -45670,7 +45717,7 @@
         <f aca="false">I18+I29+I37+I47</f>
         <v>102.3</v>
       </c>
-      <c r="J55" s="25" t="s">
+      <c r="J55" s="28" t="s">
         <v>532</v>
       </c>
     </row>
@@ -45702,7 +45749,7 @@
         <f aca="false">I24+I32+I42+I50</f>
         <v>0.100000000000023</v>
       </c>
-      <c r="J56" s="25" t="s">
+      <c r="J56" s="28" t="s">
         <v>534</v>
       </c>
     </row>
@@ -45730,7 +45777,7 @@
         <f aca="false">I56-I55</f>
         <v>-102.2</v>
       </c>
-      <c r="J57" s="25" t="s">
+      <c r="J57" s="28" t="s">
         <v>536</v>
       </c>
     </row>
@@ -45758,7 +45805,7 @@
         <f aca="false">I23+I41</f>
         <v>0</v>
       </c>
-      <c r="J58" s="25" t="s">
+      <c r="J58" s="28" t="s">
         <v>538</v>
       </c>
     </row>
@@ -45786,7 +45833,7 @@
         <f aca="false">I15-I58</f>
         <v>7389.28634906777</v>
       </c>
-      <c r="J59" s="25" t="s">
+      <c r="J59" s="28" t="s">
         <v>540</v>
       </c>
     </row>
@@ -45814,7 +45861,7 @@
         <f aca="false">H61</f>
         <v>6008.26253562355</v>
       </c>
-      <c r="J60" s="27" t="s">
+      <c r="J60" s="26" t="s">
         <v>542</v>
       </c>
     </row>
@@ -45846,7 +45893,7 @@
         <f aca="false">I60+I59</f>
         <v>13397.5488846913</v>
       </c>
-      <c r="J61" s="25" t="s">
+      <c r="J61" s="28" t="s">
         <v>544</v>
       </c>
     </row>
@@ -45874,7 +45921,7 @@
         <f aca="false">I61-I60</f>
         <v>7389.28634906777</v>
       </c>
-      <c r="J62" s="25" t="s">
+      <c r="J62" s="28" t="s">
         <v>546</v>
       </c>
     </row>
@@ -45906,7 +45953,7 @@
         <f aca="false">I12+I14-I58-I59</f>
         <v>1565.36528434696</v>
       </c>
-      <c r="J63" s="25" t="s">
+      <c r="J63" s="28" t="s">
         <v>548</v>
       </c>
     </row>
@@ -45934,7 +45981,7 @@
         <f aca="false">I130</f>
         <v>1.7529</v>
       </c>
-      <c r="J64" s="25" t="s">
+      <c r="J64" s="28" t="s">
         <v>550</v>
       </c>
     </row>
@@ -45962,7 +46009,7 @@
         <f aca="false">I132</f>
         <v>17.4333685165016</v>
       </c>
-      <c r="J65" s="25" t="s">
+      <c r="J65" s="28" t="s">
         <v>552</v>
       </c>
     </row>
@@ -45990,7 +46037,7 @@
         <f aca="false">Assumptions!$C$72</f>
         <v>30</v>
       </c>
-      <c r="J66" s="25" t="s">
+      <c r="J66" s="28" t="s">
         <v>554</v>
       </c>
     </row>
@@ -46018,23 +46065,23 @@
         <f aca="false">I133</f>
         <v>14.3195314834984</v>
       </c>
-      <c r="J67" s="25" t="s">
+      <c r="J67" s="28" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="26" t="s">
+      <c r="A69" s="25" t="s">
         <v>557</v>
       </c>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="26"/>
-      <c r="I69" s="26"/>
-      <c r="J69" s="26"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="25"/>
+      <c r="J69" s="25"/>
     </row>
     <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="13" t="s">
@@ -47607,18 +47654,18 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="26" t="s">
+      <c r="A136" s="25" t="s">
         <v>623</v>
       </c>
-      <c r="B136" s="26"/>
-      <c r="C136" s="26"/>
-      <c r="D136" s="26"/>
-      <c r="E136" s="26"/>
-      <c r="F136" s="26"/>
-      <c r="G136" s="26"/>
-      <c r="H136" s="26"/>
-      <c r="I136" s="26"/>
-      <c r="J136" s="26"/>
+      <c r="B136" s="25"/>
+      <c r="C136" s="25"/>
+      <c r="D136" s="25"/>
+      <c r="E136" s="25"/>
+      <c r="F136" s="25"/>
+      <c r="G136" s="25"/>
+      <c r="H136" s="25"/>
+      <c r="I136" s="25"/>
+      <c r="J136" s="25"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
@@ -47644,7 +47691,7 @@
         <f aca="false">ABS(I64-(I26+I34+I44+I52))</f>
         <v>0</v>
       </c>
-      <c r="J137" s="25" t="s">
+      <c r="J137" s="28" t="s">
         <v>625</v>
       </c>
     </row>
@@ -47672,7 +47719,7 @@
         <f aca="false">ABS(I65-(I6+I63)/2*Assumptions!$C$71)</f>
         <v>0</v>
       </c>
-      <c r="J138" s="25" t="s">
+      <c r="J138" s="28" t="s">
         <v>627</v>
       </c>
     </row>
@@ -47700,7 +47747,7 @@
         <f aca="false">MAX(I137,I138)</f>
         <v>0</v>
       </c>
-      <c r="J139" s="25" t="s">
+      <c r="J139" s="28" t="s">
         <v>629</v>
       </c>
     </row>
@@ -47728,7 +47775,7 @@
         <f aca="false">I139&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J140" s="25"/>
+      <c r="J140" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -47864,7 +47911,7 @@
         <f aca="false">H5</f>
         <v>1924.4</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="28" t="s">
         <v>633</v>
       </c>
     </row>
@@ -47901,7 +47948,7 @@
         <f aca="false">H6</f>
         <v>1070.2</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>336</v>
       </c>
     </row>
@@ -47938,7 +47985,7 @@
         <f aca="false">H7</f>
         <v>0</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>336</v>
       </c>
     </row>
@@ -47975,7 +48022,7 @@
         <f aca="false">H8</f>
         <v>408.2</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>635</v>
       </c>
     </row>
@@ -48003,7 +48050,7 @@
         <f aca="false">IS!I20*Assumptions!$C$59</f>
         <v>1705.5977813947</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>637</v>
       </c>
     </row>
@@ -48040,7 +48087,7 @@
         <f aca="false">H10+I9</f>
         <v>6883.87545718627</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>639</v>
       </c>
     </row>
@@ -48068,7 +48115,7 @@
         <f aca="false">Schedules!I26</f>
         <v>4447.24478038396</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>641</v>
       </c>
     </row>
@@ -48105,7 +48152,7 @@
         <f aca="false">H12+IS!I20-I11-I9</f>
         <v>48829.6560873017</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>643</v>
       </c>
     </row>
@@ -48142,7 +48189,7 @@
         <f aca="false">H13</f>
         <v>0.2</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="28" t="s">
         <v>645</v>
       </c>
     </row>
@@ -48182,7 +48229,7 @@
         <f aca="false">I5+I6-I7+I8+I10+I12+I13</f>
         <v>59116.531544488</v>
       </c>
-      <c r="J14" s="25"/>
+      <c r="J14" s="28"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
@@ -48217,7 +48264,7 @@
         <f aca="false">H15</f>
         <v>15.4</v>
       </c>
-      <c r="J15" s="25"/>
+      <c r="J15" s="28"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
@@ -48255,21 +48302,21 @@
         <f aca="false">I14+I15</f>
         <v>59131.931544488</v>
       </c>
-      <c r="J16" s="25"/>
+      <c r="J16" s="28"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
         <v>646</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
@@ -48279,7 +48326,7 @@
         <f aca="false">Assumptions!$C$8</f>
         <v>1924.4</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>648</v>
       </c>
     </row>
@@ -48290,7 +48337,7 @@
       <c r="C20" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="25" t="s">
+      <c r="J20" s="28" t="s">
         <v>650</v>
       </c>
     </row>
@@ -48302,7 +48349,7 @@
         <f aca="false">C19+C20</f>
         <v>1924.4</v>
       </c>
-      <c r="J21" s="27" t="s">
+      <c r="J21" s="26" t="s">
         <v>652</v>
       </c>
     </row>
@@ -48410,7 +48457,7 @@
         <f aca="false">IS!I24</f>
         <v>19657.2745170265</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>656</v>
       </c>
     </row>
@@ -48438,7 +48485,7 @@
         <f aca="false">Assumptions!G$37</f>
         <v>0.1317</v>
       </c>
-      <c r="J5" s="25"/>
+      <c r="J5" s="28"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
@@ -48464,7 +48511,7 @@
         <f aca="false">I4*(1-I5)</f>
         <v>17068.4114631341</v>
       </c>
-      <c r="J6" s="25"/>
+      <c r="J6" s="28"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
@@ -48490,7 +48537,7 @@
         <f aca="false">PPE!I19</f>
         <v>2908.33675064901</v>
       </c>
-      <c r="J7" s="25"/>
+      <c r="J7" s="28"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
@@ -48516,7 +48563,7 @@
         <f aca="false">Schedules!I18</f>
         <v>1413.05607955134</v>
       </c>
-      <c r="J8" s="27" t="s">
+      <c r="J8" s="26" t="s">
         <v>661</v>
       </c>
     </row>
@@ -48544,7 +48591,7 @@
         <f aca="false">PPE!I14</f>
         <v>6605.84149994415</v>
       </c>
-      <c r="J9" s="25"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
@@ -48570,7 +48617,7 @@
         <f aca="false">I6+I7-I8-I9</f>
         <v>11957.8506342877</v>
       </c>
-      <c r="J10" s="25"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
@@ -48591,7 +48638,7 @@
       <c r="I11" s="55" t="n">
         <v>4.5</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>665</v>
       </c>
     </row>
@@ -48619,7 +48666,7 @@
         <f aca="false">1/(1+Assumptions!$C$87)^I11</f>
         <v>0.720284586543908</v>
       </c>
-      <c r="J12" s="25"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -48645,7 +48692,7 @@
         <f aca="false">I10*I12</f>
         <v>8613.05550007169</v>
       </c>
-      <c r="J13" s="25"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
@@ -48655,7 +48702,7 @@
         <f aca="false">SUM(E13:I13)</f>
         <v>23205.410741057</v>
       </c>
-      <c r="J15" s="25"/>
+      <c r="J15" s="28"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
@@ -48665,7 +48712,7 @@
         <f aca="false">I10*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)</f>
         <v>269881.326390667</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="28" t="s">
         <v>670</v>
       </c>
     </row>
@@ -48677,7 +48724,7 @@
         <f aca="false">D16*I12</f>
         <v>194391.359595223</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="28" t="s">
         <v>672</v>
       </c>
     </row>
@@ -48689,7 +48736,7 @@
         <f aca="false">D15+D17</f>
         <v>217596.77033628</v>
       </c>
-      <c r="J18" s="25"/>
+      <c r="J18" s="28"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
@@ -48699,7 +48746,7 @@
         <f aca="false">BS!D4</f>
         <v>2579.1</v>
       </c>
-      <c r="J19" s="25"/>
+      <c r="J19" s="28"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
@@ -48709,7 +48756,7 @@
         <f aca="false">BS!D5</f>
         <v>0</v>
       </c>
-      <c r="J20" s="25"/>
+      <c r="J20" s="28"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
@@ -48719,7 +48766,7 @@
         <f aca="false">BS!D18</f>
         <v>486.8</v>
       </c>
-      <c r="J21" s="27" t="s">
+      <c r="J21" s="26" t="s">
         <v>677</v>
       </c>
     </row>
@@ -48731,7 +48778,7 @@
         <f aca="false">-(BS!D22+BS!D28+BS!D31+BS!D32)</f>
         <v>-4567.5</v>
       </c>
-      <c r="J22" s="25"/>
+      <c r="J22" s="28"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
@@ -48741,7 +48788,7 @@
         <f aca="false">-BS!D44</f>
         <v>-15.4</v>
       </c>
-      <c r="J23" s="27" t="s">
+      <c r="J23" s="26" t="s">
         <v>680</v>
       </c>
     </row>
@@ -48753,7 +48800,7 @@
         <f aca="false">D19+D20+D21+D22+D23</f>
         <v>-1517</v>
       </c>
-      <c r="J24" s="25" t="s">
+      <c r="J24" s="28" t="s">
         <v>682</v>
       </c>
     </row>
@@ -48765,7 +48812,7 @@
         <f aca="false">D18+D24</f>
         <v>216079.77033628</v>
       </c>
-      <c r="J25" s="25"/>
+      <c r="J25" s="28"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
@@ -48775,7 +48822,7 @@
         <f aca="false">D25/Equity_Roll!$C$21</f>
         <v>112.284229025296</v>
       </c>
-      <c r="J26" s="25" t="s">
+      <c r="J26" s="28" t="s">
         <v>685</v>
       </c>
     </row>
@@ -48787,7 +48834,7 @@
         <f aca="false">Assumptions!$C$7</f>
         <v>123.53</v>
       </c>
-      <c r="J27" s="25"/>
+      <c r="J27" s="28"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
@@ -48797,7 +48844,7 @@
         <f aca="false">D26/D27-1</f>
         <v>-0.0910367600963644</v>
       </c>
-      <c r="J28" s="25"/>
+      <c r="J28" s="28"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
@@ -48807,7 +48854,7 @@
         <f aca="false">D25/IS!E20</f>
         <v>40.8277325177545</v>
       </c>
-      <c r="J29" s="25" t="s">
+      <c r="J29" s="28" t="s">
         <v>689</v>
       </c>
     </row>
@@ -48819,7 +48866,7 @@
         <f aca="false">D18/(IS!E24+PPE!E19)</f>
         <v>30.4180571612051</v>
       </c>
-      <c r="J30" s="25"/>
+      <c r="J30" s="28"/>
     </row>
     <row r="31" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
@@ -48939,7 +48986,7 @@
         <f aca="false">IS!I20</f>
         <v>17055.977813947</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>694</v>
       </c>
     </row>
@@ -48967,7 +49014,7 @@
         <f aca="false">PPE!I19</f>
         <v>2908.33675064901</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="28" t="s">
         <v>695</v>
       </c>
     </row>
@@ -48995,7 +49042,7 @@
         <f aca="false">Schedules!I18</f>
         <v>1413.05607955134</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>696</v>
       </c>
     </row>
@@ -49023,7 +49070,7 @@
         <f aca="false">PPE!I14</f>
         <v>6605.84149994415</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>697</v>
       </c>
     </row>
@@ -49051,7 +49098,7 @@
         <f aca="false">FIN!I57</f>
         <v>-102.2</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>699</v>
       </c>
     </row>
@@ -49079,7 +49126,7 @@
         <f aca="false">-FIN!I62</f>
         <v>-7389.28634906777</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>701</v>
       </c>
     </row>
@@ -49107,7 +49154,7 @@
         <f aca="false">I4+I5-I6-I7+I8</f>
         <v>11843.2169851005</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>703</v>
       </c>
     </row>
@@ -49130,7 +49177,7 @@
       <c r="I11" s="55" t="n">
         <v>4.5</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>704</v>
       </c>
     </row>
@@ -49158,7 +49205,7 @@
         <f aca="false">1/(1+KE)^I11</f>
         <v>0.717620678364625</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>706</v>
       </c>
     </row>
@@ -49186,7 +49233,7 @@
         <f aca="false">I10*I12</f>
         <v>8498.93740686729</v>
       </c>
-      <c r="J13" s="25"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
@@ -49196,7 +49243,7 @@
         <f aca="false">SUM(E13:I13)</f>
         <v>18814.2998732006</v>
       </c>
-      <c r="J15" s="25"/>
+      <c r="J15" s="28"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
@@ -49206,7 +49253,7 @@
         <f aca="false">I10-I8+FIN!I56*TERM_G</f>
         <v>11945.4199851005</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="28" t="s">
         <v>709</v>
       </c>
     </row>
@@ -49218,7 +49265,7 @@
         <f aca="false">D16*(1+TERM_G)/(KE-TERM_G)</f>
         <v>264466.203054698</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="28" t="s">
         <v>711</v>
       </c>
     </row>
@@ -49230,7 +49277,7 @@
         <f aca="false">D17*I12</f>
         <v>189786.416040629</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>712</v>
       </c>
     </row>
@@ -49242,7 +49289,7 @@
         <f aca="false">D15+D18</f>
         <v>208600.715913829</v>
       </c>
-      <c r="J19" s="27" t="s">
+      <c r="J19" s="26" t="s">
         <v>714</v>
       </c>
     </row>
@@ -49254,7 +49301,7 @@
         <f aca="false">D19/SHARES_DIL</f>
         <v>108.397794592512</v>
       </c>
-      <c r="J20" s="25" t="s">
+      <c r="J20" s="28" t="s">
         <v>715</v>
       </c>
     </row>
@@ -49266,7 +49313,7 @@
         <f aca="false">DCF!D26</f>
         <v>112.284229025296</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="J21" s="28" t="s">
         <v>717</v>
       </c>
     </row>
@@ -49278,7 +49325,7 @@
         <f aca="false">D20/D21-1</f>
         <v>-0.0346124693246895</v>
       </c>
-      <c r="J22" s="27" t="s">
+      <c r="J22" s="26" t="s">
         <v>719</v>
       </c>
     </row>
@@ -49290,7 +49337,7 @@
         <f aca="false">IF(""&lt;&gt;"","WAIVED: ",IF(ABS(D22)&gt;=0.3,"警告: 差异≥30%, 复核债务调度/资本结构/终值","通过: 差异&lt;30%"))</f>
         <v>通过: 差异&lt;30%</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>720</v>
       </c>
     </row>
@@ -49647,17 +49694,11 @@
       <c r="A9" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="F9" s="60" t="n">
-        <f aca="false">MEDIAN(F5,F7)</f>
-        <v>42.4241238566262</v>
-      </c>
-      <c r="H9" s="60" t="n">
-        <f aca="false">MEDIAN(H5,H7)</f>
-        <v>29.7754378332788</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <f aca="false">MEDIAN(J5,J7)</f>
-        <v>1.09076437039506</v>
+      <c r="H9" s="60" t="s">
+        <v>262</v>
+      </c>
+      <c r="J9" s="60" t="s">
+        <v>262</v>
       </c>
       <c r="K9" s="22" t="s">
         <v>753</v>
@@ -49685,7 +49726,7 @@
         <f aca="false">Assumptions!$C$13/100</f>
         <v>57.402</v>
       </c>
-      <c r="F10" s="60" t="n">
+      <c r="F10" s="62" t="n">
         <f aca="false">C10/E10</f>
         <v>41.41338838368</v>
       </c>
@@ -49702,32 +49743,32 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="25" t="s">
         <v>757</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="C13" s="62" t="n">
+      <c r="C13" s="63" t="n">
         <v>30</v>
       </c>
-      <c r="K13" s="25" t="s">
+      <c r="K13" s="28" t="s">
         <v>759</v>
       </c>
     </row>
@@ -49736,10 +49777,10 @@
         <v>760</v>
       </c>
       <c r="C14" s="57" t="n">
-        <f aca="false">F9</f>
-        <v>42.4241238566262</v>
-      </c>
-      <c r="K14" s="25" t="s">
+        <f aca="false">C13</f>
+        <v>30</v>
+      </c>
+      <c r="K14" s="28" t="s">
         <v>761</v>
       </c>
     </row>
@@ -49767,7 +49808,7 @@
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">C14*C15/Equity_Roll!$C$21</f>
-        <v>116.674616628378</v>
+        <v>82.5058523466625</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49780,9 +49821,9 @@
       </c>
       <c r="D18" s="8" t="n">
         <f aca="false">C14*Assumptions!$C$13/Equity_Roll!$C$21</f>
-        <v>126.544874122743</v>
-      </c>
-      <c r="K18" s="25" t="s">
+        <v>89.48555393889</v>
+      </c>
+      <c r="K18" s="28" t="s">
         <v>766</v>
       </c>
     </row>
@@ -49796,7 +49837,7 @@
       </c>
       <c r="D19" s="19" t="n">
         <f aca="false">C17/Assumptions!$C$7-1</f>
-        <v>-0.0554956963621994</v>
+        <v>-0.332098661485773</v>
       </c>
     </row>
   </sheetData>
@@ -49857,17 +49898,17 @@
       <c r="J2" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>770</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
@@ -49959,7 +50000,7 @@
         <f aca="false">(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+D$5)/($B8-D$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v>101.867969588153</v>
       </c>
-      <c r="E8" s="63" t="n">
+      <c r="E8" s="64" t="n">
         <f aca="false">(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+E$5)/($B8-E$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v>112.284229025296</v>
       </c>
@@ -50025,48 +50066,48 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="28" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>773</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="37" t="s">
         <v>774</v>
       </c>
-      <c r="C14" s="64" t="n">
+      <c r="C14" s="65" t="n">
         <v>25</v>
       </c>
-      <c r="D14" s="64" t="n">
+      <c r="D14" s="65" t="n">
         <v>30</v>
       </c>
-      <c r="E14" s="64" t="n">
+      <c r="E14" s="65" t="n">
         <v>35</v>
       </c>
-      <c r="F14" s="64" t="n">
+      <c r="F14" s="65" t="n">
         <v>40</v>
       </c>
-      <c r="G14" s="64" t="n">
+      <c r="G14" s="65" t="n">
         <v>45</v>
       </c>
-      <c r="H14" s="64" t="n">
+      <c r="H14" s="65" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="65" t="n">
+      <c r="B15" s="66" t="n">
         <v>0.2</v>
       </c>
       <c r="C15" s="8" t="n">
@@ -50095,7 +50136,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="65" t="n">
+      <c r="B16" s="66" t="n">
         <v>0.35</v>
       </c>
       <c r="C16" s="8" t="n">
@@ -50124,7 +50165,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="65" t="n">
+      <c r="B17" s="66" t="n">
         <v>0.5</v>
       </c>
       <c r="C17" s="8" t="n">
@@ -50139,7 +50180,7 @@
         <f aca="false">IS!$D$20*(1+$B17)*E$14/Equity_Roll!$C$21</f>
         <v>104.277047391395</v>
       </c>
-      <c r="F17" s="63" t="n">
+      <c r="F17" s="64" t="n">
         <f aca="false">IS!$D$20*(1+$B17)*F$14/Equity_Roll!$C$21</f>
         <v>119.173768447308</v>
       </c>
@@ -50153,7 +50194,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="65" t="n">
+      <c r="B18" s="66" t="n">
         <v>0.65</v>
       </c>
       <c r="C18" s="8" t="n">
@@ -50182,7 +50223,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="65" t="n">
+      <c r="B19" s="66" t="n">
         <v>0.8</v>
       </c>
       <c r="C19" s="8" t="n">
@@ -50211,22 +50252,22 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="28" t="s">
         <v>775</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="25" t="s">
         <v>776</v>
       </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
@@ -50243,7 +50284,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="66" t="n">
+      <c r="B24" s="67" t="n">
         <v>-40</v>
       </c>
       <c r="C24" s="8" t="n">
@@ -50256,7 +50297,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="66" t="n">
+      <c r="B25" s="67" t="n">
         <v>-20</v>
       </c>
       <c r="C25" s="8" t="n">
@@ -50269,10 +50310,10 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="66" t="n">
+      <c r="B26" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="63" t="n">
+      <c r="C26" s="64" t="n">
         <f aca="false">((DCF!E$10+$B26/365*(IS!E$6))/(1+Assumptions!$C$87)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$87)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$87)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$87)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$87)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)/(1+Assumptions!$C$87)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v>112.284229025296</v>
       </c>
@@ -50282,7 +50323,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="66" t="n">
+      <c r="B27" s="67" t="n">
         <v>20</v>
       </c>
       <c r="C27" s="8" t="n">
@@ -50295,7 +50336,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="66" t="n">
+      <c r="B28" s="67" t="n">
         <v>40</v>
       </c>
       <c r="C28" s="8" t="n">
@@ -50308,7 +50349,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="26" t="s">
         <v>781</v>
       </c>
     </row>
@@ -50375,15 +50416,15 @@
       <c r="A3" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="B3" s="67" t="n">
+      <c r="B3" s="68" t="n">
         <f aca="false">Assumptions!$C$5</f>
         <v>2</v>
       </c>
-      <c r="C3" s="68" t="str">
+      <c r="C3" s="69" t="str">
         <f aca="false">CHOOSE(B3,"熊市","基准","牛市")</f>
         <v>基准</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="28" t="s">
         <v>785</v>
       </c>
     </row>
@@ -50395,23 +50436,23 @@
         <f aca="false">Schedules!E17/IS!E4</f>
         <v>0.123070501571818</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>788</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
@@ -50541,7 +50582,7 @@
         <f aca="false">(E11/(1+Assumptions!$C$87)^0.5+F11/(1+Assumptions!$C$87)^1.5+G11/(1+Assumptions!$C$87)^2.5+H11/(1+Assumptions!$C$87)^3.5+I11/(1+Assumptions!$C$87)^4.5+I11*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)/(1+Assumptions!$C$87)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v>43.6203931318112</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>792</v>
       </c>
     </row>
@@ -50550,26 +50591,26 @@
         <v>793</v>
       </c>
       <c r="B13" s="23" t="n">
-        <f aca="false">E10*Relative_Val!$F$9/Equity_Roll!$C$21</f>
-        <v>97.7240197223826</v>
-      </c>
-      <c r="J13" s="25" t="s">
+        <f aca="false">E10*Relative_Val!$C$13/Equity_Roll!$C$21</f>
+        <v>69.1050356532836</v>
+      </c>
+      <c r="J13" s="28" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="25" t="s">
         <v>795</v>
       </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
@@ -50699,7 +50740,7 @@
         <f aca="false">(E20/(1+Assumptions!$C$87)^0.5+F20/(1+Assumptions!$C$87)^1.5+G20/(1+Assumptions!$C$87)^2.5+H20/(1+Assumptions!$C$87)^3.5+I20/(1+Assumptions!$C$87)^4.5+I20*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)/(1+Assumptions!$C$87)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v>116.874916607451</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="J21" s="28" t="s">
         <v>792</v>
       </c>
     </row>
@@ -50708,26 +50749,26 @@
         <v>793</v>
       </c>
       <c r="B22" s="23" t="n">
-        <f aca="false">E19*Relative_Val!$F$9/Equity_Roll!$C$21</f>
-        <v>124.664373491692</v>
-      </c>
-      <c r="J22" s="25" t="s">
+        <f aca="false">E19*Relative_Val!$C$13/Equity_Roll!$C$21</f>
+        <v>88.1557676332925</v>
+      </c>
+      <c r="J22" s="28" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="25" t="s">
         <v>796</v>
       </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
@@ -50857,7 +50898,7 @@
         <f aca="false">(E29/(1+Assumptions!$C$87)^0.5+F29/(1+Assumptions!$C$87)^1.5+G29/(1+Assumptions!$C$87)^2.5+H29/(1+Assumptions!$C$87)^3.5+I29/(1+Assumptions!$C$87)^4.5+I29*(1+Assumptions!$C$88)/(Assumptions!$C$87-Assumptions!$C$88)/(1+Assumptions!$C$87)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v>188.004916194419</v>
       </c>
-      <c r="J30" s="25" t="s">
+      <c r="J30" s="28" t="s">
         <v>792</v>
       </c>
     </row>
@@ -50866,26 +50907,26 @@
         <v>793</v>
       </c>
       <c r="B31" s="23" t="n">
-        <f aca="false">E28*Relative_Val!$F$9/Equity_Roll!$C$21</f>
-        <v>141.740996825468</v>
-      </c>
-      <c r="J31" s="25" t="s">
+        <f aca="false">E28*Relative_Val!$C$13/Equity_Roll!$C$21</f>
+        <v>100.231413597004</v>
+      </c>
+      <c r="J31" s="28" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="25" t="s">
         <v>797</v>
       </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
@@ -50895,7 +50936,7 @@
         <f aca="false">DCF!D26</f>
         <v>112.284229025296</v>
       </c>
-      <c r="J34" s="25" t="s">
+      <c r="J34" s="28" t="s">
         <v>799</v>
       </c>
     </row>
@@ -50916,7 +50957,7 @@
         <f aca="false">B34/B21</f>
         <v>0.960721361645341</v>
       </c>
-      <c r="J36" s="25" t="s">
+      <c r="J36" s="28" t="s">
         <v>802</v>
       </c>
     </row>
@@ -50924,24 +50965,24 @@
       <c r="A37" s="5" t="s">
         <v>803</v>
       </c>
-      <c r="B37" s="69" t="str">
+      <c r="B37" s="70" t="str">
         <f aca="false">IF(ABS(B36-1)&gt;=0.3,"警告: 桥接差异≥30%, 复核简化假设","通过: 桥接差异&lt;30%")</f>
         <v>通过: 桥接差异&lt;30%</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="25" t="s">
         <v>804</v>
       </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
@@ -51008,15 +51049,15 @@
       </c>
       <c r="B42" s="8" t="n">
         <f aca="false">B13</f>
-        <v>97.7240197223826</v>
+        <v>69.1050356532836</v>
       </c>
       <c r="C42" s="8" t="n">
         <f aca="false">B22</f>
-        <v>124.664373491692</v>
+        <v>88.1557676332925</v>
       </c>
       <c r="D42" s="8" t="n">
         <f aca="false">B31</f>
-        <v>141.740996825468</v>
+        <v>100.231413597004</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51133,39 +51174,39 @@
       <c r="A4" s="4" t="s">
         <v>819</v>
       </c>
-      <c r="B4" s="70" t="b">
+      <c r="B4" s="71" t="b">
         <f aca="false">ABS(BS!B47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="C4" s="70" t="b">
+      <c r="C4" s="71" t="b">
         <f aca="false">ABS(BS!C47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="D4" s="70" t="b">
+      <c r="D4" s="71" t="b">
         <f aca="false">ABS(BS!D47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="E4" s="70" t="b">
+      <c r="E4" s="71" t="b">
         <f aca="false">ABS(BS!E47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="F4" s="70" t="b">
+      <c r="F4" s="71" t="b">
         <f aca="false">ABS(BS!F47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="G4" s="70" t="b">
+      <c r="G4" s="71" t="b">
         <f aca="false">ABS(BS!G47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="H4" s="70" t="b">
+      <c r="H4" s="71" t="b">
         <f aca="false">ABS(BS!H47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="I4" s="70" t="b">
+      <c r="I4" s="71" t="b">
         <f aca="false">ABS(BS!I47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>820</v>
       </c>
     </row>
@@ -51173,27 +51214,27 @@
       <c r="A5" s="4" t="s">
         <v>821</v>
       </c>
-      <c r="E5" s="70" t="b">
+      <c r="E5" s="71" t="b">
         <f aca="false">ABS(CF!E19-BS!E4)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="F5" s="70" t="b">
+      <c r="F5" s="71" t="b">
         <f aca="false">ABS(CF!F19-BS!F4)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="G5" s="70" t="b">
+      <c r="G5" s="71" t="b">
         <f aca="false">ABS(CF!G19-BS!G4)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="H5" s="70" t="b">
+      <c r="H5" s="71" t="b">
         <f aca="false">ABS(CF!H19-BS!H4)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="I5" s="70" t="b">
+      <c r="I5" s="71" t="b">
         <f aca="false">ABS(CF!I19-BS!I4)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="28" t="s">
         <v>822</v>
       </c>
     </row>
@@ -51201,27 +51242,27 @@
       <c r="A6" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="E6" s="70" t="b">
+      <c r="E6" s="71" t="b">
         <f aca="false">ABS(BS!E41-BS!D41-IS!E20+Schedules!E26+Equity_Roll!E9)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="F6" s="70" t="b">
+      <c r="F6" s="71" t="b">
         <f aca="false">ABS(BS!F41-BS!E41-IS!F20+Schedules!F26+Equity_Roll!F9)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="G6" s="70" t="b">
+      <c r="G6" s="71" t="b">
         <f aca="false">ABS(BS!G41-BS!F41-IS!G20+Schedules!G26+Equity_Roll!G9)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="H6" s="70" t="b">
+      <c r="H6" s="71" t="b">
         <f aca="false">ABS(BS!H41-BS!G41-IS!H20+Schedules!H26+Equity_Roll!H9)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="I6" s="70" t="b">
+      <c r="I6" s="71" t="b">
         <f aca="false">ABS(BS!I41-BS!H41-IS!I20+Schedules!I26+Equity_Roll!I9)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="26" t="s">
         <v>824</v>
       </c>
     </row>
@@ -51229,39 +51270,39 @@
       <c r="A7" s="4" t="s">
         <v>825</v>
       </c>
-      <c r="B7" s="70" t="b">
+      <c r="B7" s="71" t="b">
         <f aca="false">ABS(IS!B4-Revenue_Segments!B20)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="C7" s="70" t="b">
+      <c r="C7" s="71" t="b">
         <f aca="false">ABS(IS!C4-Revenue_Segments!C20)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="D7" s="70" t="b">
+      <c r="D7" s="71" t="b">
         <f aca="false">ABS(IS!D4-Revenue_Segments!D20)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="E7" s="70" t="b">
+      <c r="E7" s="71" t="b">
         <f aca="false">ABS(IS!E4-Revenue_Segments!E20)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="F7" s="70" t="b">
+      <c r="F7" s="71" t="b">
         <f aca="false">ABS(IS!F4-Revenue_Segments!F20)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="G7" s="70" t="b">
+      <c r="G7" s="71" t="b">
         <f aca="false">ABS(IS!G4-Revenue_Segments!G20)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="H7" s="70" t="b">
+      <c r="H7" s="71" t="b">
         <f aca="false">ABS(IS!H4-Revenue_Segments!H20)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="I7" s="70" t="b">
+      <c r="I7" s="71" t="b">
         <f aca="false">ABS(IS!I4-Revenue_Segments!I20)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>826</v>
       </c>
     </row>
@@ -51269,39 +51310,39 @@
       <c r="A8" s="4" t="s">
         <v>827</v>
       </c>
-      <c r="B8" s="70" t="b">
+      <c r="B8" s="71" t="b">
         <f aca="false">AND(IS!B8&gt;0,IS!B8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="C8" s="70" t="b">
+      <c r="C8" s="71" t="b">
         <f aca="false">AND(IS!C8&gt;0,IS!C8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="D8" s="70" t="b">
+      <c r="D8" s="71" t="b">
         <f aca="false">AND(IS!D8&gt;0,IS!D8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="E8" s="70" t="b">
+      <c r="E8" s="71" t="b">
         <f aca="false">AND(IS!E8&gt;0,IS!E8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="F8" s="70" t="b">
+      <c r="F8" s="71" t="b">
         <f aca="false">AND(IS!F8&gt;0,IS!F8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="G8" s="70" t="b">
+      <c r="G8" s="71" t="b">
         <f aca="false">AND(IS!G8&gt;0,IS!G8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="H8" s="70" t="b">
+      <c r="H8" s="71" t="b">
         <f aca="false">AND(IS!H8&gt;0,IS!H8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="I8" s="70" t="b">
+      <c r="I8" s="71" t="b">
         <f aca="false">AND(IS!I8&gt;0,IS!I8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>828</v>
       </c>
     </row>
@@ -51309,11 +51350,11 @@
       <c r="A9" s="4" t="s">
         <v>829</v>
       </c>
-      <c r="B9" s="70" t="b">
+      <c r="B9" s="71" t="b">
         <f aca="false">DCF!D26&gt;0</f>
         <v>1</v>
       </c>
-      <c r="J9" s="27" t="s">
+      <c r="J9" s="26" t="s">
         <v>830</v>
       </c>
     </row>
@@ -51321,11 +51362,11 @@
       <c r="A10" s="4" t="s">
         <v>831</v>
       </c>
-      <c r="B10" s="70" t="b">
+      <c r="B10" s="71" t="b">
         <f aca="false">ABS(Sensitivity!E8-DCF!D26)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>832</v>
       </c>
     </row>
@@ -51333,11 +51374,11 @@
       <c r="A11" s="4" t="s">
         <v>833</v>
       </c>
-      <c r="B11" s="70" t="b">
+      <c r="B11" s="71" t="b">
         <f aca="false">OR(ABS(Assumptions!C87-Assumptions!C85)&lt;0.000001,Assumptions!C86&lt;&gt;"")</f>
         <v>1</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>834</v>
       </c>
     </row>
@@ -51345,27 +51386,27 @@
       <c r="A12" s="4" t="s">
         <v>835</v>
       </c>
-      <c r="E12" s="70" t="b">
+      <c r="E12" s="71" t="b">
         <f aca="false">BS!E4&gt;0.01</f>
         <v>1</v>
       </c>
-      <c r="F12" s="70" t="b">
+      <c r="F12" s="71" t="b">
         <f aca="false">BS!F4&gt;0.01</f>
         <v>1</v>
       </c>
-      <c r="G12" s="70" t="b">
+      <c r="G12" s="71" t="b">
         <f aca="false">BS!G4&gt;0.01</f>
         <v>1</v>
       </c>
-      <c r="H12" s="70" t="b">
+      <c r="H12" s="71" t="b">
         <f aca="false">BS!H4&gt;0.01</f>
         <v>1</v>
       </c>
-      <c r="I12" s="70" t="b">
+      <c r="I12" s="71" t="b">
         <f aca="false">BS!I4&gt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J12" s="27" t="s">
+      <c r="J12" s="26" t="s">
         <v>836</v>
       </c>
     </row>
@@ -51373,27 +51414,27 @@
       <c r="A13" s="4" t="s">
         <v>837</v>
       </c>
-      <c r="E13" s="70" t="b">
+      <c r="E13" s="71" t="b">
         <f aca="false">MIN(FIN!E24,FIN!E32,FIN!E42,FIN!E50)&gt;=-0.01</f>
         <v>1</v>
       </c>
-      <c r="F13" s="70" t="b">
+      <c r="F13" s="71" t="b">
         <f aca="false">MIN(FIN!F24,FIN!F32,FIN!F42,FIN!F50)&gt;=-0.01</f>
         <v>1</v>
       </c>
-      <c r="G13" s="70" t="b">
+      <c r="G13" s="71" t="b">
         <f aca="false">MIN(FIN!G24,FIN!G32,FIN!G42,FIN!G50)&gt;=-0.01</f>
         <v>1</v>
       </c>
-      <c r="H13" s="70" t="b">
+      <c r="H13" s="71" t="b">
         <f aca="false">MIN(FIN!H24,FIN!H32,FIN!H42,FIN!H50)&gt;=-0.01</f>
         <v>1</v>
       </c>
-      <c r="I13" s="70" t="b">
+      <c r="I13" s="71" t="b">
         <f aca="false">MIN(FIN!I24,FIN!I32,FIN!I42,FIN!I50)&gt;=-0.01</f>
         <v>1</v>
       </c>
-      <c r="J13" s="27" t="s">
+      <c r="J13" s="26" t="s">
         <v>838</v>
       </c>
     </row>
@@ -51401,27 +51442,27 @@
       <c r="A14" s="4" t="s">
         <v>839</v>
       </c>
-      <c r="E14" s="70" t="b">
+      <c r="E14" s="71" t="b">
         <f aca="false">FIN!E139&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="F14" s="70" t="b">
+      <c r="F14" s="71" t="b">
         <f aca="false">FIN!F139&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="G14" s="70" t="b">
+      <c r="G14" s="71" t="b">
         <f aca="false">FIN!G139&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="H14" s="70" t="b">
+      <c r="H14" s="71" t="b">
         <f aca="false">FIN!H139&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="I14" s="70" t="b">
+      <c r="I14" s="71" t="b">
         <f aca="false">FIN!I139&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>840</v>
       </c>
     </row>
@@ -51429,11 +51470,11 @@
       <c r="A15" s="4" t="s">
         <v>841</v>
       </c>
-      <c r="B15" s="70" t="b">
+      <c r="B15" s="71" t="b">
         <f aca="true">AND(ISNUMBER(INDIRECT("SCEN_SWITCH")),ISNUMBER(INDIRECT("WACC_USED")),ISNUMBER(INDIRECT("WACC_CALC")),ISNUMBER(INDIRECT("TERM_G")),ISNUMBER(INDIRECT("KE")),ISNUMBER(INDIRECT("KD")),ISNUMBER(INDIRECT("RF_RATE")),ISNUMBER(INDIRECT("ERP")),ISNUMBER(INDIRECT("BETA_U")),ISNUMBER(INDIRECT("TAX_RATE_Y1")),ISNUMBER(INDIRECT("PAYOUT_Y1")),ISNUMBER(INDIRECT("MIN_CASH_PCT")),ISNUMBER(INDIRECT("SHARES_DIL")),ISNUMBER(INDIRECT("DCF_PS")),ISNUMBER(INDIRECT("FCFE_PS")))</f>
         <v>1</v>
       </c>
-      <c r="J15" s="27" t="s">
+      <c r="J15" s="26" t="s">
         <v>842</v>
       </c>
     </row>
@@ -51441,11 +51482,11 @@
       <c r="A16" s="4" t="s">
         <v>843</v>
       </c>
-      <c r="B16" s="70" t="b">
+      <c r="B16" s="71" t="b">
         <f aca="false">AND(Scenarios!B12&lt;=Scenarios!B21,Scenarios!B21&lt;=Scenarios!B30,Scenarios!B13&lt;=Scenarios!B22,Scenarios!B22&lt;=Scenarios!B31)</f>
         <v>1</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="28" t="s">
         <v>844</v>
       </c>
     </row>
@@ -51453,27 +51494,27 @@
       <c r="A18" s="5" t="s">
         <v>845</v>
       </c>
-      <c r="E18" s="71" t="n">
+      <c r="E18" s="72" t="n">
         <f aca="false">PPE!E20</f>
         <v>0.156257545247598</v>
       </c>
-      <c r="F18" s="71" t="n">
+      <c r="F18" s="72" t="n">
         <f aca="false">PPE!F20</f>
         <v>0.14159719985681</v>
       </c>
-      <c r="G18" s="71" t="n">
+      <c r="G18" s="72" t="n">
         <f aca="false">PPE!G20</f>
         <v>0.137611111382918</v>
       </c>
-      <c r="H18" s="71" t="n">
+      <c r="H18" s="72" t="n">
         <f aca="false">PPE!H20</f>
         <v>0.134833166821334</v>
       </c>
-      <c r="I18" s="71" t="n">
+      <c r="I18" s="72" t="n">
         <f aca="false">PPE!I20</f>
         <v>0.132095216400224</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>846</v>
       </c>
     </row>
@@ -51485,7 +51526,7 @@
         <f aca="false">IS!E4/Assumptions!$C$12</f>
         <v>0.996200803241469</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>848</v>
       </c>
     </row>
@@ -51510,7 +51551,7 @@
         <f aca="false">Assumptions!C87</f>
         <v>0.0756370446893662</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="J21" s="28" t="s">
         <v>851</v>
       </c>
     </row>
@@ -51526,7 +51567,7 @@
         <f aca="false">FCFE!D20</f>
         <v>108.397794592512</v>
       </c>
-      <c r="J22" s="25" t="s">
+      <c r="J22" s="28" t="s">
         <v>853</v>
       </c>
     </row>
@@ -51534,11 +51575,11 @@
       <c r="A23" s="5" t="s">
         <v>854</v>
       </c>
-      <c r="B23" s="69" t="str">
+      <c r="B23" s="70" t="str">
         <f aca="false">IF(""&lt;&gt;"","WAIVED: ",IF(ABS(FCFE!D22)&gt;=0.3,"警告: 差异≥30%, 复核债务调度/资本结构/终值","通过: 差异&lt;30%"))</f>
         <v>通过: 差异&lt;30%</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>855</v>
       </c>
     </row>
@@ -51554,7 +51595,7 @@
         <f aca="false">Scenarios!B34</f>
         <v>112.284229025296</v>
       </c>
-      <c r="J24" s="25" t="s">
+      <c r="J24" s="28" t="s">
         <v>857</v>
       </c>
     </row>
@@ -51562,11 +51603,11 @@
       <c r="A25" s="5" t="s">
         <v>858</v>
       </c>
-      <c r="B25" s="69" t="str">
+      <c r="B25" s="70" t="str">
         <f aca="false">IF(ABS(Scenarios!B36-1)&gt;=0.3,"警告: 桥接差异≥30%, 复核简化假设","通过: 桥接差异&lt;30%")</f>
         <v>通过: 桥接差异&lt;30%</v>
       </c>
-      <c r="J25" s="25" t="s">
+      <c r="J25" s="28" t="s">
         <v>859</v>
       </c>
     </row>
@@ -51582,24 +51623,24 @@
         <f aca="false">FIN!I13</f>
         <v>1565.36528434696</v>
       </c>
-      <c r="J26" s="25" t="s">
+      <c r="J26" s="28" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="73" t="s">
         <v>862</v>
       </c>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73" t="str">
+      <c r="B28" s="73"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74" t="str">
         <f aca="false">IF(AND(B4:I4,E5:I5,E6:I6,B7:I7,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15,B16),"全部通过=TRUE","存在未通过=FALSE")</f>
         <v>全部通过=TRUE</v>
       </c>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
@@ -51636,7 +51677,7 @@
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="10.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="36.39"/>
   </cols>
@@ -51809,15 +51850,15 @@
       </c>
       <c r="D9" s="8" t="n">
         <f aca="false">Relative_Val!C17</f>
-        <v>116.674616628378</v>
+        <v>82.5058523466625</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">(C9+D9)/2</f>
-        <v>99.59023448752</v>
+        <v>82.5058523466625</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">E9/Assumptions!$C$7-1</f>
-        <v>-0.193797178923986</v>
+        <v>-0.332098661485773</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>61</v>
@@ -51836,15 +51877,15 @@
       </c>
       <c r="D10" s="8" t="n">
         <f aca="false">Relative_Val!D18</f>
-        <v>126.544874122743</v>
+        <v>89.48555393889</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">(C10+D10)/2</f>
-        <v>108.015214030816</v>
+        <v>89.48555393889</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">E10/Assumptions!$C$7-1</f>
-        <v>-0.125595288344399</v>
+        <v>-0.275596584320489</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>63</v>
@@ -51894,7 +51935,7 @@
         <v>123.53</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>68</v>
       </c>
@@ -51914,21 +51955,21 @@
         <f aca="false">E13/Assumptions!$C$7-1</f>
         <v>-0.0624734504726382</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="20" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
@@ -51939,102 +51980,102 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="28" t="str">
+      <c r="B17" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D5-C5)/10,0)))&amp;"  ["&amp;TEXT(C5,"0")&amp;"—"&amp;TEXT(D5,"0")&amp;"]"</f>
         <v>▮  [112—112]</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="28" t="str">
+      <c r="B18" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D6-C6)/10,0)))&amp;"  ["&amp;TEXT(C6,"0")&amp;"—"&amp;TEXT(D6,"0")&amp;"]"</f>
         <v>▮  [44—44]</v>
       </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="28" t="str">
+      <c r="B19" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D7-C7)/10,0)))&amp;"  ["&amp;TEXT(C7,"0")&amp;"—"&amp;TEXT(D7,"0")&amp;"]"</f>
         <v>▮  [117—117]</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="28" t="str">
+      <c r="B20" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D8-C8)/10,0)))&amp;"  ["&amp;TEXT(C8,"0")&amp;"—"&amp;TEXT(D8,"0")&amp;"]"</f>
         <v>▮  [188—188]</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="28" t="str">
+      <c r="B21" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D9-C9)/10,0)))&amp;"  ["&amp;TEXT(C9,"0")&amp;"—"&amp;TEXT(D9,"0")&amp;"]"</f>
-        <v>▮▮▮  [83—117]</v>
-      </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
+        <v>▮  [83—83]</v>
+      </c>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="28" t="str">
+      <c r="B22" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D10-C10)/10,0)))&amp;"  ["&amp;TEXT(C10,"0")&amp;"—"&amp;TEXT(D10,"0")&amp;"]"</f>
-        <v>▮▮▮▮  [89—127]</v>
-      </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
+        <v>▮  [89—89]</v>
+      </c>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="28" t="str">
+      <c r="B23" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D11-C11)/10,0)))&amp;"  ["&amp;TEXT(C11,"0")&amp;"—"&amp;TEXT(D11,"0")&amp;"]"</f>
         <v>▮  [108—108]</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
@@ -52146,18 +52187,18 @@
       <c r="J2" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
@@ -52180,7 +52221,7 @@
       <c r="C6" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="28" t="s">
         <v>92</v>
       </c>
     </row>
@@ -52223,23 +52264,23 @@
         <f aca="false">C7*C8</f>
         <v>237721.132</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
@@ -52354,18 +52395,18 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
@@ -52443,18 +52484,18 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
@@ -52509,18 +52550,18 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
@@ -52745,18 +52786,18 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="25"/>
+      <c r="J41" s="25"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
@@ -52915,18 +52956,18 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="26" t="s">
+      <c r="A49" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="25"/>
+      <c r="I49" s="25"/>
+      <c r="J49" s="25"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
@@ -53025,18 +53066,18 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="26" t="s">
+      <c r="A57" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="26"/>
-      <c r="J57" s="26"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="25"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
@@ -53079,18 +53120,18 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
@@ -53304,23 +53345,23 @@
       <c r="C73" s="36" t="n">
         <v>4567.5</v>
       </c>
-      <c r="H73" s="25" t="s">
+      <c r="H73" s="28" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="26" t="s">
+      <c r="A75" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
-      <c r="D75" s="26"/>
-      <c r="E75" s="26"/>
-      <c r="F75" s="26"/>
-      <c r="G75" s="26"/>
-      <c r="H75" s="26"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="26"/>
+      <c r="B75" s="25"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="25"/>
+      <c r="I75" s="25"/>
+      <c r="J75" s="25"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
@@ -53361,7 +53402,7 @@
         <f aca="false">Relative_Val!$O$9</f>
         <v>1.010828480948</v>
       </c>
-      <c r="H78" s="25" t="s">
+      <c r="H78" s="28" t="s">
         <v>216</v>
       </c>
     </row>
@@ -53376,7 +53417,7 @@
         <f aca="false">C73/(C73+C9)</f>
         <v>0.0188514828875669</v>
       </c>
-      <c r="H79" s="25" t="s">
+      <c r="H79" s="28" t="s">
         <v>218</v>
       </c>
     </row>
@@ -53391,7 +53432,7 @@
         <f aca="false">C79/(1-C79)</f>
         <v>0.0192136894249688</v>
       </c>
-      <c r="H80" s="27" t="s">
+      <c r="H80" s="26" t="s">
         <v>220</v>
       </c>
     </row>
@@ -53406,7 +53447,7 @@
         <f aca="false">C78*(1+(1-C37)*C80)</f>
         <v>1.02769238169288</v>
       </c>
-      <c r="H81" s="27" t="s">
+      <c r="H81" s="26" t="s">
         <v>222</v>
       </c>
     </row>
@@ -53435,7 +53476,7 @@
         <f aca="false">C76+C81*C77+C82</f>
         <v>0.0765230809931084</v>
       </c>
-      <c r="H83" s="27" t="s">
+      <c r="H83" s="26" t="s">
         <v>226</v>
       </c>
     </row>
@@ -53464,7 +53505,7 @@
         <f aca="false">(1-C79)*C83+C79*C84*(1-C37)</f>
         <v>0.0756370446893662</v>
       </c>
-      <c r="H85" s="25" t="s">
+      <c r="H85" s="28" t="s">
         <v>230</v>
       </c>
     </row>
@@ -53476,7 +53517,7 @@
         <v>124</v>
       </c>
       <c r="C86" s="38"/>
-      <c r="H86" s="25" t="s">
+      <c r="H86" s="28" t="s">
         <v>232</v>
       </c>
     </row>
@@ -53491,7 +53532,7 @@
         <f aca="false">IF(C86="",C85,C86)</f>
         <v>0.0756370446893662</v>
       </c>
-      <c r="H87" s="25" t="s">
+      <c r="H87" s="28" t="s">
         <v>234</v>
       </c>
     </row>
@@ -53510,18 +53551,18 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="26" t="s">
+      <c r="A90" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="B90" s="26"/>
-      <c r="C90" s="26"/>
-      <c r="D90" s="26"/>
-      <c r="E90" s="26"/>
-      <c r="F90" s="26"/>
-      <c r="G90" s="26"/>
-      <c r="H90" s="26"/>
-      <c r="I90" s="26"/>
-      <c r="J90" s="26"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="25"/>
+      <c r="D90" s="25"/>
+      <c r="E90" s="25"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="25"/>
+      <c r="H90" s="25"/>
+      <c r="I90" s="25"/>
+      <c r="J90" s="25"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
@@ -53547,7 +53588,7 @@
       <c r="D92" s="38" t="n">
         <v>-0.03</v>
       </c>
-      <c r="H92" s="25" t="s">
+      <c r="H92" s="28" t="s">
         <v>243</v>
       </c>
     </row>
@@ -53561,7 +53602,7 @@
       <c r="D93" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="H93" s="25" t="s">
+      <c r="H93" s="28" t="s">
         <v>245</v>
       </c>
     </row>
@@ -53575,7 +53616,7 @@
       <c r="D94" s="38" t="n">
         <v>0.015</v>
       </c>
-      <c r="H94" s="25" t="s">
+      <c r="H94" s="28" t="s">
         <v>247</v>
       </c>
     </row>
@@ -53691,23 +53732,23 @@
       <c r="D4" s="36" t="n">
         <v>18945.2</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
@@ -53779,7 +53820,7 @@
         <f aca="false">I6/I20</f>
         <v>0.985107824367827</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>260</v>
       </c>
     </row>
@@ -53816,7 +53857,7 @@
         <f aca="false">(Assumptions!G$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$92,Assumptions!$C$93,Assumptions!$C$94))</f>
         <v>0.17</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>263</v>
       </c>
     </row>
@@ -53853,7 +53894,7 @@
         <f aca="false">(Assumptions!G$27+CHOOSE(Assumptions!$C$5,Assumptions!$D$92,Assumptions!$D$93,Assumptions!$D$94))</f>
         <v>0.375</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>265</v>
       </c>
     </row>
@@ -53909,18 +53950,18 @@
       <c r="J11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
@@ -53992,7 +54033,7 @@
         <f aca="false">I13/I20</f>
         <v>0.014892175632173</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>269</v>
       </c>
     </row>
@@ -54029,7 +54070,7 @@
         <f aca="false">(Assumptions!G$24+CHOOSE(Assumptions!$C$5,Assumptions!$C$92,Assumptions!$C$93,Assumptions!$C$94))</f>
         <v>0.05</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="28" t="s">
         <v>263</v>
       </c>
     </row>
@@ -54066,7 +54107,7 @@
         <f aca="false">(Assumptions!G$28+CHOOSE(Assumptions!$C$5,Assumptions!$D$92,Assumptions!$D$93,Assumptions!$D$94))</f>
         <v>0.0288</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="28" t="s">
         <v>265</v>
       </c>
     </row>
@@ -54122,18 +54163,18 @@
       <c r="J18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
@@ -54280,18 +54321,18 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
@@ -54431,18 +54472,18 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
@@ -54620,7 +54661,7 @@
         <f aca="false">Revenue_Segments!I20</f>
         <v>78268.2642173478</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>289</v>
       </c>
     </row>
@@ -54656,7 +54697,7 @@
         <f aca="false">I4/H4-1</f>
         <v>0.168012086727309</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="28" t="s">
         <v>291</v>
       </c>
     </row>
@@ -54693,7 +54734,7 @@
         <f aca="false">I4-Revenue_Segments!I21</f>
         <v>49321.1905718437</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>293</v>
       </c>
     </row>
@@ -54733,7 +54774,7 @@
         <f aca="false">I4-I6</f>
         <v>28947.0736455041</v>
       </c>
-      <c r="J7" s="25"/>
+      <c r="J7" s="28"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
@@ -54771,7 +54812,7 @@
         <f aca="false">I7/I4</f>
         <v>0.369844328796142</v>
       </c>
-      <c r="J8" s="27" t="s">
+      <c r="J8" s="26" t="s">
         <v>295</v>
       </c>
     </row>
@@ -54808,7 +54849,7 @@
         <f aca="false">I4*Assumptions!G$31</f>
         <v>461.782758882352</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>297</v>
       </c>
     </row>
@@ -54845,7 +54886,7 @@
         <f aca="false">I4*Assumptions!G$32</f>
         <v>2191.51139808574</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>299</v>
       </c>
     </row>
@@ -54882,7 +54923,7 @@
         <f aca="false">I4*Assumptions!G$33</f>
         <v>1737.55546562512</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>301</v>
       </c>
     </row>
@@ -54919,7 +54960,7 @@
         <f aca="false">I4*Assumptions!G$34</f>
         <v>4711.74950588434</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>303</v>
       </c>
     </row>
@@ -54956,7 +54997,7 @@
         <f aca="false">FIN!I67</f>
         <v>14.3195314834984</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="28" t="s">
         <v>305</v>
       </c>
     </row>
@@ -54993,7 +55034,7 @@
         <f aca="false">Assumptions!G$35</f>
         <v>-174.6</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>307</v>
       </c>
     </row>
@@ -55033,7 +55074,7 @@
         <f aca="false">I7-I9-I10-I11-I12-I13+I14</f>
         <v>19655.554985543</v>
       </c>
-      <c r="J15" s="25"/>
+      <c r="J15" s="28"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
@@ -55068,7 +55109,7 @@
         <f aca="false">Assumptions!G$36</f>
         <v>-12.6</v>
       </c>
-      <c r="J16" s="27" t="s">
+      <c r="J16" s="26" t="s">
         <v>309</v>
       </c>
     </row>
@@ -55108,7 +55149,7 @@
         <f aca="false">I15+I16</f>
         <v>19642.954985543</v>
       </c>
-      <c r="J17" s="25"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
@@ -55143,7 +55184,7 @@
         <f aca="false">I17*Assumptions!G$37</f>
         <v>2586.97717159602</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>312</v>
       </c>
     </row>
@@ -55183,7 +55224,7 @@
         <f aca="false">I17-I18</f>
         <v>17055.977813947</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>314</v>
       </c>
     </row>
@@ -55220,7 +55261,7 @@
         <f aca="false">I19*(1-Assumptions!G$38)</f>
         <v>17055.977813947</v>
       </c>
-      <c r="J20" s="25" t="s">
+      <c r="J20" s="28" t="s">
         <v>316</v>
       </c>
     </row>
@@ -55260,7 +55301,7 @@
         <f aca="false">I19-I20</f>
         <v>0</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="J21" s="28" t="s">
         <v>318</v>
       </c>
     </row>
@@ -55300,7 +55341,7 @@
         <f aca="false">I20/I4</f>
         <v>0.217916903926517</v>
       </c>
-      <c r="J22" s="27" t="s">
+      <c r="J22" s="26" t="s">
         <v>320</v>
       </c>
     </row>
@@ -55340,7 +55381,7 @@
         <f aca="false">I20/Equity_Roll!$C$21</f>
         <v>8.86301071188267</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>322</v>
       </c>
     </row>
@@ -55380,7 +55421,7 @@
         <f aca="false">I17+I13</f>
         <v>19657.2745170265</v>
       </c>
-      <c r="J24" s="25" t="s">
+      <c r="J24" s="28" t="s">
         <v>324</v>
       </c>
     </row>
@@ -55505,7 +55546,7 @@
         <f aca="false">FIN!I63</f>
         <v>1565.36528434696</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>328</v>
       </c>
     </row>
@@ -55542,7 +55583,7 @@
         <f aca="false">FIN!I61</f>
         <v>13397.5488846913</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="28" t="s">
         <v>330</v>
       </c>
     </row>
@@ -55579,7 +55620,7 @@
         <f aca="false">Assumptions!G$42/365*IS!I4</f>
         <v>22729.9616631202</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>332</v>
       </c>
     </row>
@@ -55616,7 +55657,7 @@
         <f aca="false">IS!I4*Assumptions!G$45</f>
         <v>406.994973930208</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>334</v>
       </c>
     </row>
@@ -55653,7 +55694,7 @@
         <f aca="false">H8</f>
         <v>471.6</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>336</v>
       </c>
     </row>
@@ -55690,7 +55731,7 @@
         <f aca="false">Assumptions!G$43/365*IS!I6</f>
         <v>17161.0717880114</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>338</v>
       </c>
     </row>
@@ -55727,7 +55768,7 @@
         <f aca="false">H10</f>
         <v>3072.6</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>340</v>
       </c>
     </row>
@@ -55767,7 +55808,7 @@
         <f aca="false">I4+I5+I6+I7+I8+I9+I10</f>
         <v>58805.1425941</v>
       </c>
-      <c r="J11" s="25"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
@@ -55802,7 +55843,7 @@
         <f aca="false">PPE!I18</f>
         <v>27552.4619949137</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>343</v>
       </c>
     </row>
@@ -55839,7 +55880,7 @@
         <f aca="false">H13</f>
         <v>19.4</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="28" t="s">
         <v>336</v>
       </c>
     </row>
@@ -55876,7 +55917,7 @@
         <f aca="false">Schedules!I23</f>
         <v>256.18498806784</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>346</v>
       </c>
     </row>
@@ -55913,7 +55954,7 @@
         <f aca="false">H15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="28" t="s">
         <v>336</v>
       </c>
     </row>
@@ -55950,7 +55991,7 @@
         <f aca="false">H16</f>
         <v>4.2</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="28" t="s">
         <v>336</v>
       </c>
     </row>
@@ -55987,7 +56028,7 @@
         <f aca="false">H17</f>
         <v>322.1</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="28" t="s">
         <v>336</v>
       </c>
     </row>
@@ -56024,7 +56065,7 @@
         <f aca="false">H18</f>
         <v>486.8</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>351</v>
       </c>
     </row>
@@ -56061,7 +56102,7 @@
         <f aca="false">H19</f>
         <v>2891.7</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>353</v>
       </c>
     </row>
@@ -56101,7 +56142,7 @@
         <f aca="false">I12+I13+I14+I15+I16+I17+I18+I19</f>
         <v>31532.8469829816</v>
       </c>
-      <c r="J20" s="25"/>
+      <c r="J20" s="28"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
@@ -56139,7 +56180,7 @@
         <f aca="false">I11+I20</f>
         <v>90337.9895770816</v>
       </c>
-      <c r="J21" s="27" t="s">
+      <c r="J21" s="26" t="s">
         <v>356</v>
       </c>
     </row>
@@ -56176,7 +56217,7 @@
         <f aca="false">FIN!I24</f>
         <v>0</v>
       </c>
-      <c r="J22" s="25" t="s">
+      <c r="J22" s="28" t="s">
         <v>358</v>
       </c>
     </row>
@@ -56213,7 +56254,7 @@
         <f aca="false">Assumptions!G$44/365*IS!I6</f>
         <v>26755.0568033563</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>360</v>
       </c>
     </row>
@@ -56250,7 +56291,7 @@
         <f aca="false">H24</f>
         <v>65.8</v>
       </c>
-      <c r="J24" s="25" t="s">
+      <c r="J24" s="28" t="s">
         <v>336</v>
       </c>
     </row>
@@ -56287,7 +56328,7 @@
         <f aca="false">IS!I4*Assumptions!G$46</f>
         <v>2191.51139808574</v>
       </c>
-      <c r="J25" s="25" t="s">
+      <c r="J25" s="28" t="s">
         <v>363</v>
       </c>
     </row>
@@ -56324,7 +56365,7 @@
         <f aca="false">IS!I4*Assumptions!G$47</f>
         <v>1134.88983115154</v>
       </c>
-      <c r="J26" s="25" t="s">
+      <c r="J26" s="28" t="s">
         <v>365</v>
       </c>
     </row>
@@ -56361,7 +56402,7 @@
         <f aca="false">H27</f>
         <v>554.1</v>
       </c>
-      <c r="J27" s="25" t="s">
+      <c r="J27" s="28" t="s">
         <v>336</v>
       </c>
     </row>
@@ -56398,7 +56439,7 @@
         <f aca="false">FIN!I32</f>
         <v>0.100000000000023</v>
       </c>
-      <c r="J28" s="25" t="s">
+      <c r="J28" s="28" t="s">
         <v>368</v>
       </c>
     </row>
@@ -56435,7 +56476,7 @@
         <f aca="false">H29</f>
         <v>0</v>
       </c>
-      <c r="J29" s="25" t="s">
+      <c r="J29" s="28" t="s">
         <v>353</v>
       </c>
     </row>
@@ -56475,7 +56516,7 @@
         <f aca="false">I22+I23+I24+I25+I26+I27+I28+I29</f>
         <v>30701.4580325936</v>
       </c>
-      <c r="J30" s="25"/>
+      <c r="J30" s="28"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
@@ -56510,7 +56551,7 @@
         <f aca="false">FIN!I42</f>
         <v>0</v>
       </c>
-      <c r="J31" s="25" t="s">
+      <c r="J31" s="28" t="s">
         <v>372</v>
       </c>
     </row>
@@ -56547,7 +56588,7 @@
         <f aca="false">FIN!I50</f>
         <v>0</v>
       </c>
-      <c r="J32" s="25" t="s">
+      <c r="J32" s="28" t="s">
         <v>368</v>
       </c>
     </row>
@@ -56584,7 +56625,7 @@
         <f aca="false">H33</f>
         <v>504.6</v>
       </c>
-      <c r="J33" s="25" t="s">
+      <c r="J33" s="28" t="s">
         <v>375</v>
       </c>
     </row>
@@ -56624,7 +56665,7 @@
         <f aca="false">I31+I32+I33</f>
         <v>504.6</v>
       </c>
-      <c r="J34" s="25"/>
+      <c r="J34" s="28"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
@@ -56696,7 +56737,7 @@
         <f aca="false">Equity_Roll!I5</f>
         <v>1924.4</v>
       </c>
-      <c r="J36" s="25" t="s">
+      <c r="J36" s="28" t="s">
         <v>379</v>
       </c>
     </row>
@@ -56733,7 +56774,7 @@
         <f aca="false">Equity_Roll!I6</f>
         <v>1070.2</v>
       </c>
-      <c r="J37" s="25" t="s">
+      <c r="J37" s="28" t="s">
         <v>379</v>
       </c>
     </row>
@@ -56770,7 +56811,7 @@
         <f aca="false">Equity_Roll!I7</f>
         <v>0</v>
       </c>
-      <c r="J38" s="25" t="s">
+      <c r="J38" s="28" t="s">
         <v>379</v>
       </c>
     </row>
@@ -56807,7 +56848,7 @@
         <f aca="false">Equity_Roll!I8</f>
         <v>408.2</v>
       </c>
-      <c r="J39" s="25" t="s">
+      <c r="J39" s="28" t="s">
         <v>379</v>
       </c>
     </row>
@@ -56844,7 +56885,7 @@
         <f aca="false">Equity_Roll!I10</f>
         <v>6883.87545718627</v>
       </c>
-      <c r="J40" s="25" t="s">
+      <c r="J40" s="28" t="s">
         <v>384</v>
       </c>
     </row>
@@ -56881,7 +56922,7 @@
         <f aca="false">Equity_Roll!I12</f>
         <v>48829.6560873017</v>
       </c>
-      <c r="J41" s="25" t="s">
+      <c r="J41" s="28" t="s">
         <v>386</v>
       </c>
     </row>
@@ -56918,7 +56959,7 @@
         <f aca="false">H42</f>
         <v>0.2</v>
       </c>
-      <c r="J42" s="25" t="s">
+      <c r="J42" s="28" t="s">
         <v>388</v>
       </c>
     </row>
@@ -56992,7 +57033,7 @@
         <f aca="false">H44</f>
         <v>15.4</v>
       </c>
-      <c r="J44" s="25" t="s">
+      <c r="J44" s="28" t="s">
         <v>336</v>
       </c>
     </row>
@@ -57106,7 +57147,7 @@
         <f aca="false">I21-I46</f>
         <v>0</v>
       </c>
-      <c r="J47" s="25" t="s">
+      <c r="J47" s="28" t="s">
         <v>394</v>
       </c>
     </row>
@@ -57231,7 +57272,7 @@
         <f aca="false">IS!I20</f>
         <v>17055.977813947</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>397</v>
       </c>
     </row>
@@ -57268,7 +57309,7 @@
         <f aca="false">PPE!I19</f>
         <v>2908.33675064901</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="28" t="s">
         <v>399</v>
       </c>
     </row>
@@ -57305,7 +57346,7 @@
         <f aca="false">FIN!I64</f>
         <v>1.7529</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>401</v>
       </c>
     </row>
@@ -57342,7 +57383,7 @@
         <f aca="false">-Schedules!I18</f>
         <v>-1413.05607955134</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>403</v>
       </c>
     </row>
@@ -57379,7 +57420,7 @@
         <f aca="false">I4+I5+I6+I7</f>
         <v>18553.0113850447</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>405</v>
       </c>
     </row>
@@ -57416,7 +57457,7 @@
         <f aca="false">-PPE!I14</f>
         <v>-6605.84149994415</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>407</v>
       </c>
     </row>
@@ -57453,7 +57494,7 @@
         <f aca="false">PPE!I9</f>
         <v>218.483293628183</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>409</v>
       </c>
     </row>
@@ -57490,7 +57531,7 @@
         <f aca="false">-FIN!I62</f>
         <v>-7389.28634906777</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>411</v>
       </c>
     </row>
@@ -57527,7 +57568,7 @@
         <f aca="false">I9+I10+I11</f>
         <v>-13776.6445553837</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>413</v>
       </c>
     </row>
@@ -57564,7 +57605,7 @@
         <f aca="false">FIN!I57</f>
         <v>-102.2</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="28" t="s">
         <v>415</v>
       </c>
     </row>
@@ -57601,7 +57642,7 @@
         <f aca="false">-FIN!I64</f>
         <v>-1.7529</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>417</v>
       </c>
     </row>
@@ -57638,7 +57679,7 @@
         <f aca="false">-Schedules!I26</f>
         <v>-4447.24478038396</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="28" t="s">
         <v>419</v>
       </c>
     </row>
@@ -57675,7 +57716,7 @@
         <f aca="false">I13+I14+I15</f>
         <v>-4551.19768038396</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="28" t="s">
         <v>421</v>
       </c>
     </row>
@@ -57712,7 +57753,7 @@
         <f aca="false">I8+I12+I16</f>
         <v>225.16914927698</v>
       </c>
-      <c r="J17" s="25"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
@@ -57747,7 +57788,7 @@
         <f aca="false">H19</f>
         <v>1340.19613506997</v>
       </c>
-      <c r="J18" s="27" t="s">
+      <c r="J18" s="26" t="s">
         <v>424</v>
       </c>
     </row>
@@ -57784,7 +57825,7 @@
         <f aca="false">I18+I17</f>
         <v>1565.36528434695</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>426</v>
       </c>
     </row>
@@ -57877,18 +57918,18 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>429</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
@@ -57926,7 +57967,7 @@
         <f aca="false">BS!I6</f>
         <v>22729.9616631202</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>430</v>
       </c>
     </row>
@@ -57966,7 +58007,7 @@
         <f aca="false">BS!I7</f>
         <v>406.994973930208</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>431</v>
       </c>
     </row>
@@ -58006,7 +58047,7 @@
         <f aca="false">BS!I8</f>
         <v>471.6</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>432</v>
       </c>
     </row>
@@ -58046,7 +58087,7 @@
         <f aca="false">BS!I9</f>
         <v>17161.0717880114</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>433</v>
       </c>
     </row>
@@ -58086,7 +58127,7 @@
         <f aca="false">SUM(I6:I9)</f>
         <v>40769.6284250618</v>
       </c>
-      <c r="J10" s="25"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
@@ -58124,7 +58165,7 @@
         <f aca="false">BS!I23</f>
         <v>26755.0568033563</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>435</v>
       </c>
     </row>
@@ -58164,7 +58205,7 @@
         <f aca="false">BS!I24</f>
         <v>65.8</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>436</v>
       </c>
     </row>
@@ -58204,7 +58245,7 @@
         <f aca="false">BS!I25</f>
         <v>2191.51139808574</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="28" t="s">
         <v>437</v>
       </c>
     </row>
@@ -58244,7 +58285,7 @@
         <f aca="false">BS!I26</f>
         <v>1134.88983115154</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>437</v>
       </c>
     </row>
@@ -58284,7 +58325,7 @@
         <f aca="false">BS!I27</f>
         <v>554.1</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="28" t="s">
         <v>436</v>
       </c>
     </row>
@@ -58324,7 +58365,7 @@
         <f aca="false">SUM(I11:I15)</f>
         <v>30701.3580325936</v>
       </c>
-      <c r="J16" s="25"/>
+      <c r="J16" s="28"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
@@ -58362,7 +58403,7 @@
         <f aca="false">I10-I16</f>
         <v>10068.2703924682</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="28" t="s">
         <v>440</v>
       </c>
     </row>
@@ -58390,23 +58431,23 @@
         <f aca="false">I17-H17</f>
         <v>1413.05607955134</v>
       </c>
-      <c r="J18" s="27" t="s">
+      <c r="J18" s="26" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="25" t="s">
         <v>443</v>
       </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
@@ -58432,7 +58473,7 @@
         <f aca="false">H23</f>
         <v>278.461943552</v>
       </c>
-      <c r="J21" s="27" t="s">
+      <c r="J21" s="26" t="s">
         <v>445</v>
       </c>
     </row>
@@ -58460,7 +58501,7 @@
         <f aca="false">I21*Assumptions!$C$55</f>
         <v>22.27695548416</v>
       </c>
-      <c r="J22" s="25" t="s">
+      <c r="J22" s="28" t="s">
         <v>447</v>
       </c>
     </row>
@@ -58488,23 +58529,23 @@
         <f aca="false">I21-I22</f>
         <v>256.18498806784</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="25" t="s">
         <v>450</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
@@ -58530,7 +58571,7 @@
         <f aca="false">IS!H20*Assumptions!G$58</f>
         <v>4447.24478038396</v>
       </c>
-      <c r="J26" s="25" t="s">
+      <c r="J26" s="28" t="s">
         <v>452</v>
       </c>
     </row>
@@ -58626,18 +58667,18 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>455</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
@@ -58662,7 +58703,7 @@
         <f aca="false">H10</f>
         <v>21848.3293628183</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="26" t="s">
         <v>457</v>
       </c>
     </row>
@@ -58690,7 +58731,7 @@
         <f aca="false">(I13+I14)*Assumptions!$C$51</f>
         <v>6606.50679066632</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>459</v>
       </c>
     </row>
@@ -58718,7 +58759,7 @@
         <f aca="false">I6*Assumptions!$C$52+I7*Assumptions!$C$53</f>
         <v>2886.05979516485</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>461</v>
       </c>
     </row>
@@ -58746,7 +58787,7 @@
         <f aca="false">I6*Assumptions!$C$54</f>
         <v>218.483293628183</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>463</v>
       </c>
     </row>
@@ -58774,23 +58815,23 @@
         <f aca="false">I6+I7-I8-I9</f>
         <v>25350.2930646916</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="25" t="s">
         <v>466</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
@@ -58815,7 +58856,7 @@
         <f aca="false">H15</f>
         <v>2202.83422094428</v>
       </c>
-      <c r="J13" s="27" t="s">
+      <c r="J13" s="26" t="s">
         <v>468</v>
       </c>
     </row>
@@ -58843,7 +58884,7 @@
         <f aca="false">IS!I4*Assumptions!G$50</f>
         <v>6605.84149994415</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>470</v>
       </c>
     </row>
@@ -58871,23 +58912,23 @@
         <f aca="false">I13+I14-I7</f>
         <v>2202.16893022211</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="28" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>473</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
@@ -58925,7 +58966,7 @@
         <f aca="false">I10+I15</f>
         <v>27552.4619949137</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>475</v>
       </c>
     </row>
@@ -58965,7 +59006,7 @@
         <f aca="false">I8+Schedules!I22</f>
         <v>2908.33675064901</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>477</v>
       </c>
     </row>
@@ -58993,7 +59034,7 @@
         <f aca="false">I8/I6</f>
         <v>0.132095216400224</v>
       </c>
-      <c r="J20" s="25" t="s">
+      <c r="J20" s="28" t="s">
         <v>479</v>
       </c>
     </row>
@@ -59021,7 +59062,7 @@
         <f aca="false">I6/I8</f>
         <v>7.57029684534667</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="J21" s="28" t="s">
         <v>481</v>
       </c>
     </row>
